--- a/HansoInputTool/data/Input.xlsx
+++ b/HansoInputTool/data/Input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ligdoor\source\repos\HansoInputTool\HansoInputTool\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ligdoor\source\repos\HansoInputTool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8113E0AF-F86C-4C9E-AF00-D611AA105C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A397ED-C3A8-4BA3-8097-04545DC86DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="892" xr2:uid="{88C334D1-54A2-4A07-AD58-9761E3E044DD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="892" activeTab="12" xr2:uid="{88C334D1-54A2-4A07-AD58-9761E3E044DD}"/>
   </bookViews>
   <sheets>
     <sheet name="寝台車 29" sheetId="32" r:id="rId1"/>
@@ -25,10 +25,13 @@
     <sheet name="東日本セレモニー 2259" sheetId="40" r:id="rId10"/>
     <sheet name="東日本セレモニー 2262" sheetId="41" r:id="rId11"/>
     <sheet name="東日本セレモニー 2380" sheetId="42" r:id="rId12"/>
+    <sheet name="Template1" sheetId="52" r:id="rId13"/>
+    <sheet name="Template2" sheetId="53" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'CH東富士 寝台車 1105'!$A$1:$I$103</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'CH東富士 霊柩車 1381'!$A$1:$I$103</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">Template1!$A$1:$I$103</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'寝台車 29'!$A$1:$I$103</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'寝台車 30'!$A$1:$I$103</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'大月 寝台車 1603'!$A$1:$I$103</definedName>
@@ -51,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="33">
   <si>
     <t>走行キロ(ｋｍ)</t>
     <rPh sb="0" eb="2">
@@ -1144,7 +1147,527 @@
     <cellStyle name="通貨" xfId="3" builtinId="7"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="124">
+  <dxfs count="146">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="10" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="6" formatCode="#,##0;[Red]\-#,##0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="6" formatCode="#,##0;[Red]\-#,##0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="6" formatCode="#,##0;[Red]\-#,##0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="0.0%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="179" formatCode="0&quot;Km&quot;"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="179" formatCode="0&quot;Km&quot;"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3936,7 +4459,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B57D332C-F6B7-4A53-82A7-29C4EC1C08D8}" name="搬送車_29" displayName="搬送車_29" ref="A2:I103" totalsRowShown="0" headerRowDxfId="123" headerRowBorderDxfId="122" tableBorderDxfId="121">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B57D332C-F6B7-4A53-82A7-29C4EC1C08D8}" name="搬送車_29" displayName="搬送車_29" ref="A2:I103" totalsRowShown="0" headerRowDxfId="145" headerRowBorderDxfId="144" tableBorderDxfId="143">
   <autoFilter ref="A2:I103" xr:uid="{D37F7CB6-6FCA-4B25-9A8A-2768897431DC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3954,17 +4477,17 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{8E5C5757-D9A9-420C-8AB8-38ACC45B8572}" name="基本料" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{989646CC-28B0-440A-B746-9F45A38CB63B}" name="走行料" dataDxfId="119"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="割増料" dataDxfId="118"/>
-    <tableColumn id="12" xr3:uid="{42F07E7A-A4DA-42AC-9C95-A9B310271D84}" name="合計" dataDxfId="117"/>
+    <tableColumn id="10" xr3:uid="{8E5C5757-D9A9-420C-8AB8-38ACC45B8572}" name="基本料" dataDxfId="142"/>
+    <tableColumn id="11" xr3:uid="{989646CC-28B0-440A-B746-9F45A38CB63B}" name="走行料" dataDxfId="141"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="割増料" dataDxfId="140"/>
+    <tableColumn id="12" xr3:uid="{42F07E7A-A4DA-42AC-9C95-A9B310271D84}" name="合計" dataDxfId="139"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F997EBC0-AB28-40F0-804E-94B60AF96B7C}" name="東日本セレモニー_2259" displayName="東日本セレモニー_2259" ref="A3:K6" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F997EBC0-AB28-40F0-804E-94B60AF96B7C}" name="東日本セレモニー_2259" displayName="東日本セレモニー_2259" ref="A3:K6" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" tableBorderDxfId="63">
   <autoFilter ref="A3:K6" xr:uid="{40D577DC-1C11-43A4-A797-7C623FBF0B6A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3979,24 +4502,24 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="台数" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="支社名" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="車輌番号" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="延実在_x000a_車輌数" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="延実働_x000a_車輌数" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="稼働率" dataDxfId="35" dataCellStyle="パーセント"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1100-000007000000}" name="搬送回数" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1100-000008000000}" name="有料キロ数" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1100-000009000000}" name="無料キロ数" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1100-00000A000000}" name="総走行ｋｍ" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1100-00000B000000}" name="運輸実績" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="台数" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="支社名" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="車輌番号" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="延実在_x000a_車輌数" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="延実働_x000a_車輌数" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="稼働率" dataDxfId="57" dataCellStyle="パーセント"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1100-000007000000}" name="搬送回数" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1100-000008000000}" name="有料キロ数" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1100-000009000000}" name="無料キロ数" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1100-00000A000000}" name="総走行ｋｍ" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1100-00000B000000}" name="運輸実績" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{862F6584-B183-4A23-8F27-06CB661F65B0}" name="東日本セレモニー_2262" displayName="東日本セレモニー_2262" ref="A3:K6" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{862F6584-B183-4A23-8F27-06CB661F65B0}" name="東日本セレモニー_2262" displayName="東日本セレモニー_2262" ref="A3:K6" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48">
   <autoFilter ref="A3:K6" xr:uid="{C7BC50FA-9AB2-4289-A532-2490856061EE}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4011,24 +4534,24 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1300-000001000000}" name="台数" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1300-000002000000}" name="支社名" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1300-000003000000}" name="車輌番号" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1300-000004000000}" name="延実在_x000a_車輌数" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1300-000005000000}" name="延実働_x000a_車輌数" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1300-000006000000}" name="稼働率" dataDxfId="20" dataCellStyle="パーセント"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1300-000007000000}" name="搬送回数" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1300-000008000000}" name="有料キロ数" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1300-000009000000}" name="無料キロ数" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1300-00000A000000}" name="総走行ｋｍ" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1300-00000B000000}" name="運輸実績" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1300-000001000000}" name="台数" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1300-000002000000}" name="支社名" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1300-000003000000}" name="車輌番号" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1300-000004000000}" name="延実在_x000a_車輌数" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1300-000005000000}" name="延実働_x000a_車輌数" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1300-000006000000}" name="稼働率" dataDxfId="42" dataCellStyle="パーセント"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1300-000007000000}" name="搬送回数" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1300-000008000000}" name="有料キロ数" dataDxfId="40"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1300-000009000000}" name="無料キロ数" dataDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1300-00000A000000}" name="総走行ｋｍ" dataDxfId="38"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1300-00000B000000}" name="運輸実績" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{46ACFE33-27E3-4C96-8A5A-86E68AD61DB4}" name="東日本セレモニー_2380" displayName="東日本セレモニー_2380" ref="A3:K6" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{46ACFE33-27E3-4C96-8A5A-86E68AD61DB4}" name="東日本セレモニー_2380" displayName="東日本セレモニー_2380" ref="A3:K6" totalsRowShown="0" headerRowDxfId="36" dataDxfId="34" headerRowBorderDxfId="35" tableBorderDxfId="33">
   <autoFilter ref="A3:K6" xr:uid="{D061A9DC-AE38-4E07-9D9C-C1BF1663F569}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4043,24 +4566,84 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1500-000001000000}" name="台数" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1500-000002000000}" name="支社名" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1500-000003000000}" name="車輌番号" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1500-000004000000}" name="延実在_x000a_車輌数" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1500-000005000000}" name="延実働_x000a_車輌数" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1500-000006000000}" name="稼働率" dataDxfId="5" dataCellStyle="パーセント"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1500-000007000000}" name="搬送回数" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1500-000008000000}" name="有料キロ数" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1500-000009000000}" name="無料キロ数" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1500-00000A000000}" name="総走行ｋｍ" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1500-00000B000000}" name="運輸実績" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1500-000001000000}" name="台数" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1500-000002000000}" name="支社名" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1500-000003000000}" name="車輌番号" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1500-000004000000}" name="延実在_x000a_車輌数" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1500-000005000000}" name="延実働_x000a_車輌数" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1500-000006000000}" name="稼働率" dataDxfId="27" dataCellStyle="パーセント"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1500-000007000000}" name="搬送回数" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1500-000008000000}" name="有料キロ数" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1500-000009000000}" name="無料キロ数" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1500-00000A000000}" name="総走行ｋｍ" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1500-00000B000000}" name="運輸実績" dataDxfId="22"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CEC7FB5E-D858-49F1-A06F-A6579C29929C}" name="Template1" displayName="Template1" ref="A2:I103" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19">
+  <autoFilter ref="A2:I103" xr:uid="{D37F7CB6-6FCA-4B25-9A8A-2768897431DC}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{2E01F6BA-0915-4FA6-A38A-3C5B53F439AD}" name="No"/>
+    <tableColumn id="2" xr3:uid="{7A832FC4-E720-4DAA-8007-15C8F0A10D93}" name="日"/>
+    <tableColumn id="3" xr3:uid="{16A282EC-D5A4-4109-B74B-BA9F76E4AD75}" name="搬送数"/>
+    <tableColumn id="4" xr3:uid="{4FC5ACC5-7F36-4976-9D1F-9E861AEBE018}" name="有料キロ数"/>
+    <tableColumn id="5" xr3:uid="{F7347B8B-2E0E-49A8-9373-2F2E5BFCA524}" name="無料キロ数"/>
+    <tableColumn id="10" xr3:uid="{BAE13533-D0C1-45BF-9BB5-5E2DF23FCE3B}" name="基本料" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{569C5270-3196-4243-B2E8-55F753AB64B6}" name="走行料" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{9F216DD6-F338-4FDF-B88B-7440D759C359}" name="割増料" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{2003CBB7-010B-4880-8052-074AD529A98E}" name="合計" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6613C80E-DB2E-4DFC-B3E7-E7F10516A045}" name="Template2" displayName="Template2" ref="A3:K6" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11">
+  <autoFilter ref="A3:K6" xr:uid="{F9BAA250-893E-409E-AA21-0EAE21A25964}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{96574F85-AA3E-4C49-AAB5-C2B62BF4BF48}" name="台数" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{0468C668-CC9A-4E94-9545-F0C852FCB9FC}" name="支社名" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{73A99B0A-6BB3-4C26-8B3E-68F90D339F6C}" name="車輌番号" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{DD6EFB83-AE79-4189-9FC8-CF24615E38F9}" name="延実在_x000a_車輌数" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{CDA52592-D070-4EF3-948C-2344BEFDAA00}" name="延実働_x000a_車輌数" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{84C66141-24A9-48D1-B03F-8ECEAF73C674}" name="稼働率" dataDxfId="5" dataCellStyle="パーセント"/>
+    <tableColumn id="7" xr3:uid="{2941850A-C9CB-403E-A0A5-DFD29E860358}" name="搬送回数" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{4CFD0BD9-C80E-414D-B07D-F800DA56DA45}" name="有料キロ数" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{37994764-7CA9-4034-AA84-2A0F83B29B7F}" name="無料キロ数" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{15A28708-E8A6-4A1F-BA36-36B0025A480F}" name="総走行ｋｍ" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{A2D92090-8794-41CD-B401-C2C6894CD473}" name="運輸実績" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9B36EAD0-C6B4-40D9-9B47-A820E2B69515}" name="搬送車_295" displayName="搬送車_295" ref="A2:I103" totalsRowShown="0" headerRowDxfId="116" headerRowBorderDxfId="115" tableBorderDxfId="114">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9B36EAD0-C6B4-40D9-9B47-A820E2B69515}" name="搬送車_295" displayName="搬送車_295" ref="A2:I103" totalsRowShown="0" headerRowDxfId="138" headerRowBorderDxfId="137" tableBorderDxfId="136">
   <autoFilter ref="A2:I103" xr:uid="{D37F7CB6-6FCA-4B25-9A8A-2768897431DC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4078,17 +4661,17 @@
     <tableColumn id="3" xr3:uid="{79371B50-53B7-4E0E-9AFD-B113124FE6FB}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{AA084B1D-DEA8-4D49-9F4C-CF3C7E267DDA}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{27C81F93-DBAE-4977-84AD-25AE42F3AE68}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{938B1D7B-D397-4B00-B7C4-26946C6AB679}" name="基本料" dataDxfId="113"/>
-    <tableColumn id="11" xr3:uid="{0C9D668F-8480-4C7B-AB74-5510E444D145}" name="走行料" dataDxfId="112"/>
-    <tableColumn id="8" xr3:uid="{05ECCC91-80DF-4305-9D7E-1A5FF28D7E87}" name="割増料" dataDxfId="111"/>
-    <tableColumn id="12" xr3:uid="{4D9AE709-9731-4F2E-BFC6-7E015F896C5F}" name="合計" dataDxfId="110"/>
+    <tableColumn id="10" xr3:uid="{938B1D7B-D397-4B00-B7C4-26946C6AB679}" name="基本料" dataDxfId="135"/>
+    <tableColumn id="11" xr3:uid="{0C9D668F-8480-4C7B-AB74-5510E444D145}" name="走行料" dataDxfId="134"/>
+    <tableColumn id="8" xr3:uid="{05ECCC91-80DF-4305-9D7E-1A5FF28D7E87}" name="割増料" dataDxfId="133"/>
+    <tableColumn id="12" xr3:uid="{4D9AE709-9731-4F2E-BFC6-7E015F896C5F}" name="合計" dataDxfId="132"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{26B0909A-602F-441C-9BE6-4B0CC72FDCF5}" name="搬送車_2957" displayName="搬送車_2957" ref="A2:I104" totalsRowShown="0" headerRowDxfId="109" headerRowBorderDxfId="108" tableBorderDxfId="107">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{26B0909A-602F-441C-9BE6-4B0CC72FDCF5}" name="搬送車_2957" displayName="搬送車_2957" ref="A2:I104" totalsRowShown="0" headerRowDxfId="131" headerRowBorderDxfId="130" tableBorderDxfId="129">
   <autoFilter ref="A2:I104" xr:uid="{D37F7CB6-6FCA-4B25-9A8A-2768897431DC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4106,17 +4689,17 @@
     <tableColumn id="3" xr3:uid="{9E9596FE-7994-4350-8C22-F97112832C62}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{B9077B33-BF84-417E-A20C-CDB8322B3FB4}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{3AD41ABD-E57D-4695-A3D8-64D73E52FEB3}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{51006AAF-5BFE-48AD-B9EF-9B8804255302}" name="基本料" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{25F64C39-D539-4BF9-A417-F8B395DFACCE}" name="走行料" dataDxfId="105"/>
-    <tableColumn id="8" xr3:uid="{5ED86686-236C-48AE-8D77-1C7173C8E9A5}" name="割増料" dataDxfId="104"/>
-    <tableColumn id="12" xr3:uid="{057ABC4F-5B93-407E-8F8F-2E863BDA8669}" name="合計" dataDxfId="103"/>
+    <tableColumn id="10" xr3:uid="{51006AAF-5BFE-48AD-B9EF-9B8804255302}" name="基本料" dataDxfId="128"/>
+    <tableColumn id="11" xr3:uid="{25F64C39-D539-4BF9-A417-F8B395DFACCE}" name="走行料" dataDxfId="127"/>
+    <tableColumn id="8" xr3:uid="{5ED86686-236C-48AE-8D77-1C7173C8E9A5}" name="割増料" dataDxfId="126"/>
+    <tableColumn id="12" xr3:uid="{057ABC4F-5B93-407E-8F8F-2E863BDA8669}" name="合計" dataDxfId="125"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{0524AC59-C802-4D76-94CB-D82925E9D865}" name="搬送車_29578" displayName="搬送車_29578" ref="A2:I103" totalsRowShown="0" headerRowDxfId="102" headerRowBorderDxfId="101" tableBorderDxfId="100">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{0524AC59-C802-4D76-94CB-D82925E9D865}" name="搬送車_29578" displayName="搬送車_29578" ref="A2:I103" totalsRowShown="0" headerRowDxfId="124" headerRowBorderDxfId="123" tableBorderDxfId="122">
   <autoFilter ref="A2:I103" xr:uid="{D37F7CB6-6FCA-4B25-9A8A-2768897431DC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4134,17 +4717,17 @@
     <tableColumn id="3" xr3:uid="{715C9E46-2D37-480B-A1C8-2B27E249874D}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{09B14F93-456C-4CF5-9F9D-FEF341A5BB0D}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{FB9E08B3-0400-4000-95EE-050EFCD92198}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{08DCDC24-909E-4C14-9D15-AA0B039D9264}" name="基本料" dataDxfId="99"/>
-    <tableColumn id="11" xr3:uid="{563FD2FE-2AA8-416A-BE69-F890107E240B}" name="走行料" dataDxfId="98"/>
-    <tableColumn id="8" xr3:uid="{6670DCFD-782F-4BE7-9B35-BE1CAB597CEE}" name="割増料" dataDxfId="97"/>
-    <tableColumn id="12" xr3:uid="{135B5646-38D1-4A89-83E4-7D9DAAA164A1}" name="合計" dataDxfId="96"/>
+    <tableColumn id="10" xr3:uid="{08DCDC24-909E-4C14-9D15-AA0B039D9264}" name="基本料" dataDxfId="121"/>
+    <tableColumn id="11" xr3:uid="{563FD2FE-2AA8-416A-BE69-F890107E240B}" name="走行料" dataDxfId="120"/>
+    <tableColumn id="8" xr3:uid="{6670DCFD-782F-4BE7-9B35-BE1CAB597CEE}" name="割増料" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{135B5646-38D1-4A89-83E4-7D9DAAA164A1}" name="合計" dataDxfId="118"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B05C82E1-49E9-4444-931A-5A69D254306C}" name="搬送車_2957810" displayName="搬送車_2957810" ref="A2:I103" totalsRowShown="0" headerRowDxfId="95" headerRowBorderDxfId="94" tableBorderDxfId="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B05C82E1-49E9-4444-931A-5A69D254306C}" name="搬送車_2957810" displayName="搬送車_2957810" ref="A2:I103" totalsRowShown="0" headerRowDxfId="117" headerRowBorderDxfId="116" tableBorderDxfId="115">
   <autoFilter ref="A2:I103" xr:uid="{D37F7CB6-6FCA-4B25-9A8A-2768897431DC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4162,17 +4745,17 @@
     <tableColumn id="3" xr3:uid="{B497F7BD-944D-4C2D-9019-7E98E21CC0A8}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{FB6C297D-A988-45FB-BE98-69ED10845FE4}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{F5DC85AC-CE34-4790-901C-F58515F73513}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{C31851C7-4031-4656-A568-F76E30583D6B}" name="基本料" dataDxfId="92"/>
-    <tableColumn id="11" xr3:uid="{361813D8-AAB0-4B45-913F-956A170A26CA}" name="走行料" dataDxfId="91"/>
-    <tableColumn id="8" xr3:uid="{37FF20D8-D9A4-4626-9F8F-AB6D36A385A4}" name="割増料" dataDxfId="90"/>
-    <tableColumn id="12" xr3:uid="{6B6F3918-6C6D-4A79-BA3A-895B6CA7068D}" name="合計" dataDxfId="89"/>
+    <tableColumn id="10" xr3:uid="{C31851C7-4031-4656-A568-F76E30583D6B}" name="基本料" dataDxfId="114"/>
+    <tableColumn id="11" xr3:uid="{361813D8-AAB0-4B45-913F-956A170A26CA}" name="走行料" dataDxfId="113"/>
+    <tableColumn id="8" xr3:uid="{37FF20D8-D9A4-4626-9F8F-AB6D36A385A4}" name="割増料" dataDxfId="112"/>
+    <tableColumn id="12" xr3:uid="{6B6F3918-6C6D-4A79-BA3A-895B6CA7068D}" name="合計" dataDxfId="111"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{ADBB328C-774E-4BE2-8188-01322F30917D}" name="搬送車_295781011" displayName="搬送車_295781011" ref="A2:I103" totalsRowShown="0" headerRowDxfId="88" headerRowBorderDxfId="87" tableBorderDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{ADBB328C-774E-4BE2-8188-01322F30917D}" name="搬送車_295781011" displayName="搬送車_295781011" ref="A2:I103" totalsRowShown="0" headerRowDxfId="110" headerRowBorderDxfId="109" tableBorderDxfId="108">
   <autoFilter ref="A2:I103" xr:uid="{D37F7CB6-6FCA-4B25-9A8A-2768897431DC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4190,17 +4773,17 @@
     <tableColumn id="3" xr3:uid="{79DAFC1C-874E-45D0-BC19-7AC748BA07A7}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{FA6FDB18-2DCB-4749-8B6A-797861C38F8C}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{773118EF-3E40-4559-807B-CC187C016D8B}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{6BE7FC22-4B6D-425D-A673-C801B3F6B342}" name="基本料" dataDxfId="85"/>
-    <tableColumn id="11" xr3:uid="{935282A6-3B91-4C40-BE85-227196F33B8C}" name="走行料" dataDxfId="84"/>
-    <tableColumn id="8" xr3:uid="{91B26B2B-045B-4463-AF7D-0D230B8BAF1F}" name="割増料" dataDxfId="83"/>
-    <tableColumn id="12" xr3:uid="{58276718-26DC-4A80-9440-6FC52D5676FA}" name="合計" dataDxfId="82"/>
+    <tableColumn id="10" xr3:uid="{6BE7FC22-4B6D-425D-A673-C801B3F6B342}" name="基本料" dataDxfId="107"/>
+    <tableColumn id="11" xr3:uid="{935282A6-3B91-4C40-BE85-227196F33B8C}" name="走行料" dataDxfId="106"/>
+    <tableColumn id="8" xr3:uid="{91B26B2B-045B-4463-AF7D-0D230B8BAF1F}" name="割増料" dataDxfId="105"/>
+    <tableColumn id="12" xr3:uid="{58276718-26DC-4A80-9440-6FC52D5676FA}" name="合計" dataDxfId="104"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{C1B82D02-25F0-449F-988F-27FE27EDE582}" name="搬送車_29578101116" displayName="搬送車_29578101116" ref="A2:I103" totalsRowShown="0" headerRowDxfId="81" headerRowBorderDxfId="80" tableBorderDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{C1B82D02-25F0-449F-988F-27FE27EDE582}" name="搬送車_29578101116" displayName="搬送車_29578101116" ref="A2:I103" totalsRowShown="0" headerRowDxfId="103" headerRowBorderDxfId="102" tableBorderDxfId="101">
   <autoFilter ref="A2:I103" xr:uid="{D37F7CB6-6FCA-4B25-9A8A-2768897431DC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4218,17 +4801,17 @@
     <tableColumn id="3" xr3:uid="{448B6257-96DE-44C9-92AD-B9F428CC9220}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{3C5647BC-CAAC-47FB-91F4-25C462D588F9}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{09714F5A-EE00-4E50-9192-CD833077E2AF}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{4A130223-30F0-41A9-9B04-6B18B9230A51}" name="基本料" dataDxfId="78"/>
-    <tableColumn id="11" xr3:uid="{3E56248E-23DB-45BE-8702-F5E843DA2E92}" name="走行料" dataDxfId="77"/>
-    <tableColumn id="8" xr3:uid="{23D51664-9821-4EBC-951A-BF4176CBDBF5}" name="割増料" dataDxfId="76"/>
-    <tableColumn id="12" xr3:uid="{97A6BF74-97CC-47DB-B277-B351374220FB}" name="合計" dataDxfId="75"/>
+    <tableColumn id="10" xr3:uid="{4A130223-30F0-41A9-9B04-6B18B9230A51}" name="基本料" dataDxfId="100"/>
+    <tableColumn id="11" xr3:uid="{3E56248E-23DB-45BE-8702-F5E843DA2E92}" name="走行料" dataDxfId="99"/>
+    <tableColumn id="8" xr3:uid="{23D51664-9821-4EBC-951A-BF4176CBDBF5}" name="割増料" dataDxfId="98"/>
+    <tableColumn id="12" xr3:uid="{97A6BF74-97CC-47DB-B277-B351374220FB}" name="合計" dataDxfId="97"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6BBF6397-0F09-4D6D-8633-345070A63E80}" name="東日本セレモニー_2" displayName="東日本セレモニー_2" ref="A3:K6" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6BBF6397-0F09-4D6D-8633-345070A63E80}" name="東日本セレモニー_2" displayName="東日本セレモニー_2" ref="A3:K6" totalsRowShown="0" headerRowDxfId="96" dataDxfId="94" headerRowBorderDxfId="95" tableBorderDxfId="93">
   <autoFilter ref="A3:K6" xr:uid="{F9BAA250-893E-409E-AA21-0EAE21A25964}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4243,24 +4826,24 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{53D3760A-4822-441A-9A2A-EFAD7E982A15}" name="台数" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{88416A14-103D-49B9-B879-4AB460B9BDFB}" name="支社名" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{4D51AF80-59C9-44C6-948C-B74A72BC4E9D}" name="車輌番号" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{A7F0EB96-EF15-4099-89C5-01D2C7062890}" name="延実在_x000a_車輌数" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{ABB51286-0445-4368-A3EF-D62F055709C0}" name="延実働_x000a_車輌数" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{8D7781CD-7A8C-45BF-9076-9875CB2D3503}" name="稼働率" dataDxfId="65" dataCellStyle="パーセント"/>
-    <tableColumn id="7" xr3:uid="{F2342681-D614-4082-AEDC-A277819F8EA0}" name="搬送回数" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{DB9B3737-792B-412A-A234-8F6EDD5FFA99}" name="有料キロ数" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{3CB90409-1FA9-46E6-89E3-9047DCE9D51A}" name="無料キロ数" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{48359F0E-44C5-482A-80DE-7AC18AC6A8CD}" name="総走行ｋｍ" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{D9733BFC-5F18-4B1B-B516-97F89C4F5A76}" name="運輸実績" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{53D3760A-4822-441A-9A2A-EFAD7E982A15}" name="台数" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{88416A14-103D-49B9-B879-4AB460B9BDFB}" name="支社名" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{4D51AF80-59C9-44C6-948C-B74A72BC4E9D}" name="車輌番号" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{A7F0EB96-EF15-4099-89C5-01D2C7062890}" name="延実在_x000a_車輌数" dataDxfId="89"/>
+    <tableColumn id="5" xr3:uid="{ABB51286-0445-4368-A3EF-D62F055709C0}" name="延実働_x000a_車輌数" dataDxfId="88"/>
+    <tableColumn id="6" xr3:uid="{8D7781CD-7A8C-45BF-9076-9875CB2D3503}" name="稼働率" dataDxfId="87" dataCellStyle="パーセント"/>
+    <tableColumn id="7" xr3:uid="{F2342681-D614-4082-AEDC-A277819F8EA0}" name="搬送回数" dataDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{DB9B3737-792B-412A-A234-8F6EDD5FFA99}" name="有料キロ数" dataDxfId="85"/>
+    <tableColumn id="9" xr3:uid="{3CB90409-1FA9-46E6-89E3-9047DCE9D51A}" name="無料キロ数" dataDxfId="84"/>
+    <tableColumn id="10" xr3:uid="{48359F0E-44C5-482A-80DE-7AC18AC6A8CD}" name="総走行ｋｍ" dataDxfId="83"/>
+    <tableColumn id="11" xr3:uid="{D9733BFC-5F18-4B1B-B516-97F89C4F5A76}" name="運輸実績" dataDxfId="82"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{04114E94-5B99-4B60-A4C4-595383D7B980}" name="東日本セレモニー_1961" displayName="東日本セレモニー_1961" ref="A3:K6" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{04114E94-5B99-4B60-A4C4-595383D7B980}" name="東日本セレモニー_1961" displayName="東日本セレモニー_1961" ref="A3:K6" totalsRowShown="0" headerRowDxfId="81" dataDxfId="79" headerRowBorderDxfId="80" tableBorderDxfId="78">
   <autoFilter ref="A3:K6" xr:uid="{F9BAA250-893E-409E-AA21-0EAE21A25964}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4275,17 +4858,17 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="台数" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="支社名" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="車輌番号" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="延実在_x000a_車輌数" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="延実働_x000a_車輌数" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0F00-000006000000}" name="稼働率" dataDxfId="50" dataCellStyle="パーセント"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="搬送回数" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="有料キロ数" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0F00-000009000000}" name="無料キロ数" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0F00-00000A000000}" name="総走行ｋｍ" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0F00-00000B000000}" name="運輸実績" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="台数" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="支社名" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="車輌番号" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="延実在_x000a_車輌数" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="延実働_x000a_車輌数" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0F00-000006000000}" name="稼働率" dataDxfId="72" dataCellStyle="パーセント"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="搬送回数" dataDxfId="71"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="有料キロ数" dataDxfId="70"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0F00-000009000000}" name="無料キロ数" dataDxfId="69"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0F00-00000A000000}" name="総走行ｋｍ" dataDxfId="68"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0F00-00000B000000}" name="運輸実績" dataDxfId="67"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6714,6 +7297,1799 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD604FBE-B43C-4607-83D9-7F73B53C6100}">
+  <sheetPr>
+    <tabColor indexed="17"/>
+  </sheetPr>
+  <dimension ref="A1:L103"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="6.625" customWidth="1"/>
+    <col min="2" max="2" width="9.625" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="13.25" customWidth="1"/>
+    <col min="5" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="7" max="7" width="11.75" customWidth="1"/>
+    <col min="8" max="9" width="10.625" customWidth="1"/>
+    <col min="10" max="10" width="2.625" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10">
+        <f>'寝台車 29'!A1</f>
+        <v>0</v>
+      </c>
+      <c r="B1" s="11">
+        <f>'寝台車 29'!B1</f>
+        <v>0</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="49"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="60" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+    </row>
+    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="72" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="18">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="61"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="73"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="18">
+        <v>2</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="61"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="73"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="18">
+        <v>3</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="61"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="73"/>
+    </row>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="18">
+        <v>4</v>
+      </c>
+      <c r="B6" s="24"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="61"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="73"/>
+    </row>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="18">
+        <v>5</v>
+      </c>
+      <c r="B7" s="24"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="61"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="73"/>
+    </row>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="18">
+        <v>6</v>
+      </c>
+      <c r="B8" s="24"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="61"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="73"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="18">
+        <v>7</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="61"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="73"/>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="18">
+        <v>8</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="61"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="73"/>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="18">
+        <v>9</v>
+      </c>
+      <c r="B11" s="24"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="61"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="73"/>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="18">
+        <v>10</v>
+      </c>
+      <c r="B12" s="24"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="61"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="73"/>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="18">
+        <v>11</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="61"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="73"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="18">
+        <v>12</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="61"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="73"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="18">
+        <v>13</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="61"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="73"/>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="18">
+        <v>14</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="61"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="73"/>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="18">
+        <v>15</v>
+      </c>
+      <c r="B17" s="24"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="61"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="73"/>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="61"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="73"/>
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="18">
+        <v>17</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="61"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="73"/>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="18">
+        <v>18</v>
+      </c>
+      <c r="B20" s="24"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="61"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="73"/>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="18">
+        <v>19</v>
+      </c>
+      <c r="B21" s="24"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="61"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="73"/>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="18">
+        <v>20</v>
+      </c>
+      <c r="B22" s="24"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="61"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="73"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="18">
+        <v>21</v>
+      </c>
+      <c r="B23" s="24"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="61"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="73"/>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="18">
+        <v>22</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="61"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="73"/>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="18">
+        <v>23</v>
+      </c>
+      <c r="B25" s="24"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="61"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="73"/>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="18">
+        <v>24</v>
+      </c>
+      <c r="B26" s="24"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="61"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="73"/>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="18">
+        <v>25</v>
+      </c>
+      <c r="B27" s="24"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="61"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="73"/>
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="18">
+        <v>26</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="61"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="73"/>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="18">
+        <v>27</v>
+      </c>
+      <c r="B29" s="24"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="61"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="73"/>
+    </row>
+    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="18">
+        <v>28</v>
+      </c>
+      <c r="B30" s="24"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="61"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="73"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="18">
+        <v>29</v>
+      </c>
+      <c r="B31" s="24"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="61"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="73"/>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="18">
+        <v>30</v>
+      </c>
+      <c r="B32" s="24"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="61"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="73"/>
+    </row>
+    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="18">
+        <v>31</v>
+      </c>
+      <c r="B33" s="24"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="61"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="73"/>
+    </row>
+    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="18">
+        <v>32</v>
+      </c>
+      <c r="B34" s="24"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="61"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="73"/>
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="18">
+        <v>33</v>
+      </c>
+      <c r="B35" s="24"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="61"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="73"/>
+    </row>
+    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="18">
+        <v>34</v>
+      </c>
+      <c r="B36" s="24"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="61"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="73"/>
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="18">
+        <v>35</v>
+      </c>
+      <c r="B37" s="24"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="61"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="73"/>
+    </row>
+    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="18">
+        <v>36</v>
+      </c>
+      <c r="B38" s="24"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="61"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="73"/>
+    </row>
+    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="18">
+        <v>37</v>
+      </c>
+      <c r="B39" s="24"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="61"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="73"/>
+    </row>
+    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="18">
+        <v>38</v>
+      </c>
+      <c r="B40" s="24"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="61"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="73"/>
+    </row>
+    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="18">
+        <v>39</v>
+      </c>
+      <c r="B41" s="24"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="61"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="73"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="18">
+        <v>40</v>
+      </c>
+      <c r="B42" s="24"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="61"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="73"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="18">
+        <v>41</v>
+      </c>
+      <c r="B43" s="24"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="61"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="73"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="18">
+        <v>42</v>
+      </c>
+      <c r="B44" s="24"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="61"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="73"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="18">
+        <v>43</v>
+      </c>
+      <c r="B45" s="24"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="61"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="73"/>
+    </row>
+    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="18">
+        <v>44</v>
+      </c>
+      <c r="B46" s="24"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="61"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="73"/>
+    </row>
+    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="18">
+        <v>45</v>
+      </c>
+      <c r="B47" s="24"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="61"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="73"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="18">
+        <v>46</v>
+      </c>
+      <c r="B48" s="24"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="61"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="73"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="18">
+        <v>47</v>
+      </c>
+      <c r="B49" s="24"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="64"/>
+      <c r="I49" s="61"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="73"/>
+    </row>
+    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="18">
+        <v>48</v>
+      </c>
+      <c r="B50" s="24"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="64"/>
+      <c r="I50" s="61"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="73"/>
+    </row>
+    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="18">
+        <v>49</v>
+      </c>
+      <c r="B51" s="24"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="64"/>
+      <c r="I51" s="61"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="73"/>
+    </row>
+    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="18">
+        <v>50</v>
+      </c>
+      <c r="B52" s="24"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="48"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="64"/>
+      <c r="I52" s="61"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="73"/>
+    </row>
+    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="18">
+        <v>51</v>
+      </c>
+      <c r="B53" s="24"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="64"/>
+      <c r="I53" s="61"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="73"/>
+    </row>
+    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="18">
+        <v>52</v>
+      </c>
+      <c r="B54" s="24"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="48"/>
+      <c r="G54" s="48"/>
+      <c r="H54" s="64"/>
+      <c r="I54" s="61"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="73"/>
+    </row>
+    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="18">
+        <v>53</v>
+      </c>
+      <c r="B55" s="24"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="64"/>
+      <c r="I55" s="61"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="73"/>
+    </row>
+    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="18">
+        <v>54</v>
+      </c>
+      <c r="B56" s="24"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="64"/>
+      <c r="I56" s="61"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="73"/>
+    </row>
+    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="18">
+        <v>55</v>
+      </c>
+      <c r="B57" s="24"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="64"/>
+      <c r="I57" s="61"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="73"/>
+    </row>
+    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="18">
+        <v>56</v>
+      </c>
+      <c r="B58" s="24"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="64"/>
+      <c r="I58" s="61"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="73"/>
+    </row>
+    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="18">
+        <v>57</v>
+      </c>
+      <c r="B59" s="24"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="64"/>
+      <c r="I59" s="61"/>
+      <c r="K59" s="15"/>
+      <c r="L59" s="73"/>
+    </row>
+    <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="18">
+        <v>58</v>
+      </c>
+      <c r="B60" s="24"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="64"/>
+      <c r="I60" s="61"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="73"/>
+    </row>
+    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="18">
+        <v>59</v>
+      </c>
+      <c r="B61" s="24"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="64"/>
+      <c r="I61" s="61"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="73"/>
+    </row>
+    <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="18">
+        <v>60</v>
+      </c>
+      <c r="B62" s="24"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="64"/>
+      <c r="I62" s="61"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="73"/>
+    </row>
+    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="18">
+        <v>61</v>
+      </c>
+      <c r="B63" s="24"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="64"/>
+      <c r="I63" s="61"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="73"/>
+    </row>
+    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="18">
+        <v>62</v>
+      </c>
+      <c r="B64" s="24"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="48"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="64"/>
+      <c r="I64" s="61"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="73"/>
+    </row>
+    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="18">
+        <v>63</v>
+      </c>
+      <c r="B65" s="24"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="64"/>
+      <c r="I65" s="61"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="73"/>
+    </row>
+    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="18">
+        <v>64</v>
+      </c>
+      <c r="B66" s="24"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="64"/>
+      <c r="I66" s="61"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="73"/>
+    </row>
+    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="18">
+        <v>65</v>
+      </c>
+      <c r="B67" s="24"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="48"/>
+      <c r="G67" s="48"/>
+      <c r="H67" s="64"/>
+      <c r="I67" s="61"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="73"/>
+    </row>
+    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="18">
+        <v>66</v>
+      </c>
+      <c r="B68" s="24"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="64"/>
+      <c r="I68" s="61"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="73"/>
+    </row>
+    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="18">
+        <v>67</v>
+      </c>
+      <c r="B69" s="24"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="48"/>
+      <c r="G69" s="48"/>
+      <c r="H69" s="64"/>
+      <c r="I69" s="61"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="73"/>
+    </row>
+    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="18">
+        <v>68</v>
+      </c>
+      <c r="B70" s="24"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="64"/>
+      <c r="I70" s="61"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="73"/>
+    </row>
+    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="18">
+        <v>69</v>
+      </c>
+      <c r="B71" s="24"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="64"/>
+      <c r="I71" s="61"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="73"/>
+    </row>
+    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="18">
+        <v>70</v>
+      </c>
+      <c r="B72" s="24"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="64"/>
+      <c r="I72" s="61"/>
+      <c r="K72" s="15"/>
+      <c r="L72" s="73"/>
+    </row>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="18">
+        <v>71</v>
+      </c>
+      <c r="B73" s="24"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="48"/>
+      <c r="G73" s="48"/>
+      <c r="H73" s="64"/>
+      <c r="I73" s="61"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="73"/>
+    </row>
+    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="18">
+        <v>72</v>
+      </c>
+      <c r="B74" s="24"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="64"/>
+      <c r="I74" s="61"/>
+      <c r="K74" s="15"/>
+      <c r="L74" s="73"/>
+    </row>
+    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="18">
+        <v>73</v>
+      </c>
+      <c r="B75" s="24"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="64"/>
+      <c r="I75" s="61"/>
+      <c r="K75" s="15"/>
+      <c r="L75" s="73"/>
+    </row>
+    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="18">
+        <v>74</v>
+      </c>
+      <c r="B76" s="24"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="64"/>
+      <c r="I76" s="61"/>
+      <c r="K76" s="15"/>
+      <c r="L76" s="73"/>
+    </row>
+    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="18">
+        <v>75</v>
+      </c>
+      <c r="B77" s="24"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="48"/>
+      <c r="G77" s="48"/>
+      <c r="H77" s="64"/>
+      <c r="I77" s="61"/>
+      <c r="K77" s="15"/>
+      <c r="L77" s="73"/>
+    </row>
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="18">
+        <v>76</v>
+      </c>
+      <c r="B78" s="24"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="64"/>
+      <c r="I78" s="61"/>
+      <c r="K78" s="15"/>
+      <c r="L78" s="73"/>
+    </row>
+    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="18">
+        <v>77</v>
+      </c>
+      <c r="B79" s="24"/>
+      <c r="C79" s="19"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="64"/>
+      <c r="I79" s="61"/>
+      <c r="K79" s="15"/>
+      <c r="L79" s="73"/>
+    </row>
+    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="18">
+        <v>78</v>
+      </c>
+      <c r="B80" s="24"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="48"/>
+      <c r="G80" s="48"/>
+      <c r="H80" s="64"/>
+      <c r="I80" s="61"/>
+      <c r="K80" s="15"/>
+      <c r="L80" s="73"/>
+    </row>
+    <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="18">
+        <v>79</v>
+      </c>
+      <c r="B81" s="24"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="48"/>
+      <c r="G81" s="48"/>
+      <c r="H81" s="64"/>
+      <c r="I81" s="61"/>
+      <c r="K81" s="15"/>
+      <c r="L81" s="73"/>
+    </row>
+    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="18">
+        <v>80</v>
+      </c>
+      <c r="B82" s="24"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="48"/>
+      <c r="G82" s="48"/>
+      <c r="H82" s="64"/>
+      <c r="I82" s="61"/>
+      <c r="K82" s="15"/>
+      <c r="L82" s="73"/>
+    </row>
+    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="18">
+        <v>81</v>
+      </c>
+      <c r="B83" s="24"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="48"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="64"/>
+      <c r="I83" s="61"/>
+      <c r="K83" s="15"/>
+      <c r="L83" s="73"/>
+    </row>
+    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="18">
+        <v>82</v>
+      </c>
+      <c r="B84" s="24"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="21"/>
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="64"/>
+      <c r="I84" s="61"/>
+      <c r="K84" s="15"/>
+      <c r="L84" s="73"/>
+    </row>
+    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="18">
+        <v>83</v>
+      </c>
+      <c r="B85" s="24"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="48"/>
+      <c r="G85" s="48"/>
+      <c r="H85" s="64"/>
+      <c r="I85" s="61"/>
+      <c r="K85" s="15"/>
+      <c r="L85" s="73"/>
+    </row>
+    <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="18">
+        <v>84</v>
+      </c>
+      <c r="B86" s="24"/>
+      <c r="C86" s="19"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="64"/>
+      <c r="I86" s="61"/>
+      <c r="K86" s="15"/>
+      <c r="L86" s="73"/>
+    </row>
+    <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="18">
+        <v>85</v>
+      </c>
+      <c r="B87" s="24"/>
+      <c r="C87" s="19"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="64"/>
+      <c r="I87" s="61"/>
+      <c r="K87" s="15"/>
+      <c r="L87" s="73"/>
+    </row>
+    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="18">
+        <v>86</v>
+      </c>
+      <c r="B88" s="24"/>
+      <c r="C88" s="19"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="21"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="64"/>
+      <c r="I88" s="61"/>
+      <c r="K88" s="15"/>
+      <c r="L88" s="73"/>
+    </row>
+    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="18">
+        <v>87</v>
+      </c>
+      <c r="B89" s="24"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="21"/>
+      <c r="F89" s="48"/>
+      <c r="G89" s="48"/>
+      <c r="H89" s="64"/>
+      <c r="I89" s="61"/>
+      <c r="K89" s="15"/>
+      <c r="L89" s="73"/>
+    </row>
+    <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="18">
+        <v>88</v>
+      </c>
+      <c r="B90" s="24"/>
+      <c r="C90" s="19"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="21"/>
+      <c r="F90" s="48"/>
+      <c r="G90" s="48"/>
+      <c r="H90" s="64"/>
+      <c r="I90" s="61"/>
+      <c r="K90" s="15"/>
+      <c r="L90" s="73"/>
+    </row>
+    <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="18">
+        <v>89</v>
+      </c>
+      <c r="B91" s="24"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="21"/>
+      <c r="F91" s="48"/>
+      <c r="G91" s="48"/>
+      <c r="H91" s="64"/>
+      <c r="I91" s="61"/>
+      <c r="K91" s="15"/>
+      <c r="L91" s="73"/>
+    </row>
+    <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="18">
+        <v>90</v>
+      </c>
+      <c r="B92" s="24"/>
+      <c r="C92" s="19"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="21"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="48"/>
+      <c r="H92" s="64"/>
+      <c r="I92" s="61"/>
+      <c r="K92" s="15"/>
+      <c r="L92" s="73"/>
+    </row>
+    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="18">
+        <v>91</v>
+      </c>
+      <c r="B93" s="24"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="21"/>
+      <c r="E93" s="21"/>
+      <c r="F93" s="48"/>
+      <c r="G93" s="48"/>
+      <c r="H93" s="64"/>
+      <c r="I93" s="61"/>
+      <c r="K93" s="15"/>
+      <c r="L93" s="73"/>
+    </row>
+    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="18">
+        <v>92</v>
+      </c>
+      <c r="B94" s="24"/>
+      <c r="C94" s="19"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="21"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="48"/>
+      <c r="H94" s="64"/>
+      <c r="I94" s="61"/>
+      <c r="K94" s="15"/>
+      <c r="L94" s="73"/>
+    </row>
+    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="18">
+        <v>93</v>
+      </c>
+      <c r="B95" s="24"/>
+      <c r="C95" s="19"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="21"/>
+      <c r="F95" s="48"/>
+      <c r="G95" s="48"/>
+      <c r="H95" s="64"/>
+      <c r="I95" s="61"/>
+      <c r="K95" s="15"/>
+      <c r="L95" s="73"/>
+    </row>
+    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="18">
+        <v>94</v>
+      </c>
+      <c r="B96" s="24"/>
+      <c r="C96" s="19"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="21"/>
+      <c r="F96" s="48"/>
+      <c r="G96" s="48"/>
+      <c r="H96" s="64"/>
+      <c r="I96" s="61"/>
+      <c r="K96" s="15"/>
+      <c r="L96" s="73"/>
+    </row>
+    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="18">
+        <v>95</v>
+      </c>
+      <c r="B97" s="24"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="48"/>
+      <c r="G97" s="48"/>
+      <c r="H97" s="64"/>
+      <c r="I97" s="61"/>
+      <c r="K97" s="15"/>
+      <c r="L97" s="73"/>
+    </row>
+    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="18">
+        <v>96</v>
+      </c>
+      <c r="B98" s="24"/>
+      <c r="C98" s="19"/>
+      <c r="D98" s="21"/>
+      <c r="E98" s="21"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="64"/>
+      <c r="I98" s="61"/>
+      <c r="K98" s="15"/>
+      <c r="L98" s="73"/>
+    </row>
+    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="18">
+        <v>97</v>
+      </c>
+      <c r="B99" s="24"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="64"/>
+      <c r="I99" s="61"/>
+      <c r="K99" s="15"/>
+      <c r="L99" s="73"/>
+    </row>
+    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="18">
+        <v>98</v>
+      </c>
+      <c r="B100" s="24"/>
+      <c r="C100" s="19"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="21"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="64"/>
+      <c r="I100" s="61"/>
+      <c r="K100" s="15"/>
+      <c r="L100" s="73"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A101" s="18">
+        <v>99</v>
+      </c>
+      <c r="B101" s="24"/>
+      <c r="C101" s="19"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="64"/>
+      <c r="I101" s="61"/>
+      <c r="K101" s="15"/>
+      <c r="L101" s="73"/>
+    </row>
+    <row r="102" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="18">
+        <v>100</v>
+      </c>
+      <c r="B102" s="25"/>
+      <c r="C102" s="20"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="56"/>
+      <c r="G102" s="56"/>
+      <c r="H102" s="65"/>
+      <c r="I102" s="62"/>
+      <c r="K102" s="16"/>
+      <c r="L102" s="74"/>
+    </row>
+    <row r="103" spans="1:12" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B103" s="52">
+        <f>COUNT(B3:B102)</f>
+        <v>0</v>
+      </c>
+      <c r="C103" s="53">
+        <f t="shared" ref="C103:I103" si="0">SUM(C3:C102)</f>
+        <v>0</v>
+      </c>
+      <c r="D103" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E103" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G103" s="57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H103" s="57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I103" s="57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K103" s="17"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="98" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1AE8740-45F6-4258-931D-5CA8AA479EAD}">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="7.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="37">
+        <f>'寝台車 29'!A1</f>
+        <v>0</v>
+      </c>
+      <c r="B1" s="35">
+        <f>'寝台車 29'!B1</f>
+        <v>0</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="C2" s="5"/>
+      <c r="G2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:11" ht="34.5" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="2" t="e">
+        <f>DAY(EOMONTH(DATE(VALUE(MID(A1,2,LEN(A1)-1))+2018,B1,1),0))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="7" t="e">
+        <f>E4/D4</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8">
+        <f>SUM(H4:I4)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="27"/>
+    </row>
+    <row r="5" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="38"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="42"/>
+    </row>
+    <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="34"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29" t="e">
+        <f>SUM(D4:D5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E6" s="29">
+        <f>SUM(E4:E5)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="30" t="e">
+        <f>E6/D6</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G6" s="29">
+        <f>SUM(G4:G5)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="29">
+        <f>SUM(H4:H5)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="29">
+        <f>SUM(I4:I5)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="31">
+        <f>SUM(J4:J5)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="32">
+        <f>SUM(K4:K5)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FD7BD33-688A-4C6B-B490-1A9EF67405C0}">
   <sheetPr>

--- a/HansoInputTool/data/Input.xlsx
+++ b/HansoInputTool/data/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ligdoor\source\repos\HansoInputTool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A397ED-C3A8-4BA3-8097-04545DC86DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5ED478-685F-4E33-8774-9E13A84F8911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="892" activeTab="12" xr2:uid="{88C334D1-54A2-4A07-AD58-9761E3E044DD}"/>
+    <workbookView xWindow="1095" yWindow="2310" windowWidth="22185" windowHeight="15690" tabRatio="892" firstSheet="6" activeTab="13" xr2:uid="{88C334D1-54A2-4A07-AD58-9761E3E044DD}"/>
   </bookViews>
   <sheets>
     <sheet name="寝台車 29" sheetId="32" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="33">
   <si>
     <t>走行キロ(ｋｍ)</t>
     <rPh sb="0" eb="2">
@@ -219,16 +219,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ＣH東日本</t>
-  </si>
-  <si>
-    <t>ＣH東日本</t>
-    <rPh sb="2" eb="5">
-      <t>ヒガシニホン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>延実在
 車輌数</t>
     <rPh sb="0" eb="1">
@@ -298,6 +288,17 @@
   </si>
   <si>
     <t>行旅死亡人</t>
+  </si>
+  <si>
+    <t>東日本</t>
+    <rPh sb="0" eb="3">
+      <t>ヒガシニホン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>東日本</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -5187,12 +5188,12 @@
         <v>15</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
       <c r="G1" s="60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H1" s="10">
         <v>29</v>
@@ -5218,10 +5219,10 @@
         <v>13</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>17</v>
@@ -5230,10 +5231,10 @@
         <v>18</v>
       </c>
       <c r="K2" s="69" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -6840,10 +6841,10 @@
         <v>3</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>4</v>
@@ -6869,7 +6870,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3">
         <v>2259</v>
@@ -7011,10 +7012,10 @@
         <v>3</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>4</v>
@@ -7040,7 +7041,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3">
         <v>2262</v>
@@ -7182,10 +7183,10 @@
         <v>3</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>4</v>
@@ -7211,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3">
         <v>2380</v>
@@ -7333,7 +7334,7 @@
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
       <c r="G1" s="60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -7357,10 +7358,10 @@
         <v>13</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>17</v>
@@ -7369,10 +7370,10 @@
         <v>18</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -8979,10 +8980,10 @@
         <v>3</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>4</v>
@@ -9007,7 +9008,9 @@
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="C4" s="3"/>
       <c r="D4" s="2" t="e">
         <f>DAY(EOMONTH(DATE(VALUE(MID(A1,2,LEN(A1)-1))+2018,B1,1),0))</f>
@@ -9123,12 +9126,12 @@
         <v>15</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
       <c r="G1" s="60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H1" s="10">
         <v>30</v>
@@ -9154,10 +9157,10 @@
         <v>13</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>17</v>
@@ -9166,10 +9169,10 @@
         <v>18</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -10753,12 +10756,12 @@
         <v>15</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
       <c r="G1" s="60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H1" s="10">
         <v>1603</v>
@@ -10784,10 +10787,10 @@
         <v>13</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>17</v>
@@ -10796,10 +10799,10 @@
         <v>18</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -12389,12 +12392,12 @@
         <v>15</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
       <c r="G1" s="60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H1" s="10">
         <v>1105</v>
@@ -12420,10 +12423,10 @@
         <v>13</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>17</v>
@@ -12432,10 +12435,10 @@
         <v>18</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -14019,12 +14022,12 @@
         <v>15</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
       <c r="G1" s="60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H1" s="10">
         <v>1381</v>
@@ -14050,10 +14053,10 @@
         <v>13</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>17</v>
@@ -14062,10 +14065,10 @@
         <v>18</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -15649,12 +15652,12 @@
         <v>15</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
       <c r="G1" s="60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H1" s="10">
         <v>40</v>
@@ -15680,10 +15683,10 @@
         <v>13</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>17</v>
@@ -15692,10 +15695,10 @@
         <v>18</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -17279,12 +17282,12 @@
         <v>15</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
       <c r="G1" s="60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H1" s="10">
         <v>223</v>
@@ -17310,10 +17313,10 @@
         <v>13</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>17</v>
@@ -17322,10 +17325,10 @@
         <v>18</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -18932,10 +18935,10 @@
         <v>3</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>4</v>
@@ -18961,7 +18964,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3">
         <v>1961</v>
@@ -19103,10 +19106,10 @@
         <v>3</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>4</v>
@@ -19132,7 +19135,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3">
         <v>1961</v>

--- a/HansoInputTool/data/Input.xlsx
+++ b/HansoInputTool/data/Input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ligdoor\source\repos\HansoInputTool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60218BA-922C-43BD-8248-738939F36E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4544B224-232C-41E0-BFF3-79B958306AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1545" yWindow="1740" windowWidth="27495" windowHeight="18585" tabRatio="892" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="675" yWindow="1650" windowWidth="27495" windowHeight="18585" tabRatio="892" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CH富士吉田 寝台車 29" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="30">
   <si>
     <t>月分</t>
   </si>
@@ -134,9 +134,6 @@
     <t>深夜時間（分）</t>
   </si>
   <si>
-    <t>行旅死亡人</t>
-  </si>
-  <si>
     <t>CH富士吉田 霊柩車</t>
   </si>
   <si>
@@ -150,10 +147,6 @@
   </si>
   <si>
     <t>霊柩車</t>
-  </si>
-  <si>
-    <t>エンバー</t>
-    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -172,7 +165,7 @@
     <numFmt numFmtId="183" formatCode="&quot;有料　&quot;#0&quot;ｋｍ&quot;"/>
     <numFmt numFmtId="184" formatCode="&quot;無料　&quot;#0&quot;ｋｍ&quot;"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -229,6 +222,13 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -244,7 +244,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -714,45 +714,18 @@
       <left style="mediumDashDotDot">
         <color theme="1"/>
       </left>
-      <right style="mediumDashDotDot">
-        <color theme="1"/>
-      </right>
-      <top style="mediumDashDotDot">
-        <color theme="1"/>
-      </top>
-      <bottom style="dashed">
-        <color theme="1"/>
-      </bottom>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="mediumDashDotDot">
+      <left style="mediumDashed">
         <color theme="1"/>
       </left>
-      <right style="mediumDashDotDot">
-        <color theme="1"/>
-      </right>
-      <top style="dashed">
-        <color theme="1"/>
-      </top>
-      <bottom style="dashed">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="mediumDashDotDot">
-        <color theme="1"/>
-      </left>
-      <right style="mediumDashDotDot">
-        <color theme="1"/>
-      </right>
-      <top style="dashed">
-        <color theme="1"/>
-      </top>
-      <bottom style="mediumDashDotDot">
-        <color theme="1"/>
-      </bottom>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -770,7 +743,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -987,17 +960,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2620,6 +2602,388 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <numFmt numFmtId="10" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <numFmt numFmtId="6" formatCode="#,##0;[Red]\-#,##0"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <numFmt numFmtId="6" formatCode="#,##0;[Red]\-#,##0"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <numFmt numFmtId="6" formatCode="#,##0;[Red]\-#,##0"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="0.0%"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color auto="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="right" vertical="center"/>
     </dxf>
     <dxf>
@@ -3283,388 +3647,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <numFmt numFmtId="10" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <numFmt numFmtId="6" formatCode="#,##0;[Red]\-#,##0"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <numFmt numFmtId="6" formatCode="#,##0;[Red]\-#,##0"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <numFmt numFmtId="6" formatCode="#,##0;[Red]\-#,##0"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="0.0%"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color auto="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3679,7 +3661,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="搬送車_29" displayName="搬送車_29" ref="A2:I103" totalsRowShown="0" headerRowDxfId="122" headerRowBorderDxfId="121" tableBorderDxfId="120">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="搬送車_29" displayName="搬送車_29" ref="A2:I103" totalsRowShown="0" headerRowDxfId="137" headerRowBorderDxfId="136" tableBorderDxfId="135">
   <autoFilter ref="A2:I103" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3697,10 +3679,10 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="基本料" dataDxfId="119"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="走行料" dataDxfId="118"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="割増料" dataDxfId="117"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="合計" dataDxfId="116"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="基本料" dataDxfId="134"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="走行料" dataDxfId="133"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="割増料" dataDxfId="132"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="合計" dataDxfId="131"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3863,7 +3845,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="搬送車_295" displayName="搬送車_295" ref="A2:I103" totalsRowShown="0" headerRowDxfId="115" headerRowBorderDxfId="114" tableBorderDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="搬送車_295" displayName="搬送車_295" ref="A2:I103" totalsRowShown="0" headerRowDxfId="130" headerRowBorderDxfId="129" tableBorderDxfId="128">
   <autoFilter ref="A2:I103" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3881,17 +3863,17 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="基本料" dataDxfId="112"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="走行料" dataDxfId="111"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="割増料" dataDxfId="110"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="合計" dataDxfId="109"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="基本料" dataDxfId="127"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="走行料" dataDxfId="126"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="割増料" dataDxfId="125"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="合計" dataDxfId="124"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="搬送車_295781011" displayName="搬送車_295781011" ref="A2:I103" totalsRowShown="0" headerRowDxfId="108" headerRowBorderDxfId="107" tableBorderDxfId="106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="搬送車_295781011" displayName="搬送車_295781011" ref="A2:I103" totalsRowShown="0" headerRowDxfId="123" headerRowBorderDxfId="122" tableBorderDxfId="121">
   <autoFilter ref="A2:I103" xr:uid="{00000000-0009-0000-0100-000003000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3909,17 +3891,17 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="基本料" dataDxfId="105"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="走行料" dataDxfId="104"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="割増料" dataDxfId="103"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="合計" dataDxfId="102"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="基本料" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="走行料" dataDxfId="119"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="割増料" dataDxfId="118"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="合計" dataDxfId="117"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="搬送車_29578101116" displayName="搬送車_29578101116" ref="A2:I103" totalsRowShown="0" headerRowDxfId="101" headerRowBorderDxfId="100" tableBorderDxfId="99">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="搬送車_29578101116" displayName="搬送車_29578101116" ref="A2:I103" totalsRowShown="0" headerRowDxfId="116" headerRowBorderDxfId="115" tableBorderDxfId="114">
   <autoFilter ref="A2:I103" xr:uid="{00000000-0009-0000-0100-000004000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3937,17 +3919,17 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="基本料" dataDxfId="98"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="走行料" dataDxfId="97"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="割増料" dataDxfId="96"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="合計" dataDxfId="95"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="基本料" dataDxfId="113"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="走行料" dataDxfId="112"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="割増料" dataDxfId="111"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="合計" dataDxfId="110"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="搬送車_2957" displayName="搬送車_2957" ref="A2:I104" totalsRowShown="0" headerRowDxfId="94" headerRowBorderDxfId="93" tableBorderDxfId="92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="搬送車_2957" displayName="搬送車_2957" ref="A2:I104" totalsRowShown="0" headerRowDxfId="109" headerRowBorderDxfId="108" tableBorderDxfId="107">
   <autoFilter ref="A2:I104" xr:uid="{00000000-0009-0000-0100-000005000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3965,17 +3947,17 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="基本料" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="走行料" dataDxfId="90"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="割増料" dataDxfId="89"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="合計" dataDxfId="88"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="基本料" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="走行料" dataDxfId="105"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="割増料" dataDxfId="104"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="合計" dataDxfId="103"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="CH大月_霊柩車_2577" displayName="CH大月_霊柩車_2577" ref="A2:I103" totalsRowShown="0" headerRowDxfId="87" headerRowBorderDxfId="86" tableBorderDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="CH大月_霊柩車_2577" displayName="CH大月_霊柩車_2577" ref="A2:I103" totalsRowShown="0" headerRowDxfId="102" headerRowBorderDxfId="101" tableBorderDxfId="100">
   <autoFilter ref="A2:I103" xr:uid="{00000000-0009-0000-0100-000006000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3993,17 +3975,17 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="基本料" dataDxfId="84"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="走行料" dataDxfId="83"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="割増料" dataDxfId="82"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="合計" dataDxfId="81"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="基本料" dataDxfId="99"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="走行料" dataDxfId="98"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="割増料" dataDxfId="97"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="合計" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="搬送車_29578" displayName="搬送車_29578" ref="A2:I103" totalsRowShown="0" headerRowDxfId="80" headerRowBorderDxfId="79" tableBorderDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="搬送車_29578" displayName="搬送車_29578" ref="A2:I103" totalsRowShown="0" headerRowDxfId="95" headerRowBorderDxfId="94" tableBorderDxfId="93">
   <autoFilter ref="A2:I103" xr:uid="{00000000-0009-0000-0100-000007000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4021,17 +4003,17 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="基本料" dataDxfId="77"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="走行料" dataDxfId="76"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="割増料" dataDxfId="75"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="合計" dataDxfId="74"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="基本料" dataDxfId="92"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="走行料" dataDxfId="91"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="割増料" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="合計" dataDxfId="89"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="搬送車_2957810" displayName="搬送車_2957810" ref="A2:I103" totalsRowShown="0" headerRowDxfId="73" headerRowBorderDxfId="72" tableBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="搬送車_2957810" displayName="搬送車_2957810" ref="A2:I103" totalsRowShown="0" headerRowDxfId="88" headerRowBorderDxfId="87" tableBorderDxfId="86">
   <autoFilter ref="A2:I103" xr:uid="{00000000-0009-0000-0100-000008000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4049,17 +4031,17 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="搬送数"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="有料キロ数"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="無料キロ数"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="基本料" dataDxfId="70"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="走行料" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="割増料" dataDxfId="68"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="合計" dataDxfId="67"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="基本料" dataDxfId="85"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="走行料" dataDxfId="84"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="割増料" dataDxfId="83"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="合計" dataDxfId="82"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="東日本セレモニー_1961" displayName="東日本セレモニー_1961" ref="A3:K6" totalsRowShown="0" headerRowDxfId="137" dataDxfId="135" headerRowBorderDxfId="136" tableBorderDxfId="134">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="東日本セレモニー_1961" displayName="東日本セレモニー_1961" ref="A3:K6" totalsRowShown="0" headerRowDxfId="81" dataDxfId="79" headerRowBorderDxfId="80" tableBorderDxfId="78">
   <autoFilter ref="A3:K6" xr:uid="{00000000-0009-0000-0100-000009000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4074,17 +4056,17 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="台数" dataDxfId="133"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="支社名" dataDxfId="132"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="車輌番号" dataDxfId="131"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="延実在_x000a_車輌数" dataDxfId="130"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="延実働_x000a_車輌数" dataDxfId="129"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="稼働率" dataDxfId="128" dataCellStyle="パーセント"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="搬送回数" dataDxfId="127"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="有料キロ数" dataDxfId="126"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="無料キロ数" dataDxfId="125"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="総走行ｋｍ" dataDxfId="124"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="運輸実績" dataDxfId="123"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="台数" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="支社名" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="車輌番号" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="延実在_x000a_車輌数" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="延実働_x000a_車輌数" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="稼働率" dataDxfId="72" dataCellStyle="パーセント"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="搬送回数" dataDxfId="71"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="有料キロ数" dataDxfId="70"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="無料キロ数" dataDxfId="69"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="総走行ｋｍ" dataDxfId="68"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="運輸実績" dataDxfId="67"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4383,17 +4365,17 @@
   <dimension ref="A1:M103"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="75" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="75" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="75" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="75" customWidth="1"/>
-    <col min="8" max="9" width="10.625" style="75" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="75" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="75" customWidth="1"/>
-    <col min="12" max="12" width="9" style="75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="72" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="72" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="72" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="72" customWidth="1"/>
+    <col min="8" max="9" width="10.625" style="72" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="72" customWidth="1"/>
+    <col min="12" max="12" width="9" style="72" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4453,12 +4435,8 @@
       <c r="K2" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="72" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="76" t="s">
-        <v>31</v>
-      </c>
+      <c r="L2" s="73"/>
+      <c r="M2" s="74"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="18">
@@ -4473,8 +4451,8 @@
       <c r="H3" s="63"/>
       <c r="I3" s="61"/>
       <c r="K3" s="70"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="76"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18">
@@ -4489,8 +4467,8 @@
       <c r="H4" s="64"/>
       <c r="I4" s="61"/>
       <c r="K4" s="70"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="76"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18">
@@ -4505,8 +4483,8 @@
       <c r="H5" s="64"/>
       <c r="I5" s="61"/>
       <c r="K5" s="70"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="76"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18">
@@ -4521,8 +4499,8 @@
       <c r="H6" s="64"/>
       <c r="I6" s="61"/>
       <c r="K6" s="70"/>
-      <c r="L6" s="73"/>
-      <c r="M6" s="73"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="76"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18">
@@ -4537,8 +4515,8 @@
       <c r="H7" s="64"/>
       <c r="I7" s="61"/>
       <c r="K7" s="70"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="73"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18">
@@ -4553,8 +4531,8 @@
       <c r="H8" s="64"/>
       <c r="I8" s="61"/>
       <c r="K8" s="70"/>
-      <c r="L8" s="73"/>
-      <c r="M8" s="73"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18">
@@ -4569,8 +4547,8 @@
       <c r="H9" s="64"/>
       <c r="I9" s="61"/>
       <c r="K9" s="70"/>
-      <c r="L9" s="73"/>
-      <c r="M9" s="73"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18">
@@ -4585,8 +4563,8 @@
       <c r="H10" s="64"/>
       <c r="I10" s="61"/>
       <c r="K10" s="70"/>
-      <c r="L10" s="73"/>
-      <c r="M10" s="73"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="76"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18">
@@ -4601,8 +4579,8 @@
       <c r="H11" s="64"/>
       <c r="I11" s="61"/>
       <c r="K11" s="70"/>
-      <c r="L11" s="73"/>
-      <c r="M11" s="73"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="76"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18">
@@ -4617,8 +4595,8 @@
       <c r="H12" s="64"/>
       <c r="I12" s="61"/>
       <c r="K12" s="70"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="73"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="18">
@@ -4633,8 +4611,8 @@
       <c r="H13" s="64"/>
       <c r="I13" s="61"/>
       <c r="K13" s="70"/>
-      <c r="L13" s="73"/>
-      <c r="M13" s="73"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18">
@@ -4649,8 +4627,8 @@
       <c r="H14" s="64"/>
       <c r="I14" s="61"/>
       <c r="K14" s="70"/>
-      <c r="L14" s="73"/>
-      <c r="M14" s="73"/>
+      <c r="L14" s="75"/>
+      <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18">
@@ -4665,8 +4643,8 @@
       <c r="H15" s="64"/>
       <c r="I15" s="61"/>
       <c r="K15" s="70"/>
-      <c r="L15" s="73"/>
-      <c r="M15" s="73"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="76"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18">
@@ -4681,8 +4659,8 @@
       <c r="H16" s="64"/>
       <c r="I16" s="61"/>
       <c r="K16" s="70"/>
-      <c r="L16" s="73"/>
-      <c r="M16" s="73"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="76"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18">
@@ -4697,8 +4675,8 @@
       <c r="H17" s="64"/>
       <c r="I17" s="61"/>
       <c r="K17" s="70"/>
-      <c r="L17" s="73"/>
-      <c r="M17" s="73"/>
+      <c r="L17" s="75"/>
+      <c r="M17" s="76"/>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18">
@@ -4713,8 +4691,8 @@
       <c r="H18" s="64"/>
       <c r="I18" s="61"/>
       <c r="K18" s="70"/>
-      <c r="L18" s="73"/>
-      <c r="M18" s="73"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18">
@@ -4729,8 +4707,8 @@
       <c r="H19" s="64"/>
       <c r="I19" s="61"/>
       <c r="K19" s="70"/>
-      <c r="L19" s="73"/>
-      <c r="M19" s="73"/>
+      <c r="L19" s="75"/>
+      <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18">
@@ -4745,8 +4723,8 @@
       <c r="H20" s="64"/>
       <c r="I20" s="61"/>
       <c r="K20" s="70"/>
-      <c r="L20" s="73"/>
-      <c r="M20" s="73"/>
+      <c r="L20" s="75"/>
+      <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18">
@@ -4761,8 +4739,8 @@
       <c r="H21" s="64"/>
       <c r="I21" s="61"/>
       <c r="K21" s="70"/>
-      <c r="L21" s="73"/>
-      <c r="M21" s="73"/>
+      <c r="L21" s="75"/>
+      <c r="M21" s="76"/>
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18">
@@ -4777,8 +4755,8 @@
       <c r="H22" s="64"/>
       <c r="I22" s="61"/>
       <c r="K22" s="70"/>
-      <c r="L22" s="73"/>
-      <c r="M22" s="73"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="76"/>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18">
@@ -4793,8 +4771,8 @@
       <c r="H23" s="64"/>
       <c r="I23" s="61"/>
       <c r="K23" s="70"/>
-      <c r="L23" s="73"/>
-      <c r="M23" s="73"/>
+      <c r="L23" s="75"/>
+      <c r="M23" s="76"/>
     </row>
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18">
@@ -4809,8 +4787,8 @@
       <c r="H24" s="64"/>
       <c r="I24" s="61"/>
       <c r="K24" s="70"/>
-      <c r="L24" s="73"/>
-      <c r="M24" s="73"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="76"/>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18">
@@ -4825,8 +4803,8 @@
       <c r="H25" s="64"/>
       <c r="I25" s="61"/>
       <c r="K25" s="70"/>
-      <c r="L25" s="73"/>
-      <c r="M25" s="73"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18">
@@ -4841,8 +4819,8 @@
       <c r="H26" s="64"/>
       <c r="I26" s="61"/>
       <c r="K26" s="70"/>
-      <c r="L26" s="73"/>
-      <c r="M26" s="73"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="18">
@@ -4857,8 +4835,8 @@
       <c r="H27" s="64"/>
       <c r="I27" s="61"/>
       <c r="K27" s="70"/>
-      <c r="L27" s="73"/>
-      <c r="M27" s="73"/>
+      <c r="L27" s="75"/>
+      <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18">
@@ -4873,8 +4851,8 @@
       <c r="H28" s="64"/>
       <c r="I28" s="61"/>
       <c r="K28" s="70"/>
-      <c r="L28" s="73"/>
-      <c r="M28" s="73"/>
+      <c r="L28" s="75"/>
+      <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18">
@@ -4889,8 +4867,8 @@
       <c r="H29" s="64"/>
       <c r="I29" s="61"/>
       <c r="K29" s="70"/>
-      <c r="L29" s="73"/>
-      <c r="M29" s="73"/>
+      <c r="L29" s="75"/>
+      <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18">
@@ -4905,8 +4883,8 @@
       <c r="H30" s="64"/>
       <c r="I30" s="61"/>
       <c r="K30" s="70"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
+      <c r="L30" s="75"/>
+      <c r="M30" s="76"/>
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18">
@@ -4921,8 +4899,8 @@
       <c r="H31" s="64"/>
       <c r="I31" s="61"/>
       <c r="K31" s="70"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="73"/>
+      <c r="L31" s="75"/>
+      <c r="M31" s="76"/>
     </row>
     <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18">
@@ -4937,8 +4915,8 @@
       <c r="H32" s="64"/>
       <c r="I32" s="61"/>
       <c r="K32" s="70"/>
-      <c r="L32" s="73"/>
-      <c r="M32" s="73"/>
+      <c r="L32" s="75"/>
+      <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18">
@@ -4953,8 +4931,8 @@
       <c r="H33" s="64"/>
       <c r="I33" s="61"/>
       <c r="K33" s="70"/>
-      <c r="L33" s="73"/>
-      <c r="M33" s="73"/>
+      <c r="L33" s="75"/>
+      <c r="M33" s="76"/>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18">
@@ -4969,8 +4947,8 @@
       <c r="H34" s="64"/>
       <c r="I34" s="61"/>
       <c r="K34" s="70"/>
-      <c r="L34" s="73"/>
-      <c r="M34" s="73"/>
+      <c r="L34" s="75"/>
+      <c r="M34" s="76"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18">
@@ -4985,8 +4963,8 @@
       <c r="H35" s="64"/>
       <c r="I35" s="61"/>
       <c r="K35" s="70"/>
-      <c r="L35" s="73"/>
-      <c r="M35" s="73"/>
+      <c r="L35" s="75"/>
+      <c r="M35" s="76"/>
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18">
@@ -5001,8 +4979,8 @@
       <c r="H36" s="64"/>
       <c r="I36" s="61"/>
       <c r="K36" s="70"/>
-      <c r="L36" s="73"/>
-      <c r="M36" s="73"/>
+      <c r="L36" s="75"/>
+      <c r="M36" s="76"/>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18">
@@ -5017,8 +4995,8 @@
       <c r="H37" s="64"/>
       <c r="I37" s="61"/>
       <c r="K37" s="70"/>
-      <c r="L37" s="73"/>
-      <c r="M37" s="73"/>
+      <c r="L37" s="75"/>
+      <c r="M37" s="76"/>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18">
@@ -5033,8 +5011,8 @@
       <c r="H38" s="64"/>
       <c r="I38" s="61"/>
       <c r="K38" s="70"/>
-      <c r="L38" s="73"/>
-      <c r="M38" s="73"/>
+      <c r="L38" s="75"/>
+      <c r="M38" s="76"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18">
@@ -5049,8 +5027,8 @@
       <c r="H39" s="64"/>
       <c r="I39" s="61"/>
       <c r="K39" s="70"/>
-      <c r="L39" s="73"/>
-      <c r="M39" s="73"/>
+      <c r="L39" s="75"/>
+      <c r="M39" s="76"/>
     </row>
     <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18">
@@ -5065,8 +5043,8 @@
       <c r="H40" s="64"/>
       <c r="I40" s="61"/>
       <c r="K40" s="70"/>
-      <c r="L40" s="73"/>
-      <c r="M40" s="73"/>
+      <c r="L40" s="75"/>
+      <c r="M40" s="76"/>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18">
@@ -5081,8 +5059,8 @@
       <c r="H41" s="64"/>
       <c r="I41" s="61"/>
       <c r="K41" s="70"/>
-      <c r="L41" s="73"/>
-      <c r="M41" s="73"/>
+      <c r="L41" s="75"/>
+      <c r="M41" s="76"/>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18">
@@ -5097,8 +5075,8 @@
       <c r="H42" s="64"/>
       <c r="I42" s="61"/>
       <c r="K42" s="70"/>
-      <c r="L42" s="73"/>
-      <c r="M42" s="73"/>
+      <c r="L42" s="75"/>
+      <c r="M42" s="76"/>
     </row>
     <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18">
@@ -5113,8 +5091,8 @@
       <c r="H43" s="64"/>
       <c r="I43" s="61"/>
       <c r="K43" s="70"/>
-      <c r="L43" s="73"/>
-      <c r="M43" s="73"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="76"/>
     </row>
     <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18">
@@ -5129,8 +5107,8 @@
       <c r="H44" s="64"/>
       <c r="I44" s="61"/>
       <c r="K44" s="70"/>
-      <c r="L44" s="73"/>
-      <c r="M44" s="73"/>
+      <c r="L44" s="75"/>
+      <c r="M44" s="76"/>
     </row>
     <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18">
@@ -5145,8 +5123,8 @@
       <c r="H45" s="64"/>
       <c r="I45" s="61"/>
       <c r="K45" s="70"/>
-      <c r="L45" s="73"/>
-      <c r="M45" s="73"/>
+      <c r="L45" s="75"/>
+      <c r="M45" s="76"/>
     </row>
     <row r="46" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18">
@@ -5161,8 +5139,8 @@
       <c r="H46" s="64"/>
       <c r="I46" s="61"/>
       <c r="K46" s="70"/>
-      <c r="L46" s="73"/>
-      <c r="M46" s="73"/>
+      <c r="L46" s="75"/>
+      <c r="M46" s="76"/>
     </row>
     <row r="47" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18">
@@ -5177,8 +5155,8 @@
       <c r="H47" s="64"/>
       <c r="I47" s="61"/>
       <c r="K47" s="70"/>
-      <c r="L47" s="73"/>
-      <c r="M47" s="73"/>
+      <c r="L47" s="75"/>
+      <c r="M47" s="76"/>
     </row>
     <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18">
@@ -5193,8 +5171,8 @@
       <c r="H48" s="64"/>
       <c r="I48" s="61"/>
       <c r="K48" s="70"/>
-      <c r="L48" s="73"/>
-      <c r="M48" s="73"/>
+      <c r="L48" s="75"/>
+      <c r="M48" s="76"/>
     </row>
     <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18">
@@ -5209,8 +5187,8 @@
       <c r="H49" s="64"/>
       <c r="I49" s="61"/>
       <c r="K49" s="70"/>
-      <c r="L49" s="73"/>
-      <c r="M49" s="73"/>
+      <c r="L49" s="75"/>
+      <c r="M49" s="76"/>
     </row>
     <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18">
@@ -5225,8 +5203,8 @@
       <c r="H50" s="64"/>
       <c r="I50" s="61"/>
       <c r="K50" s="70"/>
-      <c r="L50" s="73"/>
-      <c r="M50" s="73"/>
+      <c r="L50" s="75"/>
+      <c r="M50" s="76"/>
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18">
@@ -5241,8 +5219,8 @@
       <c r="H51" s="64"/>
       <c r="I51" s="61"/>
       <c r="K51" s="70"/>
-      <c r="L51" s="73"/>
-      <c r="M51" s="73"/>
+      <c r="L51" s="75"/>
+      <c r="M51" s="76"/>
     </row>
     <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18">
@@ -5257,8 +5235,8 @@
       <c r="H52" s="64"/>
       <c r="I52" s="61"/>
       <c r="K52" s="70"/>
-      <c r="L52" s="73"/>
-      <c r="M52" s="73"/>
+      <c r="L52" s="75"/>
+      <c r="M52" s="76"/>
     </row>
     <row r="53" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="18">
@@ -5273,8 +5251,8 @@
       <c r="H53" s="64"/>
       <c r="I53" s="61"/>
       <c r="K53" s="70"/>
-      <c r="L53" s="73"/>
-      <c r="M53" s="73"/>
+      <c r="L53" s="75"/>
+      <c r="M53" s="76"/>
     </row>
     <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18">
@@ -5289,8 +5267,8 @@
       <c r="H54" s="64"/>
       <c r="I54" s="61"/>
       <c r="K54" s="70"/>
-      <c r="L54" s="73"/>
-      <c r="M54" s="73"/>
+      <c r="L54" s="75"/>
+      <c r="M54" s="76"/>
     </row>
     <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18">
@@ -5305,8 +5283,8 @@
       <c r="H55" s="64"/>
       <c r="I55" s="61"/>
       <c r="K55" s="70"/>
-      <c r="L55" s="73"/>
-      <c r="M55" s="73"/>
+      <c r="L55" s="75"/>
+      <c r="M55" s="76"/>
     </row>
     <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18">
@@ -5321,8 +5299,8 @@
       <c r="H56" s="64"/>
       <c r="I56" s="61"/>
       <c r="K56" s="70"/>
-      <c r="L56" s="73"/>
-      <c r="M56" s="73"/>
+      <c r="L56" s="75"/>
+      <c r="M56" s="76"/>
     </row>
     <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18">
@@ -5337,8 +5315,8 @@
       <c r="H57" s="64"/>
       <c r="I57" s="61"/>
       <c r="K57" s="70"/>
-      <c r="L57" s="73"/>
-      <c r="M57" s="73"/>
+      <c r="L57" s="75"/>
+      <c r="M57" s="76"/>
     </row>
     <row r="58" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18">
@@ -5353,8 +5331,8 @@
       <c r="H58" s="64"/>
       <c r="I58" s="61"/>
       <c r="K58" s="70"/>
-      <c r="L58" s="73"/>
-      <c r="M58" s="73"/>
+      <c r="L58" s="75"/>
+      <c r="M58" s="76"/>
     </row>
     <row r="59" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18">
@@ -5369,8 +5347,8 @@
       <c r="H59" s="64"/>
       <c r="I59" s="61"/>
       <c r="K59" s="70"/>
-      <c r="L59" s="73"/>
-      <c r="M59" s="73"/>
+      <c r="L59" s="75"/>
+      <c r="M59" s="76"/>
     </row>
     <row r="60" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18">
@@ -5385,8 +5363,8 @@
       <c r="H60" s="64"/>
       <c r="I60" s="61"/>
       <c r="K60" s="70"/>
-      <c r="L60" s="73"/>
-      <c r="M60" s="73"/>
+      <c r="L60" s="75"/>
+      <c r="M60" s="76"/>
     </row>
     <row r="61" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18">
@@ -5401,8 +5379,8 @@
       <c r="H61" s="64"/>
       <c r="I61" s="61"/>
       <c r="K61" s="70"/>
-      <c r="L61" s="73"/>
-      <c r="M61" s="73"/>
+      <c r="L61" s="75"/>
+      <c r="M61" s="76"/>
     </row>
     <row r="62" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="18">
@@ -5417,8 +5395,8 @@
       <c r="H62" s="64"/>
       <c r="I62" s="61"/>
       <c r="K62" s="70"/>
-      <c r="L62" s="73"/>
-      <c r="M62" s="73"/>
+      <c r="L62" s="75"/>
+      <c r="M62" s="76"/>
     </row>
     <row r="63" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18">
@@ -5433,8 +5411,8 @@
       <c r="H63" s="64"/>
       <c r="I63" s="61"/>
       <c r="K63" s="70"/>
-      <c r="L63" s="73"/>
-      <c r="M63" s="73"/>
+      <c r="L63" s="75"/>
+      <c r="M63" s="76"/>
     </row>
     <row r="64" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18">
@@ -5449,8 +5427,8 @@
       <c r="H64" s="64"/>
       <c r="I64" s="61"/>
       <c r="K64" s="70"/>
-      <c r="L64" s="73"/>
-      <c r="M64" s="73"/>
+      <c r="L64" s="75"/>
+      <c r="M64" s="76"/>
     </row>
     <row r="65" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18">
@@ -5465,8 +5443,8 @@
       <c r="H65" s="64"/>
       <c r="I65" s="61"/>
       <c r="K65" s="70"/>
-      <c r="L65" s="73"/>
-      <c r="M65" s="73"/>
+      <c r="L65" s="75"/>
+      <c r="M65" s="76"/>
     </row>
     <row r="66" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18">
@@ -5481,8 +5459,8 @@
       <c r="H66" s="64"/>
       <c r="I66" s="61"/>
       <c r="K66" s="70"/>
-      <c r="L66" s="73"/>
-      <c r="M66" s="73"/>
+      <c r="L66" s="75"/>
+      <c r="M66" s="76"/>
     </row>
     <row r="67" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18">
@@ -5497,8 +5475,8 @@
       <c r="H67" s="64"/>
       <c r="I67" s="61"/>
       <c r="K67" s="70"/>
-      <c r="L67" s="73"/>
-      <c r="M67" s="73"/>
+      <c r="L67" s="75"/>
+      <c r="M67" s="76"/>
     </row>
     <row r="68" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18">
@@ -5513,8 +5491,8 @@
       <c r="H68" s="64"/>
       <c r="I68" s="61"/>
       <c r="K68" s="70"/>
-      <c r="L68" s="73"/>
-      <c r="M68" s="73"/>
+      <c r="L68" s="75"/>
+      <c r="M68" s="76"/>
     </row>
     <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18">
@@ -5529,8 +5507,8 @@
       <c r="H69" s="64"/>
       <c r="I69" s="61"/>
       <c r="K69" s="70"/>
-      <c r="L69" s="73"/>
-      <c r="M69" s="73"/>
+      <c r="L69" s="75"/>
+      <c r="M69" s="76"/>
     </row>
     <row r="70" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18">
@@ -5545,8 +5523,8 @@
       <c r="H70" s="64"/>
       <c r="I70" s="61"/>
       <c r="K70" s="70"/>
-      <c r="L70" s="73"/>
-      <c r="M70" s="73"/>
+      <c r="L70" s="75"/>
+      <c r="M70" s="76"/>
     </row>
     <row r="71" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18">
@@ -5561,8 +5539,8 @@
       <c r="H71" s="64"/>
       <c r="I71" s="61"/>
       <c r="K71" s="70"/>
-      <c r="L71" s="73"/>
-      <c r="M71" s="73"/>
+      <c r="L71" s="75"/>
+      <c r="M71" s="76"/>
     </row>
     <row r="72" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18">
@@ -5577,8 +5555,8 @@
       <c r="H72" s="64"/>
       <c r="I72" s="61"/>
       <c r="K72" s="70"/>
-      <c r="L72" s="73"/>
-      <c r="M72" s="73"/>
+      <c r="L72" s="75"/>
+      <c r="M72" s="76"/>
     </row>
     <row r="73" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18">
@@ -5593,8 +5571,8 @@
       <c r="H73" s="64"/>
       <c r="I73" s="61"/>
       <c r="K73" s="70"/>
-      <c r="L73" s="73"/>
-      <c r="M73" s="73"/>
+      <c r="L73" s="75"/>
+      <c r="M73" s="76"/>
     </row>
     <row r="74" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18">
@@ -5609,8 +5587,8 @@
       <c r="H74" s="64"/>
       <c r="I74" s="61"/>
       <c r="K74" s="70"/>
-      <c r="L74" s="73"/>
-      <c r="M74" s="73"/>
+      <c r="L74" s="75"/>
+      <c r="M74" s="76"/>
     </row>
     <row r="75" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18">
@@ -5625,8 +5603,8 @@
       <c r="H75" s="64"/>
       <c r="I75" s="61"/>
       <c r="K75" s="70"/>
-      <c r="L75" s="73"/>
-      <c r="M75" s="73"/>
+      <c r="L75" s="75"/>
+      <c r="M75" s="76"/>
     </row>
     <row r="76" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="18">
@@ -5641,8 +5619,8 @@
       <c r="H76" s="64"/>
       <c r="I76" s="61"/>
       <c r="K76" s="70"/>
-      <c r="L76" s="73"/>
-      <c r="M76" s="73"/>
+      <c r="L76" s="75"/>
+      <c r="M76" s="76"/>
     </row>
     <row r="77" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18">
@@ -5657,8 +5635,8 @@
       <c r="H77" s="64"/>
       <c r="I77" s="61"/>
       <c r="K77" s="70"/>
-      <c r="L77" s="73"/>
-      <c r="M77" s="73"/>
+      <c r="L77" s="75"/>
+      <c r="M77" s="76"/>
     </row>
     <row r="78" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18">
@@ -5673,8 +5651,8 @@
       <c r="H78" s="64"/>
       <c r="I78" s="61"/>
       <c r="K78" s="70"/>
-      <c r="L78" s="73"/>
-      <c r="M78" s="73"/>
+      <c r="L78" s="75"/>
+      <c r="M78" s="76"/>
     </row>
     <row r="79" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18">
@@ -5689,8 +5667,8 @@
       <c r="H79" s="64"/>
       <c r="I79" s="61"/>
       <c r="K79" s="70"/>
-      <c r="L79" s="73"/>
-      <c r="M79" s="73"/>
+      <c r="L79" s="75"/>
+      <c r="M79" s="76"/>
     </row>
     <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18">
@@ -5705,8 +5683,8 @@
       <c r="H80" s="64"/>
       <c r="I80" s="61"/>
       <c r="K80" s="70"/>
-      <c r="L80" s="73"/>
-      <c r="M80" s="73"/>
+      <c r="L80" s="75"/>
+      <c r="M80" s="76"/>
     </row>
     <row r="81" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18">
@@ -5721,8 +5699,8 @@
       <c r="H81" s="64"/>
       <c r="I81" s="61"/>
       <c r="K81" s="70"/>
-      <c r="L81" s="73"/>
-      <c r="M81" s="73"/>
+      <c r="L81" s="75"/>
+      <c r="M81" s="76"/>
     </row>
     <row r="82" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18">
@@ -5737,8 +5715,8 @@
       <c r="H82" s="64"/>
       <c r="I82" s="61"/>
       <c r="K82" s="70"/>
-      <c r="L82" s="73"/>
-      <c r="M82" s="73"/>
+      <c r="L82" s="75"/>
+      <c r="M82" s="76"/>
     </row>
     <row r="83" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18">
@@ -5753,8 +5731,8 @@
       <c r="H83" s="64"/>
       <c r="I83" s="61"/>
       <c r="K83" s="70"/>
-      <c r="L83" s="73"/>
-      <c r="M83" s="73"/>
+      <c r="L83" s="75"/>
+      <c r="M83" s="76"/>
     </row>
     <row r="84" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18">
@@ -5769,8 +5747,8 @@
       <c r="H84" s="64"/>
       <c r="I84" s="61"/>
       <c r="K84" s="70"/>
-      <c r="L84" s="73"/>
-      <c r="M84" s="73"/>
+      <c r="L84" s="75"/>
+      <c r="M84" s="76"/>
     </row>
     <row r="85" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18">
@@ -5785,8 +5763,8 @@
       <c r="H85" s="64"/>
       <c r="I85" s="61"/>
       <c r="K85" s="70"/>
-      <c r="L85" s="73"/>
-      <c r="M85" s="73"/>
+      <c r="L85" s="75"/>
+      <c r="M85" s="76"/>
     </row>
     <row r="86" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18">
@@ -5801,8 +5779,8 @@
       <c r="H86" s="64"/>
       <c r="I86" s="61"/>
       <c r="K86" s="70"/>
-      <c r="L86" s="73"/>
-      <c r="M86" s="73"/>
+      <c r="L86" s="75"/>
+      <c r="M86" s="76"/>
     </row>
     <row r="87" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18">
@@ -5817,8 +5795,8 @@
       <c r="H87" s="64"/>
       <c r="I87" s="61"/>
       <c r="K87" s="70"/>
-      <c r="L87" s="73"/>
-      <c r="M87" s="73"/>
+      <c r="L87" s="75"/>
+      <c r="M87" s="76"/>
     </row>
     <row r="88" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18">
@@ -5833,8 +5811,8 @@
       <c r="H88" s="64"/>
       <c r="I88" s="61"/>
       <c r="K88" s="70"/>
-      <c r="L88" s="73"/>
-      <c r="M88" s="73"/>
+      <c r="L88" s="75"/>
+      <c r="M88" s="76"/>
     </row>
     <row r="89" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="18">
@@ -5849,8 +5827,8 @@
       <c r="H89" s="64"/>
       <c r="I89" s="61"/>
       <c r="K89" s="70"/>
-      <c r="L89" s="73"/>
-      <c r="M89" s="73"/>
+      <c r="L89" s="75"/>
+      <c r="M89" s="76"/>
     </row>
     <row r="90" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18">
@@ -5865,8 +5843,8 @@
       <c r="H90" s="64"/>
       <c r="I90" s="61"/>
       <c r="K90" s="70"/>
-      <c r="L90" s="73"/>
-      <c r="M90" s="73"/>
+      <c r="L90" s="75"/>
+      <c r="M90" s="76"/>
     </row>
     <row r="91" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18">
@@ -5881,8 +5859,8 @@
       <c r="H91" s="64"/>
       <c r="I91" s="61"/>
       <c r="K91" s="70"/>
-      <c r="L91" s="73"/>
-      <c r="M91" s="73"/>
+      <c r="L91" s="75"/>
+      <c r="M91" s="76"/>
     </row>
     <row r="92" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18">
@@ -5897,8 +5875,8 @@
       <c r="H92" s="64"/>
       <c r="I92" s="61"/>
       <c r="K92" s="70"/>
-      <c r="L92" s="73"/>
-      <c r="M92" s="73"/>
+      <c r="L92" s="75"/>
+      <c r="M92" s="76"/>
     </row>
     <row r="93" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18">
@@ -5913,8 +5891,8 @@
       <c r="H93" s="64"/>
       <c r="I93" s="61"/>
       <c r="K93" s="70"/>
-      <c r="L93" s="73"/>
-      <c r="M93" s="73"/>
+      <c r="L93" s="75"/>
+      <c r="M93" s="76"/>
     </row>
     <row r="94" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18">
@@ -5929,8 +5907,8 @@
       <c r="H94" s="64"/>
       <c r="I94" s="61"/>
       <c r="K94" s="70"/>
-      <c r="L94" s="73"/>
-      <c r="M94" s="73"/>
+      <c r="L94" s="75"/>
+      <c r="M94" s="76"/>
     </row>
     <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18">
@@ -5945,8 +5923,8 @@
       <c r="H95" s="64"/>
       <c r="I95" s="61"/>
       <c r="K95" s="70"/>
-      <c r="L95" s="73"/>
-      <c r="M95" s="73"/>
+      <c r="L95" s="75"/>
+      <c r="M95" s="76"/>
     </row>
     <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18">
@@ -5961,8 +5939,8 @@
       <c r="H96" s="64"/>
       <c r="I96" s="61"/>
       <c r="K96" s="70"/>
-      <c r="L96" s="73"/>
-      <c r="M96" s="73"/>
+      <c r="L96" s="75"/>
+      <c r="M96" s="76"/>
     </row>
     <row r="97" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="18">
@@ -5977,8 +5955,8 @@
       <c r="H97" s="64"/>
       <c r="I97" s="61"/>
       <c r="K97" s="70"/>
-      <c r="L97" s="73"/>
-      <c r="M97" s="73"/>
+      <c r="L97" s="75"/>
+      <c r="M97" s="76"/>
     </row>
     <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="18">
@@ -5993,8 +5971,8 @@
       <c r="H98" s="64"/>
       <c r="I98" s="61"/>
       <c r="K98" s="70"/>
-      <c r="L98" s="73"/>
-      <c r="M98" s="73"/>
+      <c r="L98" s="75"/>
+      <c r="M98" s="76"/>
     </row>
     <row r="99" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="18">
@@ -6009,8 +5987,8 @@
       <c r="H99" s="64"/>
       <c r="I99" s="61"/>
       <c r="K99" s="70"/>
-      <c r="L99" s="73"/>
-      <c r="M99" s="73"/>
+      <c r="L99" s="75"/>
+      <c r="M99" s="76"/>
     </row>
     <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="18">
@@ -6025,8 +6003,8 @@
       <c r="H100" s="64"/>
       <c r="I100" s="61"/>
       <c r="K100" s="70"/>
-      <c r="L100" s="73"/>
-      <c r="M100" s="73"/>
+      <c r="L100" s="75"/>
+      <c r="M100" s="76"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A101" s="18">
@@ -6041,8 +6019,8 @@
       <c r="H101" s="64"/>
       <c r="I101" s="61"/>
       <c r="K101" s="70"/>
-      <c r="L101" s="73"/>
-      <c r="M101" s="73"/>
+      <c r="L101" s="75"/>
+      <c r="M101" s="76"/>
     </row>
     <row r="102" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A102" s="18">
@@ -6057,8 +6035,8 @@
       <c r="H102" s="65"/>
       <c r="I102" s="62"/>
       <c r="K102" s="71"/>
-      <c r="L102" s="74"/>
-      <c r="M102" s="74"/>
+      <c r="L102" s="75"/>
+      <c r="M102" s="76"/>
     </row>
     <row r="103" spans="1:13" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A103" s="51" t="s">
@@ -6629,16 +6607,16 @@
   <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="75" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="75" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="75" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="75" customWidth="1"/>
-    <col min="8" max="9" width="10.625" style="75" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="75" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="75" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="72" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="72" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="72" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="72" customWidth="1"/>
+    <col min="8" max="9" width="10.625" style="72" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6695,9 +6673,7 @@
       <c r="K2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="72" t="s">
-        <v>25</v>
-      </c>
+      <c r="L2" s="79"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="18">
@@ -6712,7 +6688,7 @@
       <c r="H3" s="63"/>
       <c r="I3" s="61"/>
       <c r="K3" s="15"/>
-      <c r="L3" s="73"/>
+      <c r="L3" s="78"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18">
@@ -6727,7 +6703,7 @@
       <c r="H4" s="64"/>
       <c r="I4" s="61"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="73"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18">
@@ -6742,7 +6718,7 @@
       <c r="H5" s="64"/>
       <c r="I5" s="61"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="73"/>
+      <c r="L5" s="78"/>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18">
@@ -6757,7 +6733,7 @@
       <c r="H6" s="64"/>
       <c r="I6" s="61"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="73"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18">
@@ -6772,7 +6748,7 @@
       <c r="H7" s="64"/>
       <c r="I7" s="61"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="73"/>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18">
@@ -6787,7 +6763,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="61"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="73"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18">
@@ -6802,7 +6778,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="61"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="73"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18">
@@ -6817,7 +6793,7 @@
       <c r="H10" s="64"/>
       <c r="I10" s="61"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="73"/>
+      <c r="L10" s="78"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18">
@@ -6832,7 +6808,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="61"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="73"/>
+      <c r="L11" s="78"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18">
@@ -6847,7 +6823,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="61"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="73"/>
+      <c r="L12" s="78"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="18">
@@ -6862,7 +6838,7 @@
       <c r="H13" s="64"/>
       <c r="I13" s="61"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="73"/>
+      <c r="L13" s="78"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18">
@@ -6877,7 +6853,7 @@
       <c r="H14" s="64"/>
       <c r="I14" s="61"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="73"/>
+      <c r="L14" s="78"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18">
@@ -6892,7 +6868,7 @@
       <c r="H15" s="64"/>
       <c r="I15" s="61"/>
       <c r="K15" s="15"/>
-      <c r="L15" s="73"/>
+      <c r="L15" s="78"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18">
@@ -6907,7 +6883,7 @@
       <c r="H16" s="64"/>
       <c r="I16" s="61"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="73"/>
+      <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18">
@@ -6922,7 +6898,7 @@
       <c r="H17" s="64"/>
       <c r="I17" s="61"/>
       <c r="K17" s="15"/>
-      <c r="L17" s="73"/>
+      <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18">
@@ -6937,7 +6913,7 @@
       <c r="H18" s="64"/>
       <c r="I18" s="61"/>
       <c r="K18" s="15"/>
-      <c r="L18" s="73"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18">
@@ -6952,7 +6928,7 @@
       <c r="H19" s="64"/>
       <c r="I19" s="61"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="73"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18">
@@ -6967,7 +6943,7 @@
       <c r="H20" s="64"/>
       <c r="I20" s="61"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="73"/>
+      <c r="L20" s="78"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18">
@@ -6982,7 +6958,7 @@
       <c r="H21" s="64"/>
       <c r="I21" s="61"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="73"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18">
@@ -6997,7 +6973,7 @@
       <c r="H22" s="64"/>
       <c r="I22" s="61"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="73"/>
+      <c r="L22" s="78"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18">
@@ -7012,7 +6988,7 @@
       <c r="H23" s="64"/>
       <c r="I23" s="61"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="73"/>
+      <c r="L23" s="78"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18">
@@ -7027,7 +7003,7 @@
       <c r="H24" s="64"/>
       <c r="I24" s="61"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="73"/>
+      <c r="L24" s="78"/>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18">
@@ -7042,7 +7018,7 @@
       <c r="H25" s="64"/>
       <c r="I25" s="61"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="73"/>
+      <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18">
@@ -7057,7 +7033,7 @@
       <c r="H26" s="64"/>
       <c r="I26" s="61"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="73"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="18">
@@ -7072,7 +7048,7 @@
       <c r="H27" s="64"/>
       <c r="I27" s="61"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="73"/>
+      <c r="L27" s="78"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18">
@@ -7087,7 +7063,7 @@
       <c r="H28" s="64"/>
       <c r="I28" s="61"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="73"/>
+      <c r="L28" s="78"/>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18">
@@ -7102,7 +7078,7 @@
       <c r="H29" s="64"/>
       <c r="I29" s="61"/>
       <c r="K29" s="15"/>
-      <c r="L29" s="73"/>
+      <c r="L29" s="78"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18">
@@ -7117,7 +7093,7 @@
       <c r="H30" s="64"/>
       <c r="I30" s="61"/>
       <c r="K30" s="15"/>
-      <c r="L30" s="73"/>
+      <c r="L30" s="78"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18">
@@ -7132,7 +7108,7 @@
       <c r="H31" s="64"/>
       <c r="I31" s="61"/>
       <c r="K31" s="15"/>
-      <c r="L31" s="73"/>
+      <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18">
@@ -7147,7 +7123,7 @@
       <c r="H32" s="64"/>
       <c r="I32" s="61"/>
       <c r="K32" s="15"/>
-      <c r="L32" s="73"/>
+      <c r="L32" s="78"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18">
@@ -7162,7 +7138,7 @@
       <c r="H33" s="64"/>
       <c r="I33" s="61"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="73"/>
+      <c r="L33" s="78"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18">
@@ -7177,7 +7153,7 @@
       <c r="H34" s="64"/>
       <c r="I34" s="61"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="73"/>
+      <c r="L34" s="78"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18">
@@ -7192,7 +7168,7 @@
       <c r="H35" s="64"/>
       <c r="I35" s="61"/>
       <c r="K35" s="15"/>
-      <c r="L35" s="73"/>
+      <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18">
@@ -7207,7 +7183,7 @@
       <c r="H36" s="64"/>
       <c r="I36" s="61"/>
       <c r="K36" s="15"/>
-      <c r="L36" s="73"/>
+      <c r="L36" s="78"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18">
@@ -7222,7 +7198,7 @@
       <c r="H37" s="64"/>
       <c r="I37" s="61"/>
       <c r="K37" s="15"/>
-      <c r="L37" s="73"/>
+      <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18">
@@ -7237,7 +7213,7 @@
       <c r="H38" s="64"/>
       <c r="I38" s="61"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="78"/>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18">
@@ -7252,7 +7228,7 @@
       <c r="H39" s="64"/>
       <c r="I39" s="61"/>
       <c r="K39" s="15"/>
-      <c r="L39" s="73"/>
+      <c r="L39" s="78"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18">
@@ -7267,7 +7243,7 @@
       <c r="H40" s="64"/>
       <c r="I40" s="61"/>
       <c r="K40" s="15"/>
-      <c r="L40" s="73"/>
+      <c r="L40" s="78"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18">
@@ -7282,7 +7258,7 @@
       <c r="H41" s="64"/>
       <c r="I41" s="61"/>
       <c r="K41" s="15"/>
-      <c r="L41" s="73"/>
+      <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18">
@@ -7297,7 +7273,7 @@
       <c r="H42" s="64"/>
       <c r="I42" s="61"/>
       <c r="K42" s="15"/>
-      <c r="L42" s="73"/>
+      <c r="L42" s="78"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18">
@@ -7312,7 +7288,7 @@
       <c r="H43" s="64"/>
       <c r="I43" s="61"/>
       <c r="K43" s="15"/>
-      <c r="L43" s="73"/>
+      <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18">
@@ -7327,7 +7303,7 @@
       <c r="H44" s="64"/>
       <c r="I44" s="61"/>
       <c r="K44" s="15"/>
-      <c r="L44" s="73"/>
+      <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18">
@@ -7342,7 +7318,7 @@
       <c r="H45" s="64"/>
       <c r="I45" s="61"/>
       <c r="K45" s="15"/>
-      <c r="L45" s="73"/>
+      <c r="L45" s="78"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18">
@@ -7357,7 +7333,7 @@
       <c r="H46" s="64"/>
       <c r="I46" s="61"/>
       <c r="K46" s="15"/>
-      <c r="L46" s="73"/>
+      <c r="L46" s="78"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18">
@@ -7372,7 +7348,7 @@
       <c r="H47" s="64"/>
       <c r="I47" s="61"/>
       <c r="K47" s="15"/>
-      <c r="L47" s="73"/>
+      <c r="L47" s="78"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18">
@@ -7387,7 +7363,7 @@
       <c r="H48" s="64"/>
       <c r="I48" s="61"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="73"/>
+      <c r="L48" s="78"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18">
@@ -7402,7 +7378,7 @@
       <c r="H49" s="64"/>
       <c r="I49" s="61"/>
       <c r="K49" s="15"/>
-      <c r="L49" s="73"/>
+      <c r="L49" s="78"/>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18">
@@ -7417,7 +7393,7 @@
       <c r="H50" s="64"/>
       <c r="I50" s="61"/>
       <c r="K50" s="15"/>
-      <c r="L50" s="73"/>
+      <c r="L50" s="78"/>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18">
@@ -7432,7 +7408,7 @@
       <c r="H51" s="64"/>
       <c r="I51" s="61"/>
       <c r="K51" s="15"/>
-      <c r="L51" s="73"/>
+      <c r="L51" s="78"/>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18">
@@ -7447,7 +7423,7 @@
       <c r="H52" s="64"/>
       <c r="I52" s="61"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="73"/>
+      <c r="L52" s="78"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="18">
@@ -7462,7 +7438,7 @@
       <c r="H53" s="64"/>
       <c r="I53" s="61"/>
       <c r="K53" s="15"/>
-      <c r="L53" s="73"/>
+      <c r="L53" s="78"/>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18">
@@ -7477,7 +7453,7 @@
       <c r="H54" s="64"/>
       <c r="I54" s="61"/>
       <c r="K54" s="15"/>
-      <c r="L54" s="73"/>
+      <c r="L54" s="78"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18">
@@ -7492,7 +7468,7 @@
       <c r="H55" s="64"/>
       <c r="I55" s="61"/>
       <c r="K55" s="15"/>
-      <c r="L55" s="73"/>
+      <c r="L55" s="78"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18">
@@ -7507,7 +7483,7 @@
       <c r="H56" s="64"/>
       <c r="I56" s="61"/>
       <c r="K56" s="15"/>
-      <c r="L56" s="73"/>
+      <c r="L56" s="78"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18">
@@ -7522,7 +7498,7 @@
       <c r="H57" s="64"/>
       <c r="I57" s="61"/>
       <c r="K57" s="15"/>
-      <c r="L57" s="73"/>
+      <c r="L57" s="78"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18">
@@ -7537,7 +7513,7 @@
       <c r="H58" s="64"/>
       <c r="I58" s="61"/>
       <c r="K58" s="15"/>
-      <c r="L58" s="73"/>
+      <c r="L58" s="78"/>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18">
@@ -7552,7 +7528,7 @@
       <c r="H59" s="64"/>
       <c r="I59" s="61"/>
       <c r="K59" s="15"/>
-      <c r="L59" s="73"/>
+      <c r="L59" s="78"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18">
@@ -7567,7 +7543,7 @@
       <c r="H60" s="64"/>
       <c r="I60" s="61"/>
       <c r="K60" s="15"/>
-      <c r="L60" s="73"/>
+      <c r="L60" s="78"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18">
@@ -7582,7 +7558,7 @@
       <c r="H61" s="64"/>
       <c r="I61" s="61"/>
       <c r="K61" s="15"/>
-      <c r="L61" s="73"/>
+      <c r="L61" s="78"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="18">
@@ -7597,7 +7573,7 @@
       <c r="H62" s="64"/>
       <c r="I62" s="61"/>
       <c r="K62" s="15"/>
-      <c r="L62" s="73"/>
+      <c r="L62" s="78"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18">
@@ -7612,7 +7588,7 @@
       <c r="H63" s="64"/>
       <c r="I63" s="61"/>
       <c r="K63" s="15"/>
-      <c r="L63" s="73"/>
+      <c r="L63" s="78"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18">
@@ -7627,7 +7603,7 @@
       <c r="H64" s="64"/>
       <c r="I64" s="61"/>
       <c r="K64" s="15"/>
-      <c r="L64" s="73"/>
+      <c r="L64" s="78"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18">
@@ -7642,7 +7618,7 @@
       <c r="H65" s="64"/>
       <c r="I65" s="61"/>
       <c r="K65" s="15"/>
-      <c r="L65" s="73"/>
+      <c r="L65" s="78"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18">
@@ -7657,7 +7633,7 @@
       <c r="H66" s="64"/>
       <c r="I66" s="61"/>
       <c r="K66" s="15"/>
-      <c r="L66" s="73"/>
+      <c r="L66" s="78"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18">
@@ -7672,7 +7648,7 @@
       <c r="H67" s="64"/>
       <c r="I67" s="61"/>
       <c r="K67" s="15"/>
-      <c r="L67" s="73"/>
+      <c r="L67" s="78"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18">
@@ -7687,7 +7663,7 @@
       <c r="H68" s="64"/>
       <c r="I68" s="61"/>
       <c r="K68" s="15"/>
-      <c r="L68" s="73"/>
+      <c r="L68" s="78"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18">
@@ -7702,7 +7678,7 @@
       <c r="H69" s="64"/>
       <c r="I69" s="61"/>
       <c r="K69" s="15"/>
-      <c r="L69" s="73"/>
+      <c r="L69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18">
@@ -7717,7 +7693,7 @@
       <c r="H70" s="64"/>
       <c r="I70" s="61"/>
       <c r="K70" s="15"/>
-      <c r="L70" s="73"/>
+      <c r="L70" s="78"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18">
@@ -7732,7 +7708,7 @@
       <c r="H71" s="64"/>
       <c r="I71" s="61"/>
       <c r="K71" s="15"/>
-      <c r="L71" s="73"/>
+      <c r="L71" s="78"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18">
@@ -7747,7 +7723,7 @@
       <c r="H72" s="64"/>
       <c r="I72" s="61"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="73"/>
+      <c r="L72" s="78"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18">
@@ -7762,7 +7738,7 @@
       <c r="H73" s="64"/>
       <c r="I73" s="61"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="73"/>
+      <c r="L73" s="78"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18">
@@ -7777,7 +7753,7 @@
       <c r="H74" s="64"/>
       <c r="I74" s="61"/>
       <c r="K74" s="15"/>
-      <c r="L74" s="73"/>
+      <c r="L74" s="78"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18">
@@ -7792,7 +7768,7 @@
       <c r="H75" s="64"/>
       <c r="I75" s="61"/>
       <c r="K75" s="15"/>
-      <c r="L75" s="73"/>
+      <c r="L75" s="78"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="18">
@@ -7807,7 +7783,7 @@
       <c r="H76" s="64"/>
       <c r="I76" s="61"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="73"/>
+      <c r="L76" s="78"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18">
@@ -7822,7 +7798,7 @@
       <c r="H77" s="64"/>
       <c r="I77" s="61"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="73"/>
+      <c r="L77" s="78"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18">
@@ -7837,7 +7813,7 @@
       <c r="H78" s="64"/>
       <c r="I78" s="61"/>
       <c r="K78" s="15"/>
-      <c r="L78" s="73"/>
+      <c r="L78" s="78"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18">
@@ -7852,7 +7828,7 @@
       <c r="H79" s="64"/>
       <c r="I79" s="61"/>
       <c r="K79" s="15"/>
-      <c r="L79" s="73"/>
+      <c r="L79" s="78"/>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18">
@@ -7867,7 +7843,7 @@
       <c r="H80" s="64"/>
       <c r="I80" s="61"/>
       <c r="K80" s="15"/>
-      <c r="L80" s="73"/>
+      <c r="L80" s="78"/>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18">
@@ -7882,7 +7858,7 @@
       <c r="H81" s="64"/>
       <c r="I81" s="61"/>
       <c r="K81" s="15"/>
-      <c r="L81" s="73"/>
+      <c r="L81" s="78"/>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18">
@@ -7897,7 +7873,7 @@
       <c r="H82" s="64"/>
       <c r="I82" s="61"/>
       <c r="K82" s="15"/>
-      <c r="L82" s="73"/>
+      <c r="L82" s="78"/>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18">
@@ -7912,7 +7888,7 @@
       <c r="H83" s="64"/>
       <c r="I83" s="61"/>
       <c r="K83" s="15"/>
-      <c r="L83" s="73"/>
+      <c r="L83" s="78"/>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18">
@@ -7927,7 +7903,7 @@
       <c r="H84" s="64"/>
       <c r="I84" s="61"/>
       <c r="K84" s="15"/>
-      <c r="L84" s="73"/>
+      <c r="L84" s="78"/>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18">
@@ -7942,7 +7918,7 @@
       <c r="H85" s="64"/>
       <c r="I85" s="61"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="73"/>
+      <c r="L85" s="78"/>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18">
@@ -7957,7 +7933,7 @@
       <c r="H86" s="64"/>
       <c r="I86" s="61"/>
       <c r="K86" s="15"/>
-      <c r="L86" s="73"/>
+      <c r="L86" s="78"/>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18">
@@ -7972,7 +7948,7 @@
       <c r="H87" s="64"/>
       <c r="I87" s="61"/>
       <c r="K87" s="15"/>
-      <c r="L87" s="73"/>
+      <c r="L87" s="78"/>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18">
@@ -7987,7 +7963,7 @@
       <c r="H88" s="64"/>
       <c r="I88" s="61"/>
       <c r="K88" s="15"/>
-      <c r="L88" s="73"/>
+      <c r="L88" s="78"/>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="18">
@@ -8002,7 +7978,7 @@
       <c r="H89" s="64"/>
       <c r="I89" s="61"/>
       <c r="K89" s="15"/>
-      <c r="L89" s="73"/>
+      <c r="L89" s="78"/>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18">
@@ -8017,7 +7993,7 @@
       <c r="H90" s="64"/>
       <c r="I90" s="61"/>
       <c r="K90" s="15"/>
-      <c r="L90" s="73"/>
+      <c r="L90" s="78"/>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18">
@@ -8032,7 +8008,7 @@
       <c r="H91" s="64"/>
       <c r="I91" s="61"/>
       <c r="K91" s="15"/>
-      <c r="L91" s="73"/>
+      <c r="L91" s="78"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18">
@@ -8047,7 +8023,7 @@
       <c r="H92" s="64"/>
       <c r="I92" s="61"/>
       <c r="K92" s="15"/>
-      <c r="L92" s="73"/>
+      <c r="L92" s="78"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18">
@@ -8062,7 +8038,7 @@
       <c r="H93" s="64"/>
       <c r="I93" s="61"/>
       <c r="K93" s="15"/>
-      <c r="L93" s="73"/>
+      <c r="L93" s="78"/>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18">
@@ -8077,7 +8053,7 @@
       <c r="H94" s="64"/>
       <c r="I94" s="61"/>
       <c r="K94" s="15"/>
-      <c r="L94" s="73"/>
+      <c r="L94" s="78"/>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18">
@@ -8092,7 +8068,7 @@
       <c r="H95" s="64"/>
       <c r="I95" s="61"/>
       <c r="K95" s="15"/>
-      <c r="L95" s="73"/>
+      <c r="L95" s="78"/>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18">
@@ -8107,7 +8083,7 @@
       <c r="H96" s="64"/>
       <c r="I96" s="61"/>
       <c r="K96" s="15"/>
-      <c r="L96" s="73"/>
+      <c r="L96" s="78"/>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="18">
@@ -8122,7 +8098,7 @@
       <c r="H97" s="64"/>
       <c r="I97" s="61"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="73"/>
+      <c r="L97" s="78"/>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="18">
@@ -8137,7 +8113,7 @@
       <c r="H98" s="64"/>
       <c r="I98" s="61"/>
       <c r="K98" s="15"/>
-      <c r="L98" s="73"/>
+      <c r="L98" s="78"/>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="18">
@@ -8152,7 +8128,7 @@
       <c r="H99" s="64"/>
       <c r="I99" s="61"/>
       <c r="K99" s="15"/>
-      <c r="L99" s="73"/>
+      <c r="L99" s="78"/>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="18">
@@ -8167,7 +8143,7 @@
       <c r="H100" s="64"/>
       <c r="I100" s="61"/>
       <c r="K100" s="15"/>
-      <c r="L100" s="73"/>
+      <c r="L100" s="78"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A101" s="18">
@@ -8182,7 +8158,7 @@
       <c r="H101" s="64"/>
       <c r="I101" s="61"/>
       <c r="K101" s="15"/>
-      <c r="L101" s="73"/>
+      <c r="L101" s="78"/>
     </row>
     <row r="102" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="18">
@@ -8197,7 +8173,7 @@
       <c r="H102" s="65"/>
       <c r="I102" s="62"/>
       <c r="K102" s="16"/>
-      <c r="L102" s="74"/>
+      <c r="L102" s="78"/>
     </row>
     <row r="103" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="51" t="s">
@@ -8424,16 +8400,16 @@
   <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="75" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="75" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="75" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="75" customWidth="1"/>
-    <col min="8" max="9" width="10.625" style="75" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="75" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="75" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="72" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="72" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="72" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="72" customWidth="1"/>
+    <col min="8" max="9" width="10.625" style="72" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8494,9 +8470,7 @@
       <c r="K2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="72" t="s">
-        <v>25</v>
-      </c>
+      <c r="L2" s="77"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="18">
@@ -8511,7 +8485,7 @@
       <c r="H3" s="63"/>
       <c r="I3" s="61"/>
       <c r="K3" s="15"/>
-      <c r="L3" s="73"/>
+      <c r="L3" s="78"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18">
@@ -8526,7 +8500,7 @@
       <c r="H4" s="64"/>
       <c r="I4" s="61"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="73"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18">
@@ -8541,7 +8515,7 @@
       <c r="H5" s="64"/>
       <c r="I5" s="61"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="73"/>
+      <c r="L5" s="78"/>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18">
@@ -8556,7 +8530,7 @@
       <c r="H6" s="64"/>
       <c r="I6" s="61"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="73"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18">
@@ -8571,7 +8545,7 @@
       <c r="H7" s="64"/>
       <c r="I7" s="61"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="73"/>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18">
@@ -8586,7 +8560,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="61"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="73"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18">
@@ -8601,7 +8575,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="61"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="73"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18">
@@ -8616,7 +8590,7 @@
       <c r="H10" s="64"/>
       <c r="I10" s="61"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="73"/>
+      <c r="L10" s="78"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18">
@@ -8631,7 +8605,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="61"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="73"/>
+      <c r="L11" s="78"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18">
@@ -8646,7 +8620,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="61"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="73"/>
+      <c r="L12" s="78"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="18">
@@ -8661,7 +8635,7 @@
       <c r="H13" s="64"/>
       <c r="I13" s="61"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="73"/>
+      <c r="L13" s="78"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18">
@@ -8676,7 +8650,7 @@
       <c r="H14" s="64"/>
       <c r="I14" s="61"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="73"/>
+      <c r="L14" s="78"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18">
@@ -8691,7 +8665,7 @@
       <c r="H15" s="64"/>
       <c r="I15" s="61"/>
       <c r="K15" s="15"/>
-      <c r="L15" s="73"/>
+      <c r="L15" s="78"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18">
@@ -8706,7 +8680,7 @@
       <c r="H16" s="64"/>
       <c r="I16" s="61"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="73"/>
+      <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18">
@@ -8721,7 +8695,7 @@
       <c r="H17" s="64"/>
       <c r="I17" s="61"/>
       <c r="K17" s="15"/>
-      <c r="L17" s="73"/>
+      <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18">
@@ -8736,7 +8710,7 @@
       <c r="H18" s="64"/>
       <c r="I18" s="61"/>
       <c r="K18" s="15"/>
-      <c r="L18" s="73"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18">
@@ -8751,7 +8725,7 @@
       <c r="H19" s="64"/>
       <c r="I19" s="61"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="73"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18">
@@ -8766,7 +8740,7 @@
       <c r="H20" s="64"/>
       <c r="I20" s="61"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="73"/>
+      <c r="L20" s="78"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18">
@@ -8781,7 +8755,7 @@
       <c r="H21" s="64"/>
       <c r="I21" s="61"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="73"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18">
@@ -8796,7 +8770,7 @@
       <c r="H22" s="64"/>
       <c r="I22" s="61"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="73"/>
+      <c r="L22" s="78"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18">
@@ -8811,7 +8785,7 @@
       <c r="H23" s="64"/>
       <c r="I23" s="61"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="73"/>
+      <c r="L23" s="78"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18">
@@ -8826,7 +8800,7 @@
       <c r="H24" s="64"/>
       <c r="I24" s="61"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="73"/>
+      <c r="L24" s="78"/>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18">
@@ -8841,7 +8815,7 @@
       <c r="H25" s="64"/>
       <c r="I25" s="61"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="73"/>
+      <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18">
@@ -8856,7 +8830,7 @@
       <c r="H26" s="64"/>
       <c r="I26" s="61"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="73"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="18">
@@ -8871,7 +8845,7 @@
       <c r="H27" s="64"/>
       <c r="I27" s="61"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="73"/>
+      <c r="L27" s="78"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18">
@@ -8886,7 +8860,7 @@
       <c r="H28" s="64"/>
       <c r="I28" s="61"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="73"/>
+      <c r="L28" s="78"/>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18">
@@ -8901,7 +8875,7 @@
       <c r="H29" s="64"/>
       <c r="I29" s="61"/>
       <c r="K29" s="15"/>
-      <c r="L29" s="73"/>
+      <c r="L29" s="78"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18">
@@ -8916,7 +8890,7 @@
       <c r="H30" s="64"/>
       <c r="I30" s="61"/>
       <c r="K30" s="15"/>
-      <c r="L30" s="73"/>
+      <c r="L30" s="78"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18">
@@ -8931,7 +8905,7 @@
       <c r="H31" s="64"/>
       <c r="I31" s="61"/>
       <c r="K31" s="15"/>
-      <c r="L31" s="73"/>
+      <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18">
@@ -8946,7 +8920,7 @@
       <c r="H32" s="64"/>
       <c r="I32" s="61"/>
       <c r="K32" s="15"/>
-      <c r="L32" s="73"/>
+      <c r="L32" s="78"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18">
@@ -8961,7 +8935,7 @@
       <c r="H33" s="64"/>
       <c r="I33" s="61"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="73"/>
+      <c r="L33" s="78"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18">
@@ -8976,7 +8950,7 @@
       <c r="H34" s="64"/>
       <c r="I34" s="61"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="73"/>
+      <c r="L34" s="78"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18">
@@ -8991,7 +8965,7 @@
       <c r="H35" s="64"/>
       <c r="I35" s="61"/>
       <c r="K35" s="15"/>
-      <c r="L35" s="73"/>
+      <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18">
@@ -9006,7 +8980,7 @@
       <c r="H36" s="64"/>
       <c r="I36" s="61"/>
       <c r="K36" s="15"/>
-      <c r="L36" s="73"/>
+      <c r="L36" s="78"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18">
@@ -9021,7 +8995,7 @@
       <c r="H37" s="64"/>
       <c r="I37" s="61"/>
       <c r="K37" s="15"/>
-      <c r="L37" s="73"/>
+      <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18">
@@ -9036,7 +9010,7 @@
       <c r="H38" s="64"/>
       <c r="I38" s="61"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="78"/>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18">
@@ -9051,7 +9025,7 @@
       <c r="H39" s="64"/>
       <c r="I39" s="61"/>
       <c r="K39" s="15"/>
-      <c r="L39" s="73"/>
+      <c r="L39" s="78"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18">
@@ -9066,7 +9040,7 @@
       <c r="H40" s="64"/>
       <c r="I40" s="61"/>
       <c r="K40" s="15"/>
-      <c r="L40" s="73"/>
+      <c r="L40" s="78"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18">
@@ -9081,7 +9055,7 @@
       <c r="H41" s="64"/>
       <c r="I41" s="61"/>
       <c r="K41" s="15"/>
-      <c r="L41" s="73"/>
+      <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18">
@@ -9096,7 +9070,7 @@
       <c r="H42" s="64"/>
       <c r="I42" s="61"/>
       <c r="K42" s="15"/>
-      <c r="L42" s="73"/>
+      <c r="L42" s="78"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18">
@@ -9111,7 +9085,7 @@
       <c r="H43" s="64"/>
       <c r="I43" s="61"/>
       <c r="K43" s="15"/>
-      <c r="L43" s="73"/>
+      <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18">
@@ -9126,7 +9100,7 @@
       <c r="H44" s="64"/>
       <c r="I44" s="61"/>
       <c r="K44" s="15"/>
-      <c r="L44" s="73"/>
+      <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18">
@@ -9141,7 +9115,7 @@
       <c r="H45" s="64"/>
       <c r="I45" s="61"/>
       <c r="K45" s="15"/>
-      <c r="L45" s="73"/>
+      <c r="L45" s="78"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18">
@@ -9156,7 +9130,7 @@
       <c r="H46" s="64"/>
       <c r="I46" s="61"/>
       <c r="K46" s="15"/>
-      <c r="L46" s="73"/>
+      <c r="L46" s="78"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18">
@@ -9171,7 +9145,7 @@
       <c r="H47" s="64"/>
       <c r="I47" s="61"/>
       <c r="K47" s="15"/>
-      <c r="L47" s="73"/>
+      <c r="L47" s="78"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18">
@@ -9186,7 +9160,7 @@
       <c r="H48" s="64"/>
       <c r="I48" s="61"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="73"/>
+      <c r="L48" s="78"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18">
@@ -9201,7 +9175,7 @@
       <c r="H49" s="64"/>
       <c r="I49" s="61"/>
       <c r="K49" s="15"/>
-      <c r="L49" s="73"/>
+      <c r="L49" s="78"/>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18">
@@ -9216,7 +9190,7 @@
       <c r="H50" s="64"/>
       <c r="I50" s="61"/>
       <c r="K50" s="15"/>
-      <c r="L50" s="73"/>
+      <c r="L50" s="78"/>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18">
@@ -9231,7 +9205,7 @@
       <c r="H51" s="64"/>
       <c r="I51" s="61"/>
       <c r="K51" s="15"/>
-      <c r="L51" s="73"/>
+      <c r="L51" s="78"/>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18">
@@ -9246,7 +9220,7 @@
       <c r="H52" s="64"/>
       <c r="I52" s="61"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="73"/>
+      <c r="L52" s="78"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="18">
@@ -9261,7 +9235,7 @@
       <c r="H53" s="64"/>
       <c r="I53" s="61"/>
       <c r="K53" s="15"/>
-      <c r="L53" s="73"/>
+      <c r="L53" s="78"/>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18">
@@ -9276,7 +9250,7 @@
       <c r="H54" s="64"/>
       <c r="I54" s="61"/>
       <c r="K54" s="15"/>
-      <c r="L54" s="73"/>
+      <c r="L54" s="78"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18">
@@ -9291,7 +9265,7 @@
       <c r="H55" s="64"/>
       <c r="I55" s="61"/>
       <c r="K55" s="15"/>
-      <c r="L55" s="73"/>
+      <c r="L55" s="78"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18">
@@ -9306,7 +9280,7 @@
       <c r="H56" s="64"/>
       <c r="I56" s="61"/>
       <c r="K56" s="15"/>
-      <c r="L56" s="73"/>
+      <c r="L56" s="78"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18">
@@ -9321,7 +9295,7 @@
       <c r="H57" s="64"/>
       <c r="I57" s="61"/>
       <c r="K57" s="15"/>
-      <c r="L57" s="73"/>
+      <c r="L57" s="78"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18">
@@ -9336,7 +9310,7 @@
       <c r="H58" s="64"/>
       <c r="I58" s="61"/>
       <c r="K58" s="15"/>
-      <c r="L58" s="73"/>
+      <c r="L58" s="78"/>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18">
@@ -9351,7 +9325,7 @@
       <c r="H59" s="64"/>
       <c r="I59" s="61"/>
       <c r="K59" s="15"/>
-      <c r="L59" s="73"/>
+      <c r="L59" s="78"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18">
@@ -9366,7 +9340,7 @@
       <c r="H60" s="64"/>
       <c r="I60" s="61"/>
       <c r="K60" s="15"/>
-      <c r="L60" s="73"/>
+      <c r="L60" s="78"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18">
@@ -9381,7 +9355,7 @@
       <c r="H61" s="64"/>
       <c r="I61" s="61"/>
       <c r="K61" s="15"/>
-      <c r="L61" s="73"/>
+      <c r="L61" s="78"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="18">
@@ -9396,7 +9370,7 @@
       <c r="H62" s="64"/>
       <c r="I62" s="61"/>
       <c r="K62" s="15"/>
-      <c r="L62" s="73"/>
+      <c r="L62" s="78"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18">
@@ -9411,7 +9385,7 @@
       <c r="H63" s="64"/>
       <c r="I63" s="61"/>
       <c r="K63" s="15"/>
-      <c r="L63" s="73"/>
+      <c r="L63" s="78"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18">
@@ -9426,7 +9400,7 @@
       <c r="H64" s="64"/>
       <c r="I64" s="61"/>
       <c r="K64" s="15"/>
-      <c r="L64" s="73"/>
+      <c r="L64" s="78"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18">
@@ -9441,7 +9415,7 @@
       <c r="H65" s="64"/>
       <c r="I65" s="61"/>
       <c r="K65" s="15"/>
-      <c r="L65" s="73"/>
+      <c r="L65" s="78"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18">
@@ -9456,7 +9430,7 @@
       <c r="H66" s="64"/>
       <c r="I66" s="61"/>
       <c r="K66" s="15"/>
-      <c r="L66" s="73"/>
+      <c r="L66" s="78"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18">
@@ -9471,7 +9445,7 @@
       <c r="H67" s="64"/>
       <c r="I67" s="61"/>
       <c r="K67" s="15"/>
-      <c r="L67" s="73"/>
+      <c r="L67" s="78"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18">
@@ -9486,7 +9460,7 @@
       <c r="H68" s="64"/>
       <c r="I68" s="61"/>
       <c r="K68" s="15"/>
-      <c r="L68" s="73"/>
+      <c r="L68" s="78"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18">
@@ -9501,7 +9475,7 @@
       <c r="H69" s="64"/>
       <c r="I69" s="61"/>
       <c r="K69" s="15"/>
-      <c r="L69" s="73"/>
+      <c r="L69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18">
@@ -9516,7 +9490,7 @@
       <c r="H70" s="64"/>
       <c r="I70" s="61"/>
       <c r="K70" s="15"/>
-      <c r="L70" s="73"/>
+      <c r="L70" s="78"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18">
@@ -9531,7 +9505,7 @@
       <c r="H71" s="64"/>
       <c r="I71" s="61"/>
       <c r="K71" s="15"/>
-      <c r="L71" s="73"/>
+      <c r="L71" s="78"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18">
@@ -9546,7 +9520,7 @@
       <c r="H72" s="64"/>
       <c r="I72" s="61"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="73"/>
+      <c r="L72" s="78"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18">
@@ -9561,7 +9535,7 @@
       <c r="H73" s="64"/>
       <c r="I73" s="61"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="73"/>
+      <c r="L73" s="78"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18">
@@ -9576,7 +9550,7 @@
       <c r="H74" s="64"/>
       <c r="I74" s="61"/>
       <c r="K74" s="15"/>
-      <c r="L74" s="73"/>
+      <c r="L74" s="78"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18">
@@ -9591,7 +9565,7 @@
       <c r="H75" s="64"/>
       <c r="I75" s="61"/>
       <c r="K75" s="15"/>
-      <c r="L75" s="73"/>
+      <c r="L75" s="78"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="18">
@@ -9606,7 +9580,7 @@
       <c r="H76" s="64"/>
       <c r="I76" s="61"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="73"/>
+      <c r="L76" s="78"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18">
@@ -9621,7 +9595,7 @@
       <c r="H77" s="64"/>
       <c r="I77" s="61"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="73"/>
+      <c r="L77" s="78"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18">
@@ -9636,7 +9610,7 @@
       <c r="H78" s="64"/>
       <c r="I78" s="61"/>
       <c r="K78" s="15"/>
-      <c r="L78" s="73"/>
+      <c r="L78" s="78"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18">
@@ -9651,7 +9625,7 @@
       <c r="H79" s="64"/>
       <c r="I79" s="61"/>
       <c r="K79" s="15"/>
-      <c r="L79" s="73"/>
+      <c r="L79" s="78"/>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18">
@@ -9666,7 +9640,7 @@
       <c r="H80" s="64"/>
       <c r="I80" s="61"/>
       <c r="K80" s="15"/>
-      <c r="L80" s="73"/>
+      <c r="L80" s="78"/>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18">
@@ -9681,7 +9655,7 @@
       <c r="H81" s="64"/>
       <c r="I81" s="61"/>
       <c r="K81" s="15"/>
-      <c r="L81" s="73"/>
+      <c r="L81" s="78"/>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18">
@@ -9696,7 +9670,7 @@
       <c r="H82" s="64"/>
       <c r="I82" s="61"/>
       <c r="K82" s="15"/>
-      <c r="L82" s="73"/>
+      <c r="L82" s="78"/>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18">
@@ -9711,7 +9685,7 @@
       <c r="H83" s="64"/>
       <c r="I83" s="61"/>
       <c r="K83" s="15"/>
-      <c r="L83" s="73"/>
+      <c r="L83" s="78"/>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18">
@@ -9726,7 +9700,7 @@
       <c r="H84" s="64"/>
       <c r="I84" s="61"/>
       <c r="K84" s="15"/>
-      <c r="L84" s="73"/>
+      <c r="L84" s="78"/>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18">
@@ -9741,7 +9715,7 @@
       <c r="H85" s="64"/>
       <c r="I85" s="61"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="73"/>
+      <c r="L85" s="78"/>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18">
@@ -9756,7 +9730,7 @@
       <c r="H86" s="64"/>
       <c r="I86" s="61"/>
       <c r="K86" s="15"/>
-      <c r="L86" s="73"/>
+      <c r="L86" s="78"/>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18">
@@ -9771,7 +9745,7 @@
       <c r="H87" s="64"/>
       <c r="I87" s="61"/>
       <c r="K87" s="15"/>
-      <c r="L87" s="73"/>
+      <c r="L87" s="78"/>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18">
@@ -9786,7 +9760,7 @@
       <c r="H88" s="64"/>
       <c r="I88" s="61"/>
       <c r="K88" s="15"/>
-      <c r="L88" s="73"/>
+      <c r="L88" s="78"/>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="18">
@@ -9801,7 +9775,7 @@
       <c r="H89" s="64"/>
       <c r="I89" s="61"/>
       <c r="K89" s="15"/>
-      <c r="L89" s="73"/>
+      <c r="L89" s="78"/>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18">
@@ -9816,7 +9790,7 @@
       <c r="H90" s="64"/>
       <c r="I90" s="61"/>
       <c r="K90" s="15"/>
-      <c r="L90" s="73"/>
+      <c r="L90" s="78"/>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18">
@@ -9831,7 +9805,7 @@
       <c r="H91" s="64"/>
       <c r="I91" s="61"/>
       <c r="K91" s="15"/>
-      <c r="L91" s="73"/>
+      <c r="L91" s="78"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18">
@@ -9846,7 +9820,7 @@
       <c r="H92" s="64"/>
       <c r="I92" s="61"/>
       <c r="K92" s="15"/>
-      <c r="L92" s="73"/>
+      <c r="L92" s="78"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18">
@@ -9861,7 +9835,7 @@
       <c r="H93" s="64"/>
       <c r="I93" s="61"/>
       <c r="K93" s="15"/>
-      <c r="L93" s="73"/>
+      <c r="L93" s="78"/>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18">
@@ -9876,7 +9850,7 @@
       <c r="H94" s="64"/>
       <c r="I94" s="61"/>
       <c r="K94" s="15"/>
-      <c r="L94" s="73"/>
+      <c r="L94" s="78"/>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18">
@@ -9891,7 +9865,7 @@
       <c r="H95" s="64"/>
       <c r="I95" s="61"/>
       <c r="K95" s="15"/>
-      <c r="L95" s="73"/>
+      <c r="L95" s="78"/>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18">
@@ -9906,7 +9880,7 @@
       <c r="H96" s="64"/>
       <c r="I96" s="61"/>
       <c r="K96" s="15"/>
-      <c r="L96" s="73"/>
+      <c r="L96" s="78"/>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="18">
@@ -9921,7 +9895,7 @@
       <c r="H97" s="64"/>
       <c r="I97" s="61"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="73"/>
+      <c r="L97" s="78"/>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="18">
@@ -9936,7 +9910,7 @@
       <c r="H98" s="64"/>
       <c r="I98" s="61"/>
       <c r="K98" s="15"/>
-      <c r="L98" s="73"/>
+      <c r="L98" s="78"/>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="18">
@@ -9951,7 +9925,7 @@
       <c r="H99" s="64"/>
       <c r="I99" s="61"/>
       <c r="K99" s="15"/>
-      <c r="L99" s="73"/>
+      <c r="L99" s="78"/>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="18">
@@ -9966,7 +9940,7 @@
       <c r="H100" s="64"/>
       <c r="I100" s="61"/>
       <c r="K100" s="15"/>
-      <c r="L100" s="73"/>
+      <c r="L100" s="78"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A101" s="18">
@@ -9981,7 +9955,7 @@
       <c r="H101" s="64"/>
       <c r="I101" s="61"/>
       <c r="K101" s="15"/>
-      <c r="L101" s="73"/>
+      <c r="L101" s="78"/>
     </row>
     <row r="102" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="18">
@@ -9996,7 +9970,7 @@
       <c r="H102" s="65"/>
       <c r="I102" s="62"/>
       <c r="K102" s="16"/>
-      <c r="L102" s="74"/>
+      <c r="L102" s="78"/>
     </row>
     <row r="103" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="51" t="s">
@@ -10054,16 +10028,16 @@
   <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="75" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="75" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="75" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="75" customWidth="1"/>
-    <col min="8" max="9" width="10.625" style="75" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="75" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="75" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="72" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="72" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="72" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="72" customWidth="1"/>
+    <col min="8" max="9" width="10.625" style="72" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10079,7 +10053,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
@@ -10124,9 +10098,7 @@
       <c r="K2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="72" t="s">
-        <v>25</v>
-      </c>
+      <c r="L2" s="77"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="18">
@@ -10141,7 +10113,7 @@
       <c r="H3" s="63"/>
       <c r="I3" s="61"/>
       <c r="K3" s="15"/>
-      <c r="L3" s="73"/>
+      <c r="L3" s="78"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18">
@@ -10156,7 +10128,7 @@
       <c r="H4" s="64"/>
       <c r="I4" s="61"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="73"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18">
@@ -10171,7 +10143,7 @@
       <c r="H5" s="64"/>
       <c r="I5" s="61"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="73"/>
+      <c r="L5" s="78"/>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18">
@@ -10186,7 +10158,7 @@
       <c r="H6" s="64"/>
       <c r="I6" s="61"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="73"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18">
@@ -10201,7 +10173,7 @@
       <c r="H7" s="64"/>
       <c r="I7" s="61"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="73"/>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18">
@@ -10216,7 +10188,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="61"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="73"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18">
@@ -10231,7 +10203,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="61"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="73"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18">
@@ -10246,7 +10218,7 @@
       <c r="H10" s="64"/>
       <c r="I10" s="61"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="73"/>
+      <c r="L10" s="78"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18">
@@ -10261,7 +10233,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="61"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="73"/>
+      <c r="L11" s="78"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18">
@@ -10276,7 +10248,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="61"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="73"/>
+      <c r="L12" s="78"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="18">
@@ -10291,7 +10263,7 @@
       <c r="H13" s="64"/>
       <c r="I13" s="61"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="73"/>
+      <c r="L13" s="78"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18">
@@ -10306,7 +10278,7 @@
       <c r="H14" s="64"/>
       <c r="I14" s="61"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="73"/>
+      <c r="L14" s="78"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18">
@@ -10321,7 +10293,7 @@
       <c r="H15" s="64"/>
       <c r="I15" s="61"/>
       <c r="K15" s="15"/>
-      <c r="L15" s="73"/>
+      <c r="L15" s="78"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18">
@@ -10336,7 +10308,7 @@
       <c r="H16" s="64"/>
       <c r="I16" s="61"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="73"/>
+      <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18">
@@ -10351,7 +10323,7 @@
       <c r="H17" s="64"/>
       <c r="I17" s="61"/>
       <c r="K17" s="15"/>
-      <c r="L17" s="73"/>
+      <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18">
@@ -10366,7 +10338,7 @@
       <c r="H18" s="64"/>
       <c r="I18" s="61"/>
       <c r="K18" s="15"/>
-      <c r="L18" s="73"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18">
@@ -10381,7 +10353,7 @@
       <c r="H19" s="64"/>
       <c r="I19" s="61"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="73"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18">
@@ -10396,7 +10368,7 @@
       <c r="H20" s="64"/>
       <c r="I20" s="61"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="73"/>
+      <c r="L20" s="78"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18">
@@ -10411,7 +10383,7 @@
       <c r="H21" s="64"/>
       <c r="I21" s="61"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="73"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18">
@@ -10426,7 +10398,7 @@
       <c r="H22" s="64"/>
       <c r="I22" s="61"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="73"/>
+      <c r="L22" s="78"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18">
@@ -10441,7 +10413,7 @@
       <c r="H23" s="64"/>
       <c r="I23" s="61"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="73"/>
+      <c r="L23" s="78"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18">
@@ -10456,7 +10428,7 @@
       <c r="H24" s="64"/>
       <c r="I24" s="61"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="73"/>
+      <c r="L24" s="78"/>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18">
@@ -10471,7 +10443,7 @@
       <c r="H25" s="64"/>
       <c r="I25" s="61"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="73"/>
+      <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18">
@@ -10486,7 +10458,7 @@
       <c r="H26" s="64"/>
       <c r="I26" s="61"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="73"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="18">
@@ -10501,7 +10473,7 @@
       <c r="H27" s="64"/>
       <c r="I27" s="61"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="73"/>
+      <c r="L27" s="78"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18">
@@ -10516,7 +10488,7 @@
       <c r="H28" s="64"/>
       <c r="I28" s="61"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="73"/>
+      <c r="L28" s="78"/>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18">
@@ -10531,7 +10503,7 @@
       <c r="H29" s="64"/>
       <c r="I29" s="61"/>
       <c r="K29" s="15"/>
-      <c r="L29" s="73"/>
+      <c r="L29" s="78"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18">
@@ -10546,7 +10518,7 @@
       <c r="H30" s="64"/>
       <c r="I30" s="61"/>
       <c r="K30" s="15"/>
-      <c r="L30" s="73"/>
+      <c r="L30" s="78"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18">
@@ -10561,7 +10533,7 @@
       <c r="H31" s="64"/>
       <c r="I31" s="61"/>
       <c r="K31" s="15"/>
-      <c r="L31" s="73"/>
+      <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18">
@@ -10576,7 +10548,7 @@
       <c r="H32" s="64"/>
       <c r="I32" s="61"/>
       <c r="K32" s="15"/>
-      <c r="L32" s="73"/>
+      <c r="L32" s="78"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18">
@@ -10591,7 +10563,7 @@
       <c r="H33" s="64"/>
       <c r="I33" s="61"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="73"/>
+      <c r="L33" s="78"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18">
@@ -10606,7 +10578,7 @@
       <c r="H34" s="64"/>
       <c r="I34" s="61"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="73"/>
+      <c r="L34" s="78"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18">
@@ -10621,7 +10593,7 @@
       <c r="H35" s="64"/>
       <c r="I35" s="61"/>
       <c r="K35" s="15"/>
-      <c r="L35" s="73"/>
+      <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18">
@@ -10636,7 +10608,7 @@
       <c r="H36" s="64"/>
       <c r="I36" s="61"/>
       <c r="K36" s="15"/>
-      <c r="L36" s="73"/>
+      <c r="L36" s="78"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18">
@@ -10651,7 +10623,7 @@
       <c r="H37" s="64"/>
       <c r="I37" s="61"/>
       <c r="K37" s="15"/>
-      <c r="L37" s="73"/>
+      <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18">
@@ -10666,7 +10638,7 @@
       <c r="H38" s="64"/>
       <c r="I38" s="61"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="78"/>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18">
@@ -10681,7 +10653,7 @@
       <c r="H39" s="64"/>
       <c r="I39" s="61"/>
       <c r="K39" s="15"/>
-      <c r="L39" s="73"/>
+      <c r="L39" s="78"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18">
@@ -10696,7 +10668,7 @@
       <c r="H40" s="64"/>
       <c r="I40" s="61"/>
       <c r="K40" s="15"/>
-      <c r="L40" s="73"/>
+      <c r="L40" s="78"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18">
@@ -10711,7 +10683,7 @@
       <c r="H41" s="64"/>
       <c r="I41" s="61"/>
       <c r="K41" s="15"/>
-      <c r="L41" s="73"/>
+      <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18">
@@ -10726,7 +10698,7 @@
       <c r="H42" s="64"/>
       <c r="I42" s="61"/>
       <c r="K42" s="15"/>
-      <c r="L42" s="73"/>
+      <c r="L42" s="78"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18">
@@ -10741,7 +10713,7 @@
       <c r="H43" s="64"/>
       <c r="I43" s="61"/>
       <c r="K43" s="15"/>
-      <c r="L43" s="73"/>
+      <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18">
@@ -10756,7 +10728,7 @@
       <c r="H44" s="64"/>
       <c r="I44" s="61"/>
       <c r="K44" s="15"/>
-      <c r="L44" s="73"/>
+      <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18">
@@ -10771,7 +10743,7 @@
       <c r="H45" s="64"/>
       <c r="I45" s="61"/>
       <c r="K45" s="15"/>
-      <c r="L45" s="73"/>
+      <c r="L45" s="78"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18">
@@ -10786,7 +10758,7 @@
       <c r="H46" s="64"/>
       <c r="I46" s="61"/>
       <c r="K46" s="15"/>
-      <c r="L46" s="73"/>
+      <c r="L46" s="78"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18">
@@ -10801,7 +10773,7 @@
       <c r="H47" s="64"/>
       <c r="I47" s="61"/>
       <c r="K47" s="15"/>
-      <c r="L47" s="73"/>
+      <c r="L47" s="78"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18">
@@ -10816,7 +10788,7 @@
       <c r="H48" s="64"/>
       <c r="I48" s="61"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="73"/>
+      <c r="L48" s="78"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18">
@@ -10831,7 +10803,7 @@
       <c r="H49" s="64"/>
       <c r="I49" s="61"/>
       <c r="K49" s="15"/>
-      <c r="L49" s="73"/>
+      <c r="L49" s="78"/>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18">
@@ -10846,7 +10818,7 @@
       <c r="H50" s="64"/>
       <c r="I50" s="61"/>
       <c r="K50" s="15"/>
-      <c r="L50" s="73"/>
+      <c r="L50" s="78"/>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18">
@@ -10861,7 +10833,7 @@
       <c r="H51" s="64"/>
       <c r="I51" s="61"/>
       <c r="K51" s="15"/>
-      <c r="L51" s="73"/>
+      <c r="L51" s="78"/>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18">
@@ -10876,7 +10848,7 @@
       <c r="H52" s="64"/>
       <c r="I52" s="61"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="73"/>
+      <c r="L52" s="78"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="18">
@@ -10891,7 +10863,7 @@
       <c r="H53" s="64"/>
       <c r="I53" s="61"/>
       <c r="K53" s="15"/>
-      <c r="L53" s="73"/>
+      <c r="L53" s="78"/>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18">
@@ -10906,7 +10878,7 @@
       <c r="H54" s="64"/>
       <c r="I54" s="61"/>
       <c r="K54" s="15"/>
-      <c r="L54" s="73"/>
+      <c r="L54" s="78"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18">
@@ -10921,7 +10893,7 @@
       <c r="H55" s="64"/>
       <c r="I55" s="61"/>
       <c r="K55" s="15"/>
-      <c r="L55" s="73"/>
+      <c r="L55" s="78"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18">
@@ -10936,7 +10908,7 @@
       <c r="H56" s="64"/>
       <c r="I56" s="61"/>
       <c r="K56" s="15"/>
-      <c r="L56" s="73"/>
+      <c r="L56" s="78"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18">
@@ -10951,7 +10923,7 @@
       <c r="H57" s="64"/>
       <c r="I57" s="61"/>
       <c r="K57" s="15"/>
-      <c r="L57" s="73"/>
+      <c r="L57" s="78"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18">
@@ -10966,7 +10938,7 @@
       <c r="H58" s="64"/>
       <c r="I58" s="61"/>
       <c r="K58" s="15"/>
-      <c r="L58" s="73"/>
+      <c r="L58" s="78"/>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18">
@@ -10981,7 +10953,7 @@
       <c r="H59" s="64"/>
       <c r="I59" s="61"/>
       <c r="K59" s="15"/>
-      <c r="L59" s="73"/>
+      <c r="L59" s="78"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18">
@@ -10996,7 +10968,7 @@
       <c r="H60" s="64"/>
       <c r="I60" s="61"/>
       <c r="K60" s="15"/>
-      <c r="L60" s="73"/>
+      <c r="L60" s="78"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18">
@@ -11011,7 +10983,7 @@
       <c r="H61" s="64"/>
       <c r="I61" s="61"/>
       <c r="K61" s="15"/>
-      <c r="L61" s="73"/>
+      <c r="L61" s="78"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="18">
@@ -11026,7 +10998,7 @@
       <c r="H62" s="64"/>
       <c r="I62" s="61"/>
       <c r="K62" s="15"/>
-      <c r="L62" s="73"/>
+      <c r="L62" s="78"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18">
@@ -11041,7 +11013,7 @@
       <c r="H63" s="64"/>
       <c r="I63" s="61"/>
       <c r="K63" s="15"/>
-      <c r="L63" s="73"/>
+      <c r="L63" s="78"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18">
@@ -11056,7 +11028,7 @@
       <c r="H64" s="64"/>
       <c r="I64" s="61"/>
       <c r="K64" s="15"/>
-      <c r="L64" s="73"/>
+      <c r="L64" s="78"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18">
@@ -11071,7 +11043,7 @@
       <c r="H65" s="64"/>
       <c r="I65" s="61"/>
       <c r="K65" s="15"/>
-      <c r="L65" s="73"/>
+      <c r="L65" s="78"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18">
@@ -11086,7 +11058,7 @@
       <c r="H66" s="64"/>
       <c r="I66" s="61"/>
       <c r="K66" s="15"/>
-      <c r="L66" s="73"/>
+      <c r="L66" s="78"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18">
@@ -11101,7 +11073,7 @@
       <c r="H67" s="64"/>
       <c r="I67" s="61"/>
       <c r="K67" s="15"/>
-      <c r="L67" s="73"/>
+      <c r="L67" s="78"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18">
@@ -11116,7 +11088,7 @@
       <c r="H68" s="64"/>
       <c r="I68" s="61"/>
       <c r="K68" s="15"/>
-      <c r="L68" s="73"/>
+      <c r="L68" s="78"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18">
@@ -11131,7 +11103,7 @@
       <c r="H69" s="64"/>
       <c r="I69" s="61"/>
       <c r="K69" s="15"/>
-      <c r="L69" s="73"/>
+      <c r="L69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18">
@@ -11146,7 +11118,7 @@
       <c r="H70" s="64"/>
       <c r="I70" s="61"/>
       <c r="K70" s="15"/>
-      <c r="L70" s="73"/>
+      <c r="L70" s="78"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18">
@@ -11161,7 +11133,7 @@
       <c r="H71" s="64"/>
       <c r="I71" s="61"/>
       <c r="K71" s="15"/>
-      <c r="L71" s="73"/>
+      <c r="L71" s="78"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18">
@@ -11176,7 +11148,7 @@
       <c r="H72" s="64"/>
       <c r="I72" s="61"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="73"/>
+      <c r="L72" s="78"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18">
@@ -11191,7 +11163,7 @@
       <c r="H73" s="64"/>
       <c r="I73" s="61"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="73"/>
+      <c r="L73" s="78"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18">
@@ -11206,7 +11178,7 @@
       <c r="H74" s="64"/>
       <c r="I74" s="61"/>
       <c r="K74" s="15"/>
-      <c r="L74" s="73"/>
+      <c r="L74" s="78"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18">
@@ -11221,7 +11193,7 @@
       <c r="H75" s="64"/>
       <c r="I75" s="61"/>
       <c r="K75" s="15"/>
-      <c r="L75" s="73"/>
+      <c r="L75" s="78"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="18">
@@ -11236,7 +11208,7 @@
       <c r="H76" s="64"/>
       <c r="I76" s="61"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="73"/>
+      <c r="L76" s="78"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18">
@@ -11251,7 +11223,7 @@
       <c r="H77" s="64"/>
       <c r="I77" s="61"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="73"/>
+      <c r="L77" s="78"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18">
@@ -11266,7 +11238,7 @@
       <c r="H78" s="64"/>
       <c r="I78" s="61"/>
       <c r="K78" s="15"/>
-      <c r="L78" s="73"/>
+      <c r="L78" s="78"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18">
@@ -11281,7 +11253,7 @@
       <c r="H79" s="64"/>
       <c r="I79" s="61"/>
       <c r="K79" s="15"/>
-      <c r="L79" s="73"/>
+      <c r="L79" s="78"/>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18">
@@ -11296,7 +11268,7 @@
       <c r="H80" s="64"/>
       <c r="I80" s="61"/>
       <c r="K80" s="15"/>
-      <c r="L80" s="73"/>
+      <c r="L80" s="78"/>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18">
@@ -11311,7 +11283,7 @@
       <c r="H81" s="64"/>
       <c r="I81" s="61"/>
       <c r="K81" s="15"/>
-      <c r="L81" s="73"/>
+      <c r="L81" s="78"/>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18">
@@ -11326,7 +11298,7 @@
       <c r="H82" s="64"/>
       <c r="I82" s="61"/>
       <c r="K82" s="15"/>
-      <c r="L82" s="73"/>
+      <c r="L82" s="78"/>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18">
@@ -11341,7 +11313,7 @@
       <c r="H83" s="64"/>
       <c r="I83" s="61"/>
       <c r="K83" s="15"/>
-      <c r="L83" s="73"/>
+      <c r="L83" s="78"/>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18">
@@ -11356,7 +11328,7 @@
       <c r="H84" s="64"/>
       <c r="I84" s="61"/>
       <c r="K84" s="15"/>
-      <c r="L84" s="73"/>
+      <c r="L84" s="78"/>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18">
@@ -11371,7 +11343,7 @@
       <c r="H85" s="64"/>
       <c r="I85" s="61"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="73"/>
+      <c r="L85" s="78"/>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18">
@@ -11386,7 +11358,7 @@
       <c r="H86" s="64"/>
       <c r="I86" s="61"/>
       <c r="K86" s="15"/>
-      <c r="L86" s="73"/>
+      <c r="L86" s="78"/>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18">
@@ -11401,7 +11373,7 @@
       <c r="H87" s="64"/>
       <c r="I87" s="61"/>
       <c r="K87" s="15"/>
-      <c r="L87" s="73"/>
+      <c r="L87" s="78"/>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18">
@@ -11416,7 +11388,7 @@
       <c r="H88" s="64"/>
       <c r="I88" s="61"/>
       <c r="K88" s="15"/>
-      <c r="L88" s="73"/>
+      <c r="L88" s="78"/>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="18">
@@ -11431,7 +11403,7 @@
       <c r="H89" s="64"/>
       <c r="I89" s="61"/>
       <c r="K89" s="15"/>
-      <c r="L89" s="73"/>
+      <c r="L89" s="78"/>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18">
@@ -11446,7 +11418,7 @@
       <c r="H90" s="64"/>
       <c r="I90" s="61"/>
       <c r="K90" s="15"/>
-      <c r="L90" s="73"/>
+      <c r="L90" s="78"/>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18">
@@ -11461,7 +11433,7 @@
       <c r="H91" s="64"/>
       <c r="I91" s="61"/>
       <c r="K91" s="15"/>
-      <c r="L91" s="73"/>
+      <c r="L91" s="78"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18">
@@ -11476,7 +11448,7 @@
       <c r="H92" s="64"/>
       <c r="I92" s="61"/>
       <c r="K92" s="15"/>
-      <c r="L92" s="73"/>
+      <c r="L92" s="78"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18">
@@ -11491,7 +11463,7 @@
       <c r="H93" s="64"/>
       <c r="I93" s="61"/>
       <c r="K93" s="15"/>
-      <c r="L93" s="73"/>
+      <c r="L93" s="78"/>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18">
@@ -11506,7 +11478,7 @@
       <c r="H94" s="64"/>
       <c r="I94" s="61"/>
       <c r="K94" s="15"/>
-      <c r="L94" s="73"/>
+      <c r="L94" s="78"/>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18">
@@ -11521,7 +11493,7 @@
       <c r="H95" s="64"/>
       <c r="I95" s="61"/>
       <c r="K95" s="15"/>
-      <c r="L95" s="73"/>
+      <c r="L95" s="78"/>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18">
@@ -11536,7 +11508,7 @@
       <c r="H96" s="64"/>
       <c r="I96" s="61"/>
       <c r="K96" s="15"/>
-      <c r="L96" s="73"/>
+      <c r="L96" s="78"/>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="18">
@@ -11551,7 +11523,7 @@
       <c r="H97" s="64"/>
       <c r="I97" s="61"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="73"/>
+      <c r="L97" s="78"/>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="18">
@@ -11566,7 +11538,7 @@
       <c r="H98" s="64"/>
       <c r="I98" s="61"/>
       <c r="K98" s="15"/>
-      <c r="L98" s="73"/>
+      <c r="L98" s="78"/>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="18">
@@ -11581,7 +11553,7 @@
       <c r="H99" s="64"/>
       <c r="I99" s="61"/>
       <c r="K99" s="15"/>
-      <c r="L99" s="73"/>
+      <c r="L99" s="78"/>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="18">
@@ -11596,7 +11568,7 @@
       <c r="H100" s="64"/>
       <c r="I100" s="61"/>
       <c r="K100" s="15"/>
-      <c r="L100" s="73"/>
+      <c r="L100" s="78"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A101" s="18">
@@ -11611,7 +11583,7 @@
       <c r="H101" s="64"/>
       <c r="I101" s="61"/>
       <c r="K101" s="15"/>
-      <c r="L101" s="73"/>
+      <c r="L101" s="78"/>
     </row>
     <row r="102" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="18">
@@ -11626,7 +11598,7 @@
       <c r="H102" s="65"/>
       <c r="I102" s="62"/>
       <c r="K102" s="16"/>
-      <c r="L102" s="74"/>
+      <c r="L102" s="78"/>
     </row>
     <row r="103" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="51" t="s">
@@ -11684,16 +11656,16 @@
   <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="75" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="75" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="75" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="75" customWidth="1"/>
-    <col min="8" max="9" width="10.625" style="75" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="75" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="75" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="72" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="72" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="72" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="72" customWidth="1"/>
+    <col min="8" max="9" width="10.625" style="72" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -11709,7 +11681,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
@@ -11754,9 +11726,7 @@
       <c r="K2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="72" t="s">
-        <v>25</v>
-      </c>
+      <c r="L2" s="77"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="18">
@@ -11771,7 +11741,7 @@
       <c r="H3" s="63"/>
       <c r="I3" s="61"/>
       <c r="K3" s="15"/>
-      <c r="L3" s="73"/>
+      <c r="L3" s="78"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18">
@@ -11786,7 +11756,7 @@
       <c r="H4" s="64"/>
       <c r="I4" s="61"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="73"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18">
@@ -11801,7 +11771,7 @@
       <c r="H5" s="64"/>
       <c r="I5" s="61"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="73"/>
+      <c r="L5" s="78"/>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18">
@@ -11816,7 +11786,7 @@
       <c r="H6" s="64"/>
       <c r="I6" s="61"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="73"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18">
@@ -11831,7 +11801,7 @@
       <c r="H7" s="64"/>
       <c r="I7" s="61"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="73"/>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18">
@@ -11846,7 +11816,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="61"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="73"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18">
@@ -11861,7 +11831,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="61"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="73"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18">
@@ -11876,7 +11846,7 @@
       <c r="H10" s="64"/>
       <c r="I10" s="61"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="73"/>
+      <c r="L10" s="78"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18">
@@ -11891,7 +11861,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="61"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="73"/>
+      <c r="L11" s="78"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18">
@@ -11906,7 +11876,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="61"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="73"/>
+      <c r="L12" s="78"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="18">
@@ -11921,7 +11891,7 @@
       <c r="H13" s="64"/>
       <c r="I13" s="61"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="73"/>
+      <c r="L13" s="78"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18">
@@ -11936,7 +11906,7 @@
       <c r="H14" s="64"/>
       <c r="I14" s="61"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="73"/>
+      <c r="L14" s="78"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18">
@@ -11951,7 +11921,7 @@
       <c r="H15" s="64"/>
       <c r="I15" s="61"/>
       <c r="K15" s="15"/>
-      <c r="L15" s="73"/>
+      <c r="L15" s="78"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18">
@@ -11966,7 +11936,7 @@
       <c r="H16" s="64"/>
       <c r="I16" s="61"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="73"/>
+      <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18">
@@ -11981,7 +11951,7 @@
       <c r="H17" s="64"/>
       <c r="I17" s="61"/>
       <c r="K17" s="15"/>
-      <c r="L17" s="73"/>
+      <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18">
@@ -11996,7 +11966,7 @@
       <c r="H18" s="64"/>
       <c r="I18" s="61"/>
       <c r="K18" s="15"/>
-      <c r="L18" s="73"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18">
@@ -12011,7 +11981,7 @@
       <c r="H19" s="64"/>
       <c r="I19" s="61"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="73"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18">
@@ -12026,7 +11996,7 @@
       <c r="H20" s="64"/>
       <c r="I20" s="61"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="73"/>
+      <c r="L20" s="78"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18">
@@ -12041,7 +12011,7 @@
       <c r="H21" s="64"/>
       <c r="I21" s="61"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="73"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18">
@@ -12056,7 +12026,7 @@
       <c r="H22" s="64"/>
       <c r="I22" s="61"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="73"/>
+      <c r="L22" s="78"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18">
@@ -12071,7 +12041,7 @@
       <c r="H23" s="64"/>
       <c r="I23" s="61"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="73"/>
+      <c r="L23" s="78"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18">
@@ -12086,7 +12056,7 @@
       <c r="H24" s="64"/>
       <c r="I24" s="61"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="73"/>
+      <c r="L24" s="78"/>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18">
@@ -12101,7 +12071,7 @@
       <c r="H25" s="64"/>
       <c r="I25" s="61"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="73"/>
+      <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18">
@@ -12116,7 +12086,7 @@
       <c r="H26" s="64"/>
       <c r="I26" s="61"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="73"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="18">
@@ -12131,7 +12101,7 @@
       <c r="H27" s="64"/>
       <c r="I27" s="61"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="73"/>
+      <c r="L27" s="78"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18">
@@ -12146,7 +12116,7 @@
       <c r="H28" s="64"/>
       <c r="I28" s="61"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="73"/>
+      <c r="L28" s="78"/>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18">
@@ -12161,7 +12131,7 @@
       <c r="H29" s="64"/>
       <c r="I29" s="61"/>
       <c r="K29" s="15"/>
-      <c r="L29" s="73"/>
+      <c r="L29" s="78"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18">
@@ -12176,7 +12146,7 @@
       <c r="H30" s="64"/>
       <c r="I30" s="61"/>
       <c r="K30" s="15"/>
-      <c r="L30" s="73"/>
+      <c r="L30" s="78"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18">
@@ -12191,7 +12161,7 @@
       <c r="H31" s="64"/>
       <c r="I31" s="61"/>
       <c r="K31" s="15"/>
-      <c r="L31" s="73"/>
+      <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18">
@@ -12206,7 +12176,7 @@
       <c r="H32" s="64"/>
       <c r="I32" s="61"/>
       <c r="K32" s="15"/>
-      <c r="L32" s="73"/>
+      <c r="L32" s="78"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18">
@@ -12221,7 +12191,7 @@
       <c r="H33" s="64"/>
       <c r="I33" s="61"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="73"/>
+      <c r="L33" s="78"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18">
@@ -12236,7 +12206,7 @@
       <c r="H34" s="64"/>
       <c r="I34" s="61"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="73"/>
+      <c r="L34" s="78"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18">
@@ -12251,7 +12221,7 @@
       <c r="H35" s="64"/>
       <c r="I35" s="61"/>
       <c r="K35" s="15"/>
-      <c r="L35" s="73"/>
+      <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18">
@@ -12266,7 +12236,7 @@
       <c r="H36" s="64"/>
       <c r="I36" s="61"/>
       <c r="K36" s="15"/>
-      <c r="L36" s="73"/>
+      <c r="L36" s="78"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18">
@@ -12281,7 +12251,7 @@
       <c r="H37" s="64"/>
       <c r="I37" s="61"/>
       <c r="K37" s="15"/>
-      <c r="L37" s="73"/>
+      <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18">
@@ -12296,7 +12266,7 @@
       <c r="H38" s="64"/>
       <c r="I38" s="61"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="78"/>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18">
@@ -12311,7 +12281,7 @@
       <c r="H39" s="64"/>
       <c r="I39" s="61"/>
       <c r="K39" s="15"/>
-      <c r="L39" s="73"/>
+      <c r="L39" s="78"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18">
@@ -12326,7 +12296,7 @@
       <c r="H40" s="64"/>
       <c r="I40" s="61"/>
       <c r="K40" s="15"/>
-      <c r="L40" s="73"/>
+      <c r="L40" s="78"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18">
@@ -12341,7 +12311,7 @@
       <c r="H41" s="64"/>
       <c r="I41" s="61"/>
       <c r="K41" s="15"/>
-      <c r="L41" s="73"/>
+      <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18">
@@ -12356,7 +12326,7 @@
       <c r="H42" s="64"/>
       <c r="I42" s="61"/>
       <c r="K42" s="15"/>
-      <c r="L42" s="73"/>
+      <c r="L42" s="78"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18">
@@ -12371,7 +12341,7 @@
       <c r="H43" s="64"/>
       <c r="I43" s="61"/>
       <c r="K43" s="15"/>
-      <c r="L43" s="73"/>
+      <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18">
@@ -12386,7 +12356,7 @@
       <c r="H44" s="64"/>
       <c r="I44" s="61"/>
       <c r="K44" s="15"/>
-      <c r="L44" s="73"/>
+      <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18">
@@ -12401,7 +12371,7 @@
       <c r="H45" s="64"/>
       <c r="I45" s="61"/>
       <c r="K45" s="15"/>
-      <c r="L45" s="73"/>
+      <c r="L45" s="78"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18">
@@ -12416,7 +12386,7 @@
       <c r="H46" s="64"/>
       <c r="I46" s="61"/>
       <c r="K46" s="15"/>
-      <c r="L46" s="73"/>
+      <c r="L46" s="78"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18">
@@ -12431,7 +12401,7 @@
       <c r="H47" s="64"/>
       <c r="I47" s="61"/>
       <c r="K47" s="15"/>
-      <c r="L47" s="73"/>
+      <c r="L47" s="78"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18">
@@ -12446,7 +12416,7 @@
       <c r="H48" s="64"/>
       <c r="I48" s="61"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="73"/>
+      <c r="L48" s="78"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18">
@@ -12461,7 +12431,7 @@
       <c r="H49" s="64"/>
       <c r="I49" s="61"/>
       <c r="K49" s="15"/>
-      <c r="L49" s="73"/>
+      <c r="L49" s="78"/>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18">
@@ -12476,7 +12446,7 @@
       <c r="H50" s="64"/>
       <c r="I50" s="61"/>
       <c r="K50" s="15"/>
-      <c r="L50" s="73"/>
+      <c r="L50" s="78"/>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18">
@@ -12491,7 +12461,7 @@
       <c r="H51" s="64"/>
       <c r="I51" s="61"/>
       <c r="K51" s="15"/>
-      <c r="L51" s="73"/>
+      <c r="L51" s="78"/>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18">
@@ -12506,7 +12476,7 @@
       <c r="H52" s="64"/>
       <c r="I52" s="61"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="73"/>
+      <c r="L52" s="78"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="18">
@@ -12521,7 +12491,7 @@
       <c r="H53" s="64"/>
       <c r="I53" s="61"/>
       <c r="K53" s="15"/>
-      <c r="L53" s="73"/>
+      <c r="L53" s="78"/>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18">
@@ -12536,7 +12506,7 @@
       <c r="H54" s="64"/>
       <c r="I54" s="61"/>
       <c r="K54" s="15"/>
-      <c r="L54" s="73"/>
+      <c r="L54" s="78"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18">
@@ -12551,7 +12521,7 @@
       <c r="H55" s="64"/>
       <c r="I55" s="61"/>
       <c r="K55" s="15"/>
-      <c r="L55" s="73"/>
+      <c r="L55" s="78"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18">
@@ -12566,7 +12536,7 @@
       <c r="H56" s="64"/>
       <c r="I56" s="61"/>
       <c r="K56" s="15"/>
-      <c r="L56" s="73"/>
+      <c r="L56" s="78"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18">
@@ -12581,7 +12551,7 @@
       <c r="H57" s="64"/>
       <c r="I57" s="61"/>
       <c r="K57" s="15"/>
-      <c r="L57" s="73"/>
+      <c r="L57" s="78"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18">
@@ -12596,7 +12566,7 @@
       <c r="H58" s="64"/>
       <c r="I58" s="61"/>
       <c r="K58" s="15"/>
-      <c r="L58" s="73"/>
+      <c r="L58" s="78"/>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18">
@@ -12611,7 +12581,7 @@
       <c r="H59" s="64"/>
       <c r="I59" s="61"/>
       <c r="K59" s="15"/>
-      <c r="L59" s="73"/>
+      <c r="L59" s="78"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18">
@@ -12626,7 +12596,7 @@
       <c r="H60" s="64"/>
       <c r="I60" s="61"/>
       <c r="K60" s="15"/>
-      <c r="L60" s="73"/>
+      <c r="L60" s="78"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18">
@@ -12641,7 +12611,7 @@
       <c r="H61" s="64"/>
       <c r="I61" s="61"/>
       <c r="K61" s="15"/>
-      <c r="L61" s="73"/>
+      <c r="L61" s="78"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="18">
@@ -12656,7 +12626,7 @@
       <c r="H62" s="64"/>
       <c r="I62" s="61"/>
       <c r="K62" s="15"/>
-      <c r="L62" s="73"/>
+      <c r="L62" s="78"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18">
@@ -12671,7 +12641,7 @@
       <c r="H63" s="64"/>
       <c r="I63" s="61"/>
       <c r="K63" s="15"/>
-      <c r="L63" s="73"/>
+      <c r="L63" s="78"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18">
@@ -12686,7 +12656,7 @@
       <c r="H64" s="64"/>
       <c r="I64" s="61"/>
       <c r="K64" s="15"/>
-      <c r="L64" s="73"/>
+      <c r="L64" s="78"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18">
@@ -12701,7 +12671,7 @@
       <c r="H65" s="64"/>
       <c r="I65" s="61"/>
       <c r="K65" s="15"/>
-      <c r="L65" s="73"/>
+      <c r="L65" s="78"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18">
@@ -12716,7 +12686,7 @@
       <c r="H66" s="64"/>
       <c r="I66" s="61"/>
       <c r="K66" s="15"/>
-      <c r="L66" s="73"/>
+      <c r="L66" s="78"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18">
@@ -12731,7 +12701,7 @@
       <c r="H67" s="64"/>
       <c r="I67" s="61"/>
       <c r="K67" s="15"/>
-      <c r="L67" s="73"/>
+      <c r="L67" s="78"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18">
@@ -12746,7 +12716,7 @@
       <c r="H68" s="64"/>
       <c r="I68" s="61"/>
       <c r="K68" s="15"/>
-      <c r="L68" s="73"/>
+      <c r="L68" s="78"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18">
@@ -12761,7 +12731,7 @@
       <c r="H69" s="64"/>
       <c r="I69" s="61"/>
       <c r="K69" s="15"/>
-      <c r="L69" s="73"/>
+      <c r="L69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18">
@@ -12776,7 +12746,7 @@
       <c r="H70" s="64"/>
       <c r="I70" s="61"/>
       <c r="K70" s="15"/>
-      <c r="L70" s="73"/>
+      <c r="L70" s="78"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18">
@@ -12791,7 +12761,7 @@
       <c r="H71" s="64"/>
       <c r="I71" s="61"/>
       <c r="K71" s="15"/>
-      <c r="L71" s="73"/>
+      <c r="L71" s="78"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18">
@@ -12806,7 +12776,7 @@
       <c r="H72" s="64"/>
       <c r="I72" s="61"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="73"/>
+      <c r="L72" s="78"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18">
@@ -12821,7 +12791,7 @@
       <c r="H73" s="64"/>
       <c r="I73" s="61"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="73"/>
+      <c r="L73" s="78"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18">
@@ -12836,7 +12806,7 @@
       <c r="H74" s="64"/>
       <c r="I74" s="61"/>
       <c r="K74" s="15"/>
-      <c r="L74" s="73"/>
+      <c r="L74" s="78"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18">
@@ -12851,7 +12821,7 @@
       <c r="H75" s="64"/>
       <c r="I75" s="61"/>
       <c r="K75" s="15"/>
-      <c r="L75" s="73"/>
+      <c r="L75" s="78"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="18">
@@ -12866,7 +12836,7 @@
       <c r="H76" s="64"/>
       <c r="I76" s="61"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="73"/>
+      <c r="L76" s="78"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18">
@@ -12881,7 +12851,7 @@
       <c r="H77" s="64"/>
       <c r="I77" s="61"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="73"/>
+      <c r="L77" s="78"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18">
@@ -12896,7 +12866,7 @@
       <c r="H78" s="64"/>
       <c r="I78" s="61"/>
       <c r="K78" s="15"/>
-      <c r="L78" s="73"/>
+      <c r="L78" s="78"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18">
@@ -12911,7 +12881,7 @@
       <c r="H79" s="64"/>
       <c r="I79" s="61"/>
       <c r="K79" s="15"/>
-      <c r="L79" s="73"/>
+      <c r="L79" s="78"/>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18">
@@ -12926,7 +12896,7 @@
       <c r="H80" s="64"/>
       <c r="I80" s="61"/>
       <c r="K80" s="15"/>
-      <c r="L80" s="73"/>
+      <c r="L80" s="78"/>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18">
@@ -12941,7 +12911,7 @@
       <c r="H81" s="64"/>
       <c r="I81" s="61"/>
       <c r="K81" s="15"/>
-      <c r="L81" s="73"/>
+      <c r="L81" s="78"/>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18">
@@ -12956,7 +12926,7 @@
       <c r="H82" s="64"/>
       <c r="I82" s="61"/>
       <c r="K82" s="15"/>
-      <c r="L82" s="73"/>
+      <c r="L82" s="78"/>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18">
@@ -12971,7 +12941,7 @@
       <c r="H83" s="64"/>
       <c r="I83" s="61"/>
       <c r="K83" s="15"/>
-      <c r="L83" s="73"/>
+      <c r="L83" s="78"/>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18">
@@ -12986,7 +12956,7 @@
       <c r="H84" s="64"/>
       <c r="I84" s="61"/>
       <c r="K84" s="15"/>
-      <c r="L84" s="73"/>
+      <c r="L84" s="78"/>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18">
@@ -13001,7 +12971,7 @@
       <c r="H85" s="64"/>
       <c r="I85" s="61"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="73"/>
+      <c r="L85" s="78"/>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18">
@@ -13016,7 +12986,7 @@
       <c r="H86" s="64"/>
       <c r="I86" s="61"/>
       <c r="K86" s="15"/>
-      <c r="L86" s="73"/>
+      <c r="L86" s="78"/>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18">
@@ -13031,7 +13001,7 @@
       <c r="H87" s="64"/>
       <c r="I87" s="61"/>
       <c r="K87" s="15"/>
-      <c r="L87" s="73"/>
+      <c r="L87" s="78"/>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18">
@@ -13046,7 +13016,7 @@
       <c r="H88" s="64"/>
       <c r="I88" s="61"/>
       <c r="K88" s="15"/>
-      <c r="L88" s="73"/>
+      <c r="L88" s="78"/>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="18">
@@ -13061,7 +13031,7 @@
       <c r="H89" s="64"/>
       <c r="I89" s="61"/>
       <c r="K89" s="15"/>
-      <c r="L89" s="73"/>
+      <c r="L89" s="78"/>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18">
@@ -13076,7 +13046,7 @@
       <c r="H90" s="64"/>
       <c r="I90" s="61"/>
       <c r="K90" s="15"/>
-      <c r="L90" s="73"/>
+      <c r="L90" s="78"/>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18">
@@ -13091,7 +13061,7 @@
       <c r="H91" s="64"/>
       <c r="I91" s="61"/>
       <c r="K91" s="15"/>
-      <c r="L91" s="73"/>
+      <c r="L91" s="78"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18">
@@ -13106,7 +13076,7 @@
       <c r="H92" s="64"/>
       <c r="I92" s="61"/>
       <c r="K92" s="15"/>
-      <c r="L92" s="73"/>
+      <c r="L92" s="78"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18">
@@ -13121,7 +13091,7 @@
       <c r="H93" s="64"/>
       <c r="I93" s="61"/>
       <c r="K93" s="15"/>
-      <c r="L93" s="73"/>
+      <c r="L93" s="78"/>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18">
@@ -13136,7 +13106,7 @@
       <c r="H94" s="64"/>
       <c r="I94" s="61"/>
       <c r="K94" s="15"/>
-      <c r="L94" s="73"/>
+      <c r="L94" s="78"/>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18">
@@ -13151,7 +13121,7 @@
       <c r="H95" s="64"/>
       <c r="I95" s="61"/>
       <c r="K95" s="15"/>
-      <c r="L95" s="73"/>
+      <c r="L95" s="78"/>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18">
@@ -13166,7 +13136,7 @@
       <c r="H96" s="64"/>
       <c r="I96" s="61"/>
       <c r="K96" s="15"/>
-      <c r="L96" s="73"/>
+      <c r="L96" s="78"/>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="18">
@@ -13181,7 +13151,7 @@
       <c r="H97" s="64"/>
       <c r="I97" s="61"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="73"/>
+      <c r="L97" s="78"/>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="18">
@@ -13196,7 +13166,7 @@
       <c r="H98" s="64"/>
       <c r="I98" s="61"/>
       <c r="K98" s="15"/>
-      <c r="L98" s="73"/>
+      <c r="L98" s="78"/>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="18">
@@ -13211,7 +13181,7 @@
       <c r="H99" s="64"/>
       <c r="I99" s="61"/>
       <c r="K99" s="15"/>
-      <c r="L99" s="73"/>
+      <c r="L99" s="78"/>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="18">
@@ -13226,7 +13196,7 @@
       <c r="H100" s="64"/>
       <c r="I100" s="61"/>
       <c r="K100" s="15"/>
-      <c r="L100" s="73"/>
+      <c r="L100" s="78"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A101" s="18">
@@ -13241,7 +13211,7 @@
       <c r="H101" s="64"/>
       <c r="I101" s="61"/>
       <c r="K101" s="15"/>
-      <c r="L101" s="73"/>
+      <c r="L101" s="78"/>
     </row>
     <row r="102" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="18">
@@ -13256,7 +13226,7 @@
       <c r="H102" s="65"/>
       <c r="I102" s="62"/>
       <c r="K102" s="16"/>
-      <c r="L102" s="74"/>
+      <c r="L102" s="78"/>
     </row>
     <row r="103" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="51" t="s">
@@ -13314,16 +13284,16 @@
   <dimension ref="A1:L104"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="75" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="75" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="75" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="75" customWidth="1"/>
-    <col min="8" max="9" width="10.625" style="75" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="75" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="75" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="72" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="72" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="72" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="72" customWidth="1"/>
+    <col min="8" max="9" width="10.625" style="72" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -13339,7 +13309,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
@@ -13384,9 +13354,7 @@
       <c r="K2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="72" t="s">
-        <v>25</v>
-      </c>
+      <c r="L2" s="77"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="18">
@@ -13401,7 +13369,7 @@
       <c r="H3" s="63"/>
       <c r="I3" s="61"/>
       <c r="K3" s="15"/>
-      <c r="L3" s="73"/>
+      <c r="L3" s="78"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18">
@@ -13416,7 +13384,7 @@
       <c r="H4" s="64"/>
       <c r="I4" s="61"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="73"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18">
@@ -13431,7 +13399,7 @@
       <c r="H5" s="64"/>
       <c r="I5" s="61"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="73"/>
+      <c r="L5" s="78"/>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18">
@@ -13446,7 +13414,7 @@
       <c r="H6" s="64"/>
       <c r="I6" s="61"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="73"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18">
@@ -13461,7 +13429,7 @@
       <c r="H7" s="64"/>
       <c r="I7" s="61"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="73"/>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18">
@@ -13476,7 +13444,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="61"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="73"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18">
@@ -13491,7 +13459,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="61"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="73"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18">
@@ -13506,7 +13474,7 @@
       <c r="H10" s="64"/>
       <c r="I10" s="61"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="73"/>
+      <c r="L10" s="78"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18">
@@ -13521,7 +13489,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="61"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="73"/>
+      <c r="L11" s="78"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18">
@@ -13536,7 +13504,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="61"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="73"/>
+      <c r="L12" s="78"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="18">
@@ -13551,7 +13519,7 @@
       <c r="H13" s="64"/>
       <c r="I13" s="61"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="73"/>
+      <c r="L13" s="78"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18">
@@ -13566,7 +13534,7 @@
       <c r="H14" s="64"/>
       <c r="I14" s="61"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="73"/>
+      <c r="L14" s="78"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18">
@@ -13581,7 +13549,7 @@
       <c r="H15" s="64"/>
       <c r="I15" s="61"/>
       <c r="K15" s="15"/>
-      <c r="L15" s="73"/>
+      <c r="L15" s="78"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18">
@@ -13596,7 +13564,7 @@
       <c r="H16" s="64"/>
       <c r="I16" s="61"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="73"/>
+      <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18">
@@ -13611,7 +13579,7 @@
       <c r="H17" s="64"/>
       <c r="I17" s="61"/>
       <c r="K17" s="15"/>
-      <c r="L17" s="73"/>
+      <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18">
@@ -13626,7 +13594,7 @@
       <c r="H18" s="64"/>
       <c r="I18" s="61"/>
       <c r="K18" s="15"/>
-      <c r="L18" s="73"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18">
@@ -13641,7 +13609,7 @@
       <c r="H19" s="64"/>
       <c r="I19" s="61"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="73"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18">
@@ -13656,7 +13624,7 @@
       <c r="H20" s="64"/>
       <c r="I20" s="61"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="73"/>
+      <c r="L20" s="78"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18">
@@ -13671,7 +13639,7 @@
       <c r="H21" s="64"/>
       <c r="I21" s="61"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="73"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18">
@@ -13686,7 +13654,7 @@
       <c r="H22" s="64"/>
       <c r="I22" s="61"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="73"/>
+      <c r="L22" s="78"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18">
@@ -13701,7 +13669,7 @@
       <c r="H23" s="64"/>
       <c r="I23" s="61"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="73"/>
+      <c r="L23" s="78"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18">
@@ -13716,7 +13684,7 @@
       <c r="H24" s="64"/>
       <c r="I24" s="61"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="73"/>
+      <c r="L24" s="78"/>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18">
@@ -13731,7 +13699,7 @@
       <c r="H25" s="64"/>
       <c r="I25" s="61"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="73"/>
+      <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18">
@@ -13746,7 +13714,7 @@
       <c r="H26" s="64"/>
       <c r="I26" s="61"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="73"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="18">
@@ -13761,7 +13729,7 @@
       <c r="H27" s="64"/>
       <c r="I27" s="61"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="73"/>
+      <c r="L27" s="78"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18">
@@ -13776,7 +13744,7 @@
       <c r="H28" s="64"/>
       <c r="I28" s="61"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="73"/>
+      <c r="L28" s="78"/>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18">
@@ -13791,7 +13759,7 @@
       <c r="H29" s="64"/>
       <c r="I29" s="61"/>
       <c r="K29" s="15"/>
-      <c r="L29" s="73"/>
+      <c r="L29" s="78"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18">
@@ -13806,7 +13774,7 @@
       <c r="H30" s="64"/>
       <c r="I30" s="61"/>
       <c r="K30" s="15"/>
-      <c r="L30" s="73"/>
+      <c r="L30" s="78"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18">
@@ -13821,7 +13789,7 @@
       <c r="H31" s="64"/>
       <c r="I31" s="61"/>
       <c r="K31" s="15"/>
-      <c r="L31" s="73"/>
+      <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18">
@@ -13836,7 +13804,7 @@
       <c r="H32" s="64"/>
       <c r="I32" s="61"/>
       <c r="K32" s="15"/>
-      <c r="L32" s="73"/>
+      <c r="L32" s="78"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18">
@@ -13851,7 +13819,7 @@
       <c r="H33" s="64"/>
       <c r="I33" s="61"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="73"/>
+      <c r="L33" s="78"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18">
@@ -13866,7 +13834,7 @@
       <c r="H34" s="64"/>
       <c r="I34" s="61"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="73"/>
+      <c r="L34" s="78"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18">
@@ -13881,7 +13849,7 @@
       <c r="H35" s="64"/>
       <c r="I35" s="61"/>
       <c r="K35" s="15"/>
-      <c r="L35" s="73"/>
+      <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18">
@@ -13896,7 +13864,7 @@
       <c r="H36" s="64"/>
       <c r="I36" s="61"/>
       <c r="K36" s="15"/>
-      <c r="L36" s="73"/>
+      <c r="L36" s="78"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18">
@@ -13911,7 +13879,7 @@
       <c r="H37" s="64"/>
       <c r="I37" s="61"/>
       <c r="K37" s="15"/>
-      <c r="L37" s="73"/>
+      <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18">
@@ -13926,7 +13894,7 @@
       <c r="H38" s="64"/>
       <c r="I38" s="61"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="78"/>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18">
@@ -13941,7 +13909,7 @@
       <c r="H39" s="64"/>
       <c r="I39" s="61"/>
       <c r="K39" s="15"/>
-      <c r="L39" s="73"/>
+      <c r="L39" s="78"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18">
@@ -13956,7 +13924,7 @@
       <c r="H40" s="64"/>
       <c r="I40" s="61"/>
       <c r="K40" s="15"/>
-      <c r="L40" s="73"/>
+      <c r="L40" s="78"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18">
@@ -13971,7 +13939,7 @@
       <c r="H41" s="64"/>
       <c r="I41" s="61"/>
       <c r="K41" s="15"/>
-      <c r="L41" s="73"/>
+      <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18">
@@ -13986,7 +13954,7 @@
       <c r="H42" s="64"/>
       <c r="I42" s="61"/>
       <c r="K42" s="15"/>
-      <c r="L42" s="73"/>
+      <c r="L42" s="78"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18">
@@ -14001,7 +13969,7 @@
       <c r="H43" s="64"/>
       <c r="I43" s="61"/>
       <c r="K43" s="15"/>
-      <c r="L43" s="73"/>
+      <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18">
@@ -14016,7 +13984,7 @@
       <c r="H44" s="64"/>
       <c r="I44" s="61"/>
       <c r="K44" s="15"/>
-      <c r="L44" s="73"/>
+      <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18">
@@ -14031,7 +13999,7 @@
       <c r="H45" s="64"/>
       <c r="I45" s="61"/>
       <c r="K45" s="15"/>
-      <c r="L45" s="73"/>
+      <c r="L45" s="78"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18">
@@ -14046,7 +14014,7 @@
       <c r="H46" s="64"/>
       <c r="I46" s="61"/>
       <c r="K46" s="15"/>
-      <c r="L46" s="73"/>
+      <c r="L46" s="78"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18">
@@ -14061,7 +14029,7 @@
       <c r="H47" s="64"/>
       <c r="I47" s="61"/>
       <c r="K47" s="15"/>
-      <c r="L47" s="73"/>
+      <c r="L47" s="78"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18">
@@ -14076,7 +14044,7 @@
       <c r="H48" s="64"/>
       <c r="I48" s="61"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="73"/>
+      <c r="L48" s="78"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18">
@@ -14091,7 +14059,7 @@
       <c r="H49" s="64"/>
       <c r="I49" s="61"/>
       <c r="K49" s="15"/>
-      <c r="L49" s="73"/>
+      <c r="L49" s="78"/>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18">
@@ -14106,7 +14074,7 @@
       <c r="H50" s="64"/>
       <c r="I50" s="61"/>
       <c r="K50" s="15"/>
-      <c r="L50" s="73"/>
+      <c r="L50" s="78"/>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18">
@@ -14121,7 +14089,7 @@
       <c r="H51" s="64"/>
       <c r="I51" s="61"/>
       <c r="K51" s="15"/>
-      <c r="L51" s="73"/>
+      <c r="L51" s="78"/>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18">
@@ -14136,7 +14104,7 @@
       <c r="H52" s="64"/>
       <c r="I52" s="61"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="73"/>
+      <c r="L52" s="78"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="18">
@@ -14151,7 +14119,7 @@
       <c r="H53" s="64"/>
       <c r="I53" s="61"/>
       <c r="K53" s="15"/>
-      <c r="L53" s="73"/>
+      <c r="L53" s="78"/>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18">
@@ -14166,7 +14134,7 @@
       <c r="H54" s="64"/>
       <c r="I54" s="61"/>
       <c r="K54" s="15"/>
-      <c r="L54" s="73"/>
+      <c r="L54" s="78"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18">
@@ -14181,7 +14149,7 @@
       <c r="H55" s="64"/>
       <c r="I55" s="61"/>
       <c r="K55" s="15"/>
-      <c r="L55" s="73"/>
+      <c r="L55" s="78"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18">
@@ -14196,7 +14164,7 @@
       <c r="H56" s="64"/>
       <c r="I56" s="61"/>
       <c r="K56" s="15"/>
-      <c r="L56" s="73"/>
+      <c r="L56" s="78"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18">
@@ -14211,7 +14179,7 @@
       <c r="H57" s="64"/>
       <c r="I57" s="61"/>
       <c r="K57" s="15"/>
-      <c r="L57" s="73"/>
+      <c r="L57" s="78"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18">
@@ -14226,7 +14194,7 @@
       <c r="H58" s="64"/>
       <c r="I58" s="61"/>
       <c r="K58" s="15"/>
-      <c r="L58" s="73"/>
+      <c r="L58" s="78"/>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18">
@@ -14241,7 +14209,7 @@
       <c r="H59" s="64"/>
       <c r="I59" s="61"/>
       <c r="K59" s="15"/>
-      <c r="L59" s="73"/>
+      <c r="L59" s="78"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18">
@@ -14256,7 +14224,7 @@
       <c r="H60" s="64"/>
       <c r="I60" s="61"/>
       <c r="K60" s="15"/>
-      <c r="L60" s="73"/>
+      <c r="L60" s="78"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18">
@@ -14271,7 +14239,7 @@
       <c r="H61" s="64"/>
       <c r="I61" s="61"/>
       <c r="K61" s="15"/>
-      <c r="L61" s="73"/>
+      <c r="L61" s="78"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="18">
@@ -14286,7 +14254,7 @@
       <c r="H62" s="64"/>
       <c r="I62" s="61"/>
       <c r="K62" s="15"/>
-      <c r="L62" s="73"/>
+      <c r="L62" s="78"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18">
@@ -14301,7 +14269,7 @@
       <c r="H63" s="64"/>
       <c r="I63" s="61"/>
       <c r="K63" s="15"/>
-      <c r="L63" s="73"/>
+      <c r="L63" s="78"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18">
@@ -14316,7 +14284,7 @@
       <c r="H64" s="64"/>
       <c r="I64" s="61"/>
       <c r="K64" s="15"/>
-      <c r="L64" s="73"/>
+      <c r="L64" s="78"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18">
@@ -14331,7 +14299,7 @@
       <c r="H65" s="64"/>
       <c r="I65" s="61"/>
       <c r="K65" s="15"/>
-      <c r="L65" s="73"/>
+      <c r="L65" s="78"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18">
@@ -14346,7 +14314,7 @@
       <c r="H66" s="64"/>
       <c r="I66" s="61"/>
       <c r="K66" s="15"/>
-      <c r="L66" s="73"/>
+      <c r="L66" s="78"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18">
@@ -14361,7 +14329,7 @@
       <c r="H67" s="64"/>
       <c r="I67" s="61"/>
       <c r="K67" s="15"/>
-      <c r="L67" s="73"/>
+      <c r="L67" s="78"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18">
@@ -14376,7 +14344,7 @@
       <c r="H68" s="64"/>
       <c r="I68" s="61"/>
       <c r="K68" s="15"/>
-      <c r="L68" s="73"/>
+      <c r="L68" s="78"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18">
@@ -14391,7 +14359,7 @@
       <c r="H69" s="64"/>
       <c r="I69" s="61"/>
       <c r="K69" s="15"/>
-      <c r="L69" s="73"/>
+      <c r="L69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18">
@@ -14406,7 +14374,7 @@
       <c r="H70" s="64"/>
       <c r="I70" s="61"/>
       <c r="K70" s="15"/>
-      <c r="L70" s="73"/>
+      <c r="L70" s="78"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18">
@@ -14421,7 +14389,7 @@
       <c r="H71" s="64"/>
       <c r="I71" s="61"/>
       <c r="K71" s="15"/>
-      <c r="L71" s="73"/>
+      <c r="L71" s="78"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18">
@@ -14436,7 +14404,7 @@
       <c r="H72" s="64"/>
       <c r="I72" s="61"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="73"/>
+      <c r="L72" s="78"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18">
@@ -14451,7 +14419,7 @@
       <c r="H73" s="64"/>
       <c r="I73" s="61"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="73"/>
+      <c r="L73" s="78"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18">
@@ -14466,7 +14434,7 @@
       <c r="H74" s="64"/>
       <c r="I74" s="61"/>
       <c r="K74" s="15"/>
-      <c r="L74" s="73"/>
+      <c r="L74" s="78"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18">
@@ -14481,7 +14449,7 @@
       <c r="H75" s="64"/>
       <c r="I75" s="61"/>
       <c r="K75" s="15"/>
-      <c r="L75" s="73"/>
+      <c r="L75" s="78"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="18">
@@ -14496,7 +14464,7 @@
       <c r="H76" s="64"/>
       <c r="I76" s="61"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="73"/>
+      <c r="L76" s="78"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18">
@@ -14511,7 +14479,7 @@
       <c r="H77" s="64"/>
       <c r="I77" s="61"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="73"/>
+      <c r="L77" s="78"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18">
@@ -14526,7 +14494,7 @@
       <c r="H78" s="64"/>
       <c r="I78" s="61"/>
       <c r="K78" s="15"/>
-      <c r="L78" s="73"/>
+      <c r="L78" s="78"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18">
@@ -14541,7 +14509,7 @@
       <c r="H79" s="64"/>
       <c r="I79" s="61"/>
       <c r="K79" s="15"/>
-      <c r="L79" s="73"/>
+      <c r="L79" s="78"/>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18">
@@ -14556,7 +14524,7 @@
       <c r="H80" s="64"/>
       <c r="I80" s="61"/>
       <c r="K80" s="15"/>
-      <c r="L80" s="73"/>
+      <c r="L80" s="78"/>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18">
@@ -14571,7 +14539,7 @@
       <c r="H81" s="64"/>
       <c r="I81" s="61"/>
       <c r="K81" s="15"/>
-      <c r="L81" s="73"/>
+      <c r="L81" s="78"/>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18">
@@ -14586,7 +14554,7 @@
       <c r="H82" s="64"/>
       <c r="I82" s="61"/>
       <c r="K82" s="15"/>
-      <c r="L82" s="73"/>
+      <c r="L82" s="78"/>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18">
@@ -14601,7 +14569,7 @@
       <c r="H83" s="64"/>
       <c r="I83" s="61"/>
       <c r="K83" s="15"/>
-      <c r="L83" s="73"/>
+      <c r="L83" s="78"/>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18">
@@ -14616,7 +14584,7 @@
       <c r="H84" s="64"/>
       <c r="I84" s="61"/>
       <c r="K84" s="15"/>
-      <c r="L84" s="73"/>
+      <c r="L84" s="78"/>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18">
@@ -14631,7 +14599,7 @@
       <c r="H85" s="64"/>
       <c r="I85" s="61"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="73"/>
+      <c r="L85" s="78"/>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18">
@@ -14646,7 +14614,7 @@
       <c r="H86" s="64"/>
       <c r="I86" s="61"/>
       <c r="K86" s="15"/>
-      <c r="L86" s="73"/>
+      <c r="L86" s="78"/>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18">
@@ -14661,7 +14629,7 @@
       <c r="H87" s="64"/>
       <c r="I87" s="61"/>
       <c r="K87" s="15"/>
-      <c r="L87" s="73"/>
+      <c r="L87" s="78"/>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18">
@@ -14676,7 +14644,7 @@
       <c r="H88" s="64"/>
       <c r="I88" s="61"/>
       <c r="K88" s="15"/>
-      <c r="L88" s="73"/>
+      <c r="L88" s="78"/>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="18">
@@ -14691,7 +14659,7 @@
       <c r="H89" s="64"/>
       <c r="I89" s="61"/>
       <c r="K89" s="15"/>
-      <c r="L89" s="73"/>
+      <c r="L89" s="78"/>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18">
@@ -14706,7 +14674,7 @@
       <c r="H90" s="64"/>
       <c r="I90" s="61"/>
       <c r="K90" s="15"/>
-      <c r="L90" s="73"/>
+      <c r="L90" s="78"/>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18">
@@ -14721,7 +14689,7 @@
       <c r="H91" s="64"/>
       <c r="I91" s="61"/>
       <c r="K91" s="15"/>
-      <c r="L91" s="73"/>
+      <c r="L91" s="78"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18">
@@ -14736,7 +14704,7 @@
       <c r="H92" s="64"/>
       <c r="I92" s="61"/>
       <c r="K92" s="15"/>
-      <c r="L92" s="73"/>
+      <c r="L92" s="78"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18">
@@ -14751,7 +14719,7 @@
       <c r="H93" s="64"/>
       <c r="I93" s="61"/>
       <c r="K93" s="15"/>
-      <c r="L93" s="73"/>
+      <c r="L93" s="78"/>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18">
@@ -14766,7 +14734,7 @@
       <c r="H94" s="64"/>
       <c r="I94" s="61"/>
       <c r="K94" s="15"/>
-      <c r="L94" s="73"/>
+      <c r="L94" s="78"/>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18">
@@ -14781,7 +14749,7 @@
       <c r="H95" s="64"/>
       <c r="I95" s="61"/>
       <c r="K95" s="15"/>
-      <c r="L95" s="73"/>
+      <c r="L95" s="78"/>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18">
@@ -14796,7 +14764,7 @@
       <c r="H96" s="64"/>
       <c r="I96" s="61"/>
       <c r="K96" s="15"/>
-      <c r="L96" s="73"/>
+      <c r="L96" s="78"/>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="18">
@@ -14811,7 +14779,7 @@
       <c r="H97" s="64"/>
       <c r="I97" s="61"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="73"/>
+      <c r="L97" s="78"/>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="18">
@@ -14826,7 +14794,7 @@
       <c r="H98" s="64"/>
       <c r="I98" s="61"/>
       <c r="K98" s="15"/>
-      <c r="L98" s="73"/>
+      <c r="L98" s="78"/>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="18">
@@ -14841,7 +14809,7 @@
       <c r="H99" s="64"/>
       <c r="I99" s="61"/>
       <c r="K99" s="15"/>
-      <c r="L99" s="73"/>
+      <c r="L99" s="78"/>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="18">
@@ -14856,7 +14824,7 @@
       <c r="H100" s="64"/>
       <c r="I100" s="61"/>
       <c r="K100" s="15"/>
-      <c r="L100" s="73"/>
+      <c r="L100" s="78"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A101" s="18">
@@ -14871,7 +14839,7 @@
       <c r="H101" s="64"/>
       <c r="I101" s="61"/>
       <c r="K101" s="15"/>
-      <c r="L101" s="73"/>
+      <c r="L101" s="78"/>
     </row>
     <row r="102" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="18">
@@ -14886,7 +14854,7 @@
       <c r="H102" s="65"/>
       <c r="I102" s="62"/>
       <c r="K102" s="16"/>
-      <c r="L102" s="74"/>
+      <c r="L102" s="78"/>
     </row>
     <row r="103" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="51" t="s">
@@ -14950,16 +14918,16 @@
   <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="75" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="75" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="75" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="75" customWidth="1"/>
-    <col min="8" max="9" width="10.625" style="75" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="75" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="75" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="72" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="72" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="72" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="72" customWidth="1"/>
+    <col min="8" max="9" width="10.625" style="72" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -14975,7 +14943,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
@@ -15020,9 +14988,7 @@
       <c r="K2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="72" t="s">
-        <v>25</v>
-      </c>
+      <c r="L2" s="77"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="18">
@@ -15037,7 +15003,7 @@
       <c r="H3" s="63"/>
       <c r="I3" s="61"/>
       <c r="K3" s="15"/>
-      <c r="L3" s="73"/>
+      <c r="L3" s="78"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18">
@@ -15052,7 +15018,7 @@
       <c r="H4" s="64"/>
       <c r="I4" s="61"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="73"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18">
@@ -15067,7 +15033,7 @@
       <c r="H5" s="64"/>
       <c r="I5" s="61"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="73"/>
+      <c r="L5" s="78"/>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18">
@@ -15082,7 +15048,7 @@
       <c r="H6" s="64"/>
       <c r="I6" s="61"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="73"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18">
@@ -15097,7 +15063,7 @@
       <c r="H7" s="64"/>
       <c r="I7" s="61"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="73"/>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18">
@@ -15112,7 +15078,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="61"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="73"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18">
@@ -15127,7 +15093,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="61"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="73"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18">
@@ -15142,7 +15108,7 @@
       <c r="H10" s="64"/>
       <c r="I10" s="61"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="73"/>
+      <c r="L10" s="78"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18">
@@ -15157,7 +15123,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="61"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="73"/>
+      <c r="L11" s="78"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18">
@@ -15172,7 +15138,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="61"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="73"/>
+      <c r="L12" s="78"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="18">
@@ -15187,7 +15153,7 @@
       <c r="H13" s="64"/>
       <c r="I13" s="61"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="73"/>
+      <c r="L13" s="78"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18">
@@ -15202,7 +15168,7 @@
       <c r="H14" s="64"/>
       <c r="I14" s="61"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="73"/>
+      <c r="L14" s="78"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18">
@@ -15217,7 +15183,7 @@
       <c r="H15" s="64"/>
       <c r="I15" s="61"/>
       <c r="K15" s="15"/>
-      <c r="L15" s="73"/>
+      <c r="L15" s="78"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18">
@@ -15232,7 +15198,7 @@
       <c r="H16" s="64"/>
       <c r="I16" s="61"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="73"/>
+      <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18">
@@ -15247,7 +15213,7 @@
       <c r="H17" s="64"/>
       <c r="I17" s="61"/>
       <c r="K17" s="15"/>
-      <c r="L17" s="73"/>
+      <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18">
@@ -15262,7 +15228,7 @@
       <c r="H18" s="64"/>
       <c r="I18" s="61"/>
       <c r="K18" s="15"/>
-      <c r="L18" s="73"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18">
@@ -15277,7 +15243,7 @@
       <c r="H19" s="64"/>
       <c r="I19" s="61"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="73"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18">
@@ -15292,7 +15258,7 @@
       <c r="H20" s="64"/>
       <c r="I20" s="61"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="73"/>
+      <c r="L20" s="78"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18">
@@ -15307,7 +15273,7 @@
       <c r="H21" s="64"/>
       <c r="I21" s="61"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="73"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18">
@@ -15322,7 +15288,7 @@
       <c r="H22" s="64"/>
       <c r="I22" s="61"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="73"/>
+      <c r="L22" s="78"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18">
@@ -15337,7 +15303,7 @@
       <c r="H23" s="64"/>
       <c r="I23" s="61"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="73"/>
+      <c r="L23" s="78"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18">
@@ -15352,7 +15318,7 @@
       <c r="H24" s="64"/>
       <c r="I24" s="61"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="73"/>
+      <c r="L24" s="78"/>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18">
@@ -15367,7 +15333,7 @@
       <c r="H25" s="64"/>
       <c r="I25" s="61"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="73"/>
+      <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18">
@@ -15382,7 +15348,7 @@
       <c r="H26" s="64"/>
       <c r="I26" s="61"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="73"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="18">
@@ -15397,7 +15363,7 @@
       <c r="H27" s="64"/>
       <c r="I27" s="61"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="73"/>
+      <c r="L27" s="78"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18">
@@ -15412,7 +15378,7 @@
       <c r="H28" s="64"/>
       <c r="I28" s="61"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="73"/>
+      <c r="L28" s="78"/>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18">
@@ -15427,7 +15393,7 @@
       <c r="H29" s="64"/>
       <c r="I29" s="61"/>
       <c r="K29" s="15"/>
-      <c r="L29" s="73"/>
+      <c r="L29" s="78"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18">
@@ -15442,7 +15408,7 @@
       <c r="H30" s="64"/>
       <c r="I30" s="61"/>
       <c r="K30" s="15"/>
-      <c r="L30" s="73"/>
+      <c r="L30" s="78"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18">
@@ -15457,7 +15423,7 @@
       <c r="H31" s="64"/>
       <c r="I31" s="61"/>
       <c r="K31" s="15"/>
-      <c r="L31" s="73"/>
+      <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18">
@@ -15472,7 +15438,7 @@
       <c r="H32" s="64"/>
       <c r="I32" s="61"/>
       <c r="K32" s="15"/>
-      <c r="L32" s="73"/>
+      <c r="L32" s="78"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18">
@@ -15487,7 +15453,7 @@
       <c r="H33" s="64"/>
       <c r="I33" s="61"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="73"/>
+      <c r="L33" s="78"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18">
@@ -15502,7 +15468,7 @@
       <c r="H34" s="64"/>
       <c r="I34" s="61"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="73"/>
+      <c r="L34" s="78"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18">
@@ -15517,7 +15483,7 @@
       <c r="H35" s="64"/>
       <c r="I35" s="61"/>
       <c r="K35" s="15"/>
-      <c r="L35" s="73"/>
+      <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18">
@@ -15532,7 +15498,7 @@
       <c r="H36" s="64"/>
       <c r="I36" s="61"/>
       <c r="K36" s="15"/>
-      <c r="L36" s="73"/>
+      <c r="L36" s="78"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18">
@@ -15547,7 +15513,7 @@
       <c r="H37" s="64"/>
       <c r="I37" s="61"/>
       <c r="K37" s="15"/>
-      <c r="L37" s="73"/>
+      <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18">
@@ -15562,7 +15528,7 @@
       <c r="H38" s="64"/>
       <c r="I38" s="61"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="78"/>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18">
@@ -15577,7 +15543,7 @@
       <c r="H39" s="64"/>
       <c r="I39" s="61"/>
       <c r="K39" s="15"/>
-      <c r="L39" s="73"/>
+      <c r="L39" s="78"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18">
@@ -15592,7 +15558,7 @@
       <c r="H40" s="64"/>
       <c r="I40" s="61"/>
       <c r="K40" s="15"/>
-      <c r="L40" s="73"/>
+      <c r="L40" s="78"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18">
@@ -15607,7 +15573,7 @@
       <c r="H41" s="64"/>
       <c r="I41" s="61"/>
       <c r="K41" s="15"/>
-      <c r="L41" s="73"/>
+      <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18">
@@ -15622,7 +15588,7 @@
       <c r="H42" s="64"/>
       <c r="I42" s="61"/>
       <c r="K42" s="15"/>
-      <c r="L42" s="73"/>
+      <c r="L42" s="78"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18">
@@ -15637,7 +15603,7 @@
       <c r="H43" s="64"/>
       <c r="I43" s="61"/>
       <c r="K43" s="15"/>
-      <c r="L43" s="73"/>
+      <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18">
@@ -15652,7 +15618,7 @@
       <c r="H44" s="64"/>
       <c r="I44" s="61"/>
       <c r="K44" s="15"/>
-      <c r="L44" s="73"/>
+      <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18">
@@ -15667,7 +15633,7 @@
       <c r="H45" s="64"/>
       <c r="I45" s="61"/>
       <c r="K45" s="15"/>
-      <c r="L45" s="73"/>
+      <c r="L45" s="78"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18">
@@ -15682,7 +15648,7 @@
       <c r="H46" s="64"/>
       <c r="I46" s="61"/>
       <c r="K46" s="15"/>
-      <c r="L46" s="73"/>
+      <c r="L46" s="78"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18">
@@ -15697,7 +15663,7 @@
       <c r="H47" s="64"/>
       <c r="I47" s="61"/>
       <c r="K47" s="15"/>
-      <c r="L47" s="73"/>
+      <c r="L47" s="78"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18">
@@ -15712,7 +15678,7 @@
       <c r="H48" s="64"/>
       <c r="I48" s="61"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="73"/>
+      <c r="L48" s="78"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18">
@@ -15727,7 +15693,7 @@
       <c r="H49" s="64"/>
       <c r="I49" s="61"/>
       <c r="K49" s="15"/>
-      <c r="L49" s="73"/>
+      <c r="L49" s="78"/>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18">
@@ -15742,7 +15708,7 @@
       <c r="H50" s="64"/>
       <c r="I50" s="61"/>
       <c r="K50" s="15"/>
-      <c r="L50" s="73"/>
+      <c r="L50" s="78"/>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18">
@@ -15757,7 +15723,7 @@
       <c r="H51" s="64"/>
       <c r="I51" s="61"/>
       <c r="K51" s="15"/>
-      <c r="L51" s="73"/>
+      <c r="L51" s="78"/>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18">
@@ -15772,7 +15738,7 @@
       <c r="H52" s="64"/>
       <c r="I52" s="61"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="73"/>
+      <c r="L52" s="78"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="18">
@@ -15787,7 +15753,7 @@
       <c r="H53" s="64"/>
       <c r="I53" s="61"/>
       <c r="K53" s="15"/>
-      <c r="L53" s="73"/>
+      <c r="L53" s="78"/>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18">
@@ -15802,7 +15768,7 @@
       <c r="H54" s="64"/>
       <c r="I54" s="61"/>
       <c r="K54" s="15"/>
-      <c r="L54" s="73"/>
+      <c r="L54" s="78"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18">
@@ -15817,7 +15783,7 @@
       <c r="H55" s="64"/>
       <c r="I55" s="61"/>
       <c r="K55" s="15"/>
-      <c r="L55" s="73"/>
+      <c r="L55" s="78"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18">
@@ -15832,7 +15798,7 @@
       <c r="H56" s="64"/>
       <c r="I56" s="61"/>
       <c r="K56" s="15"/>
-      <c r="L56" s="73"/>
+      <c r="L56" s="78"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18">
@@ -15847,7 +15813,7 @@
       <c r="H57" s="64"/>
       <c r="I57" s="61"/>
       <c r="K57" s="15"/>
-      <c r="L57" s="73"/>
+      <c r="L57" s="78"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18">
@@ -15862,7 +15828,7 @@
       <c r="H58" s="64"/>
       <c r="I58" s="61"/>
       <c r="K58" s="15"/>
-      <c r="L58" s="73"/>
+      <c r="L58" s="78"/>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18">
@@ -15877,7 +15843,7 @@
       <c r="H59" s="64"/>
       <c r="I59" s="61"/>
       <c r="K59" s="15"/>
-      <c r="L59" s="73"/>
+      <c r="L59" s="78"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18">
@@ -15892,7 +15858,7 @@
       <c r="H60" s="64"/>
       <c r="I60" s="61"/>
       <c r="K60" s="15"/>
-      <c r="L60" s="73"/>
+      <c r="L60" s="78"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18">
@@ -15907,7 +15873,7 @@
       <c r="H61" s="64"/>
       <c r="I61" s="61"/>
       <c r="K61" s="15"/>
-      <c r="L61" s="73"/>
+      <c r="L61" s="78"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="18">
@@ -15922,7 +15888,7 @@
       <c r="H62" s="64"/>
       <c r="I62" s="61"/>
       <c r="K62" s="15"/>
-      <c r="L62" s="73"/>
+      <c r="L62" s="78"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18">
@@ -15937,7 +15903,7 @@
       <c r="H63" s="64"/>
       <c r="I63" s="61"/>
       <c r="K63" s="15"/>
-      <c r="L63" s="73"/>
+      <c r="L63" s="78"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18">
@@ -15952,7 +15918,7 @@
       <c r="H64" s="64"/>
       <c r="I64" s="61"/>
       <c r="K64" s="15"/>
-      <c r="L64" s="73"/>
+      <c r="L64" s="78"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18">
@@ -15967,7 +15933,7 @@
       <c r="H65" s="64"/>
       <c r="I65" s="61"/>
       <c r="K65" s="15"/>
-      <c r="L65" s="73"/>
+      <c r="L65" s="78"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18">
@@ -15982,7 +15948,7 @@
       <c r="H66" s="64"/>
       <c r="I66" s="61"/>
       <c r="K66" s="15"/>
-      <c r="L66" s="73"/>
+      <c r="L66" s="78"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18">
@@ -15997,7 +15963,7 @@
       <c r="H67" s="64"/>
       <c r="I67" s="61"/>
       <c r="K67" s="15"/>
-      <c r="L67" s="73"/>
+      <c r="L67" s="78"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18">
@@ -16012,7 +15978,7 @@
       <c r="H68" s="64"/>
       <c r="I68" s="61"/>
       <c r="K68" s="15"/>
-      <c r="L68" s="73"/>
+      <c r="L68" s="78"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18">
@@ -16027,7 +15993,7 @@
       <c r="H69" s="64"/>
       <c r="I69" s="61"/>
       <c r="K69" s="15"/>
-      <c r="L69" s="73"/>
+      <c r="L69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18">
@@ -16042,7 +16008,7 @@
       <c r="H70" s="64"/>
       <c r="I70" s="61"/>
       <c r="K70" s="15"/>
-      <c r="L70" s="73"/>
+      <c r="L70" s="78"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18">
@@ -16057,7 +16023,7 @@
       <c r="H71" s="64"/>
       <c r="I71" s="61"/>
       <c r="K71" s="15"/>
-      <c r="L71" s="73"/>
+      <c r="L71" s="78"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18">
@@ -16072,7 +16038,7 @@
       <c r="H72" s="64"/>
       <c r="I72" s="61"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="73"/>
+      <c r="L72" s="78"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18">
@@ -16087,7 +16053,7 @@
       <c r="H73" s="64"/>
       <c r="I73" s="61"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="73"/>
+      <c r="L73" s="78"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18">
@@ -16102,7 +16068,7 @@
       <c r="H74" s="64"/>
       <c r="I74" s="61"/>
       <c r="K74" s="15"/>
-      <c r="L74" s="73"/>
+      <c r="L74" s="78"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18">
@@ -16117,7 +16083,7 @@
       <c r="H75" s="64"/>
       <c r="I75" s="61"/>
       <c r="K75" s="15"/>
-      <c r="L75" s="73"/>
+      <c r="L75" s="78"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="18">
@@ -16132,7 +16098,7 @@
       <c r="H76" s="64"/>
       <c r="I76" s="61"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="73"/>
+      <c r="L76" s="78"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18">
@@ -16147,7 +16113,7 @@
       <c r="H77" s="64"/>
       <c r="I77" s="61"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="73"/>
+      <c r="L77" s="78"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18">
@@ -16162,7 +16128,7 @@
       <c r="H78" s="64"/>
       <c r="I78" s="61"/>
       <c r="K78" s="15"/>
-      <c r="L78" s="73"/>
+      <c r="L78" s="78"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18">
@@ -16177,7 +16143,7 @@
       <c r="H79" s="64"/>
       <c r="I79" s="61"/>
       <c r="K79" s="15"/>
-      <c r="L79" s="73"/>
+      <c r="L79" s="78"/>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18">
@@ -16192,7 +16158,7 @@
       <c r="H80" s="64"/>
       <c r="I80" s="61"/>
       <c r="K80" s="15"/>
-      <c r="L80" s="73"/>
+      <c r="L80" s="78"/>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18">
@@ -16207,7 +16173,7 @@
       <c r="H81" s="64"/>
       <c r="I81" s="61"/>
       <c r="K81" s="15"/>
-      <c r="L81" s="73"/>
+      <c r="L81" s="78"/>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18">
@@ -16222,7 +16188,7 @@
       <c r="H82" s="64"/>
       <c r="I82" s="61"/>
       <c r="K82" s="15"/>
-      <c r="L82" s="73"/>
+      <c r="L82" s="78"/>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18">
@@ -16237,7 +16203,7 @@
       <c r="H83" s="64"/>
       <c r="I83" s="61"/>
       <c r="K83" s="15"/>
-      <c r="L83" s="73"/>
+      <c r="L83" s="78"/>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18">
@@ -16252,7 +16218,7 @@
       <c r="H84" s="64"/>
       <c r="I84" s="61"/>
       <c r="K84" s="15"/>
-      <c r="L84" s="73"/>
+      <c r="L84" s="78"/>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18">
@@ -16267,7 +16233,7 @@
       <c r="H85" s="64"/>
       <c r="I85" s="61"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="73"/>
+      <c r="L85" s="78"/>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18">
@@ -16282,7 +16248,7 @@
       <c r="H86" s="64"/>
       <c r="I86" s="61"/>
       <c r="K86" s="15"/>
-      <c r="L86" s="73"/>
+      <c r="L86" s="78"/>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18">
@@ -16297,7 +16263,7 @@
       <c r="H87" s="64"/>
       <c r="I87" s="61"/>
       <c r="K87" s="15"/>
-      <c r="L87" s="73"/>
+      <c r="L87" s="78"/>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18">
@@ -16312,7 +16278,7 @@
       <c r="H88" s="64"/>
       <c r="I88" s="61"/>
       <c r="K88" s="15"/>
-      <c r="L88" s="73"/>
+      <c r="L88" s="78"/>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="18">
@@ -16327,7 +16293,7 @@
       <c r="H89" s="64"/>
       <c r="I89" s="61"/>
       <c r="K89" s="15"/>
-      <c r="L89" s="73"/>
+      <c r="L89" s="78"/>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18">
@@ -16342,7 +16308,7 @@
       <c r="H90" s="64"/>
       <c r="I90" s="61"/>
       <c r="K90" s="15"/>
-      <c r="L90" s="73"/>
+      <c r="L90" s="78"/>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18">
@@ -16357,7 +16323,7 @@
       <c r="H91" s="64"/>
       <c r="I91" s="61"/>
       <c r="K91" s="15"/>
-      <c r="L91" s="73"/>
+      <c r="L91" s="78"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18">
@@ -16372,7 +16338,7 @@
       <c r="H92" s="64"/>
       <c r="I92" s="61"/>
       <c r="K92" s="15"/>
-      <c r="L92" s="73"/>
+      <c r="L92" s="78"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18">
@@ -16387,7 +16353,7 @@
       <c r="H93" s="64"/>
       <c r="I93" s="61"/>
       <c r="K93" s="15"/>
-      <c r="L93" s="73"/>
+      <c r="L93" s="78"/>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18">
@@ -16402,7 +16368,7 @@
       <c r="H94" s="64"/>
       <c r="I94" s="61"/>
       <c r="K94" s="15"/>
-      <c r="L94" s="73"/>
+      <c r="L94" s="78"/>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18">
@@ -16417,7 +16383,7 @@
       <c r="H95" s="64"/>
       <c r="I95" s="61"/>
       <c r="K95" s="15"/>
-      <c r="L95" s="73"/>
+      <c r="L95" s="78"/>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18">
@@ -16432,7 +16398,7 @@
       <c r="H96" s="64"/>
       <c r="I96" s="61"/>
       <c r="K96" s="15"/>
-      <c r="L96" s="73"/>
+      <c r="L96" s="78"/>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="18">
@@ -16447,7 +16413,7 @@
       <c r="H97" s="64"/>
       <c r="I97" s="61"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="73"/>
+      <c r="L97" s="78"/>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="18">
@@ -16462,7 +16428,7 @@
       <c r="H98" s="64"/>
       <c r="I98" s="61"/>
       <c r="K98" s="15"/>
-      <c r="L98" s="73"/>
+      <c r="L98" s="78"/>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="18">
@@ -16477,7 +16443,7 @@
       <c r="H99" s="64"/>
       <c r="I99" s="61"/>
       <c r="K99" s="15"/>
-      <c r="L99" s="73"/>
+      <c r="L99" s="78"/>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="18">
@@ -16492,7 +16458,7 @@
       <c r="H100" s="64"/>
       <c r="I100" s="61"/>
       <c r="K100" s="15"/>
-      <c r="L100" s="73"/>
+      <c r="L100" s="78"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A101" s="18">
@@ -16507,7 +16473,7 @@
       <c r="H101" s="64"/>
       <c r="I101" s="61"/>
       <c r="K101" s="15"/>
-      <c r="L101" s="73"/>
+      <c r="L101" s="78"/>
     </row>
     <row r="102" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="18">
@@ -16522,7 +16488,7 @@
       <c r="H102" s="65"/>
       <c r="I102" s="62"/>
       <c r="K102" s="16"/>
-      <c r="L102" s="74"/>
+      <c r="L102" s="78"/>
     </row>
     <row r="103" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="51" t="s">
@@ -16580,16 +16546,16 @@
   <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="75" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="75" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="75" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="75" customWidth="1"/>
-    <col min="8" max="9" width="10.625" style="75" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="75" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="75" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="72" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="72" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="72" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="72" customWidth="1"/>
+    <col min="8" max="9" width="10.625" style="72" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -16605,7 +16571,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
@@ -16650,9 +16616,7 @@
       <c r="K2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="72" t="s">
-        <v>25</v>
-      </c>
+      <c r="L2" s="77"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="18">
@@ -16667,7 +16631,7 @@
       <c r="H3" s="63"/>
       <c r="I3" s="61"/>
       <c r="K3" s="15"/>
-      <c r="L3" s="73"/>
+      <c r="L3" s="78"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18">
@@ -16682,7 +16646,7 @@
       <c r="H4" s="64"/>
       <c r="I4" s="61"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="73"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18">
@@ -16697,7 +16661,7 @@
       <c r="H5" s="64"/>
       <c r="I5" s="61"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="73"/>
+      <c r="L5" s="78"/>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18">
@@ -16712,7 +16676,7 @@
       <c r="H6" s="64"/>
       <c r="I6" s="61"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="73"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18">
@@ -16727,7 +16691,7 @@
       <c r="H7" s="64"/>
       <c r="I7" s="61"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="73"/>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18">
@@ -16742,7 +16706,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="61"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="73"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18">
@@ -16757,7 +16721,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="61"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="73"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18">
@@ -16772,7 +16736,7 @@
       <c r="H10" s="64"/>
       <c r="I10" s="61"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="73"/>
+      <c r="L10" s="78"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18">
@@ -16787,7 +16751,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="61"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="73"/>
+      <c r="L11" s="78"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18">
@@ -16802,7 +16766,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="61"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="73"/>
+      <c r="L12" s="78"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="18">
@@ -16817,7 +16781,7 @@
       <c r="H13" s="64"/>
       <c r="I13" s="61"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="73"/>
+      <c r="L13" s="78"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18">
@@ -16832,7 +16796,7 @@
       <c r="H14" s="64"/>
       <c r="I14" s="61"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="73"/>
+      <c r="L14" s="78"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18">
@@ -16847,7 +16811,7 @@
       <c r="H15" s="64"/>
       <c r="I15" s="61"/>
       <c r="K15" s="15"/>
-      <c r="L15" s="73"/>
+      <c r="L15" s="78"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18">
@@ -16862,7 +16826,7 @@
       <c r="H16" s="64"/>
       <c r="I16" s="61"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="73"/>
+      <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18">
@@ -16877,7 +16841,7 @@
       <c r="H17" s="64"/>
       <c r="I17" s="61"/>
       <c r="K17" s="15"/>
-      <c r="L17" s="73"/>
+      <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18">
@@ -16892,7 +16856,7 @@
       <c r="H18" s="64"/>
       <c r="I18" s="61"/>
       <c r="K18" s="15"/>
-      <c r="L18" s="73"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18">
@@ -16907,7 +16871,7 @@
       <c r="H19" s="64"/>
       <c r="I19" s="61"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="73"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18">
@@ -16922,7 +16886,7 @@
       <c r="H20" s="64"/>
       <c r="I20" s="61"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="73"/>
+      <c r="L20" s="78"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18">
@@ -16937,7 +16901,7 @@
       <c r="H21" s="64"/>
       <c r="I21" s="61"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="73"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18">
@@ -16952,7 +16916,7 @@
       <c r="H22" s="64"/>
       <c r="I22" s="61"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="73"/>
+      <c r="L22" s="78"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18">
@@ -16967,7 +16931,7 @@
       <c r="H23" s="64"/>
       <c r="I23" s="61"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="73"/>
+      <c r="L23" s="78"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18">
@@ -16982,7 +16946,7 @@
       <c r="H24" s="64"/>
       <c r="I24" s="61"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="73"/>
+      <c r="L24" s="78"/>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18">
@@ -16997,7 +16961,7 @@
       <c r="H25" s="64"/>
       <c r="I25" s="61"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="73"/>
+      <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18">
@@ -17012,7 +16976,7 @@
       <c r="H26" s="64"/>
       <c r="I26" s="61"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="73"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="18">
@@ -17027,7 +16991,7 @@
       <c r="H27" s="64"/>
       <c r="I27" s="61"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="73"/>
+      <c r="L27" s="78"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18">
@@ -17042,7 +17006,7 @@
       <c r="H28" s="64"/>
       <c r="I28" s="61"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="73"/>
+      <c r="L28" s="78"/>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18">
@@ -17057,7 +17021,7 @@
       <c r="H29" s="64"/>
       <c r="I29" s="61"/>
       <c r="K29" s="15"/>
-      <c r="L29" s="73"/>
+      <c r="L29" s="78"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18">
@@ -17072,7 +17036,7 @@
       <c r="H30" s="64"/>
       <c r="I30" s="61"/>
       <c r="K30" s="15"/>
-      <c r="L30" s="73"/>
+      <c r="L30" s="78"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18">
@@ -17087,7 +17051,7 @@
       <c r="H31" s="64"/>
       <c r="I31" s="61"/>
       <c r="K31" s="15"/>
-      <c r="L31" s="73"/>
+      <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18">
@@ -17102,7 +17066,7 @@
       <c r="H32" s="64"/>
       <c r="I32" s="61"/>
       <c r="K32" s="15"/>
-      <c r="L32" s="73"/>
+      <c r="L32" s="78"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18">
@@ -17117,7 +17081,7 @@
       <c r="H33" s="64"/>
       <c r="I33" s="61"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="73"/>
+      <c r="L33" s="78"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18">
@@ -17132,7 +17096,7 @@
       <c r="H34" s="64"/>
       <c r="I34" s="61"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="73"/>
+      <c r="L34" s="78"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18">
@@ -17147,7 +17111,7 @@
       <c r="H35" s="64"/>
       <c r="I35" s="61"/>
       <c r="K35" s="15"/>
-      <c r="L35" s="73"/>
+      <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18">
@@ -17162,7 +17126,7 @@
       <c r="H36" s="64"/>
       <c r="I36" s="61"/>
       <c r="K36" s="15"/>
-      <c r="L36" s="73"/>
+      <c r="L36" s="78"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18">
@@ -17177,7 +17141,7 @@
       <c r="H37" s="64"/>
       <c r="I37" s="61"/>
       <c r="K37" s="15"/>
-      <c r="L37" s="73"/>
+      <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18">
@@ -17192,7 +17156,7 @@
       <c r="H38" s="64"/>
       <c r="I38" s="61"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="78"/>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18">
@@ -17207,7 +17171,7 @@
       <c r="H39" s="64"/>
       <c r="I39" s="61"/>
       <c r="K39" s="15"/>
-      <c r="L39" s="73"/>
+      <c r="L39" s="78"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18">
@@ -17222,7 +17186,7 @@
       <c r="H40" s="64"/>
       <c r="I40" s="61"/>
       <c r="K40" s="15"/>
-      <c r="L40" s="73"/>
+      <c r="L40" s="78"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18">
@@ -17237,7 +17201,7 @@
       <c r="H41" s="64"/>
       <c r="I41" s="61"/>
       <c r="K41" s="15"/>
-      <c r="L41" s="73"/>
+      <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18">
@@ -17252,7 +17216,7 @@
       <c r="H42" s="64"/>
       <c r="I42" s="61"/>
       <c r="K42" s="15"/>
-      <c r="L42" s="73"/>
+      <c r="L42" s="78"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18">
@@ -17267,7 +17231,7 @@
       <c r="H43" s="64"/>
       <c r="I43" s="61"/>
       <c r="K43" s="15"/>
-      <c r="L43" s="73"/>
+      <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18">
@@ -17282,7 +17246,7 @@
       <c r="H44" s="64"/>
       <c r="I44" s="61"/>
       <c r="K44" s="15"/>
-      <c r="L44" s="73"/>
+      <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18">
@@ -17297,7 +17261,7 @@
       <c r="H45" s="64"/>
       <c r="I45" s="61"/>
       <c r="K45" s="15"/>
-      <c r="L45" s="73"/>
+      <c r="L45" s="78"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18">
@@ -17312,7 +17276,7 @@
       <c r="H46" s="64"/>
       <c r="I46" s="61"/>
       <c r="K46" s="15"/>
-      <c r="L46" s="73"/>
+      <c r="L46" s="78"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18">
@@ -17327,7 +17291,7 @@
       <c r="H47" s="64"/>
       <c r="I47" s="61"/>
       <c r="K47" s="15"/>
-      <c r="L47" s="73"/>
+      <c r="L47" s="78"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18">
@@ -17342,7 +17306,7 @@
       <c r="H48" s="64"/>
       <c r="I48" s="61"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="73"/>
+      <c r="L48" s="78"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18">
@@ -17357,7 +17321,7 @@
       <c r="H49" s="64"/>
       <c r="I49" s="61"/>
       <c r="K49" s="15"/>
-      <c r="L49" s="73"/>
+      <c r="L49" s="78"/>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18">
@@ -17372,7 +17336,7 @@
       <c r="H50" s="64"/>
       <c r="I50" s="61"/>
       <c r="K50" s="15"/>
-      <c r="L50" s="73"/>
+      <c r="L50" s="78"/>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18">
@@ -17387,7 +17351,7 @@
       <c r="H51" s="64"/>
       <c r="I51" s="61"/>
       <c r="K51" s="15"/>
-      <c r="L51" s="73"/>
+      <c r="L51" s="78"/>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18">
@@ -17402,7 +17366,7 @@
       <c r="H52" s="64"/>
       <c r="I52" s="61"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="73"/>
+      <c r="L52" s="78"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="18">
@@ -17417,7 +17381,7 @@
       <c r="H53" s="64"/>
       <c r="I53" s="61"/>
       <c r="K53" s="15"/>
-      <c r="L53" s="73"/>
+      <c r="L53" s="78"/>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18">
@@ -17432,7 +17396,7 @@
       <c r="H54" s="64"/>
       <c r="I54" s="61"/>
       <c r="K54" s="15"/>
-      <c r="L54" s="73"/>
+      <c r="L54" s="78"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18">
@@ -17447,7 +17411,7 @@
       <c r="H55" s="64"/>
       <c r="I55" s="61"/>
       <c r="K55" s="15"/>
-      <c r="L55" s="73"/>
+      <c r="L55" s="78"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18">
@@ -17462,7 +17426,7 @@
       <c r="H56" s="64"/>
       <c r="I56" s="61"/>
       <c r="K56" s="15"/>
-      <c r="L56" s="73"/>
+      <c r="L56" s="78"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18">
@@ -17477,7 +17441,7 @@
       <c r="H57" s="64"/>
       <c r="I57" s="61"/>
       <c r="K57" s="15"/>
-      <c r="L57" s="73"/>
+      <c r="L57" s="78"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18">
@@ -17492,7 +17456,7 @@
       <c r="H58" s="64"/>
       <c r="I58" s="61"/>
       <c r="K58" s="15"/>
-      <c r="L58" s="73"/>
+      <c r="L58" s="78"/>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18">
@@ -17507,7 +17471,7 @@
       <c r="H59" s="64"/>
       <c r="I59" s="61"/>
       <c r="K59" s="15"/>
-      <c r="L59" s="73"/>
+      <c r="L59" s="78"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18">
@@ -17522,7 +17486,7 @@
       <c r="H60" s="64"/>
       <c r="I60" s="61"/>
       <c r="K60" s="15"/>
-      <c r="L60" s="73"/>
+      <c r="L60" s="78"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18">
@@ -17537,7 +17501,7 @@
       <c r="H61" s="64"/>
       <c r="I61" s="61"/>
       <c r="K61" s="15"/>
-      <c r="L61" s="73"/>
+      <c r="L61" s="78"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="18">
@@ -17552,7 +17516,7 @@
       <c r="H62" s="64"/>
       <c r="I62" s="61"/>
       <c r="K62" s="15"/>
-      <c r="L62" s="73"/>
+      <c r="L62" s="78"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18">
@@ -17567,7 +17531,7 @@
       <c r="H63" s="64"/>
       <c r="I63" s="61"/>
       <c r="K63" s="15"/>
-      <c r="L63" s="73"/>
+      <c r="L63" s="78"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18">
@@ -17582,7 +17546,7 @@
       <c r="H64" s="64"/>
       <c r="I64" s="61"/>
       <c r="K64" s="15"/>
-      <c r="L64" s="73"/>
+      <c r="L64" s="78"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18">
@@ -17597,7 +17561,7 @@
       <c r="H65" s="64"/>
       <c r="I65" s="61"/>
       <c r="K65" s="15"/>
-      <c r="L65" s="73"/>
+      <c r="L65" s="78"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18">
@@ -17612,7 +17576,7 @@
       <c r="H66" s="64"/>
       <c r="I66" s="61"/>
       <c r="K66" s="15"/>
-      <c r="L66" s="73"/>
+      <c r="L66" s="78"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18">
@@ -17627,7 +17591,7 @@
       <c r="H67" s="64"/>
       <c r="I67" s="61"/>
       <c r="K67" s="15"/>
-      <c r="L67" s="73"/>
+      <c r="L67" s="78"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18">
@@ -17642,7 +17606,7 @@
       <c r="H68" s="64"/>
       <c r="I68" s="61"/>
       <c r="K68" s="15"/>
-      <c r="L68" s="73"/>
+      <c r="L68" s="78"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18">
@@ -17657,7 +17621,7 @@
       <c r="H69" s="64"/>
       <c r="I69" s="61"/>
       <c r="K69" s="15"/>
-      <c r="L69" s="73"/>
+      <c r="L69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18">
@@ -17672,7 +17636,7 @@
       <c r="H70" s="64"/>
       <c r="I70" s="61"/>
       <c r="K70" s="15"/>
-      <c r="L70" s="73"/>
+      <c r="L70" s="78"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18">
@@ -17687,7 +17651,7 @@
       <c r="H71" s="64"/>
       <c r="I71" s="61"/>
       <c r="K71" s="15"/>
-      <c r="L71" s="73"/>
+      <c r="L71" s="78"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18">
@@ -17702,7 +17666,7 @@
       <c r="H72" s="64"/>
       <c r="I72" s="61"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="73"/>
+      <c r="L72" s="78"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18">
@@ -17717,7 +17681,7 @@
       <c r="H73" s="64"/>
       <c r="I73" s="61"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="73"/>
+      <c r="L73" s="78"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18">
@@ -17732,7 +17696,7 @@
       <c r="H74" s="64"/>
       <c r="I74" s="61"/>
       <c r="K74" s="15"/>
-      <c r="L74" s="73"/>
+      <c r="L74" s="78"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18">
@@ -17747,7 +17711,7 @@
       <c r="H75" s="64"/>
       <c r="I75" s="61"/>
       <c r="K75" s="15"/>
-      <c r="L75" s="73"/>
+      <c r="L75" s="78"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="18">
@@ -17762,7 +17726,7 @@
       <c r="H76" s="64"/>
       <c r="I76" s="61"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="73"/>
+      <c r="L76" s="78"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18">
@@ -17777,7 +17741,7 @@
       <c r="H77" s="64"/>
       <c r="I77" s="61"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="73"/>
+      <c r="L77" s="78"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18">
@@ -17792,7 +17756,7 @@
       <c r="H78" s="64"/>
       <c r="I78" s="61"/>
       <c r="K78" s="15"/>
-      <c r="L78" s="73"/>
+      <c r="L78" s="78"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18">
@@ -17807,7 +17771,7 @@
       <c r="H79" s="64"/>
       <c r="I79" s="61"/>
       <c r="K79" s="15"/>
-      <c r="L79" s="73"/>
+      <c r="L79" s="78"/>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18">
@@ -17822,7 +17786,7 @@
       <c r="H80" s="64"/>
       <c r="I80" s="61"/>
       <c r="K80" s="15"/>
-      <c r="L80" s="73"/>
+      <c r="L80" s="78"/>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18">
@@ -17837,7 +17801,7 @@
       <c r="H81" s="64"/>
       <c r="I81" s="61"/>
       <c r="K81" s="15"/>
-      <c r="L81" s="73"/>
+      <c r="L81" s="78"/>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18">
@@ -17852,7 +17816,7 @@
       <c r="H82" s="64"/>
       <c r="I82" s="61"/>
       <c r="K82" s="15"/>
-      <c r="L82" s="73"/>
+      <c r="L82" s="78"/>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18">
@@ -17867,7 +17831,7 @@
       <c r="H83" s="64"/>
       <c r="I83" s="61"/>
       <c r="K83" s="15"/>
-      <c r="L83" s="73"/>
+      <c r="L83" s="78"/>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18">
@@ -17882,7 +17846,7 @@
       <c r="H84" s="64"/>
       <c r="I84" s="61"/>
       <c r="K84" s="15"/>
-      <c r="L84" s="73"/>
+      <c r="L84" s="78"/>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18">
@@ -17897,7 +17861,7 @@
       <c r="H85" s="64"/>
       <c r="I85" s="61"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="73"/>
+      <c r="L85" s="78"/>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18">
@@ -17912,7 +17876,7 @@
       <c r="H86" s="64"/>
       <c r="I86" s="61"/>
       <c r="K86" s="15"/>
-      <c r="L86" s="73"/>
+      <c r="L86" s="78"/>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18">
@@ -17927,7 +17891,7 @@
       <c r="H87" s="64"/>
       <c r="I87" s="61"/>
       <c r="K87" s="15"/>
-      <c r="L87" s="73"/>
+      <c r="L87" s="78"/>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18">
@@ -17942,7 +17906,7 @@
       <c r="H88" s="64"/>
       <c r="I88" s="61"/>
       <c r="K88" s="15"/>
-      <c r="L88" s="73"/>
+      <c r="L88" s="78"/>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="18">
@@ -17957,7 +17921,7 @@
       <c r="H89" s="64"/>
       <c r="I89" s="61"/>
       <c r="K89" s="15"/>
-      <c r="L89" s="73"/>
+      <c r="L89" s="78"/>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18">
@@ -17972,7 +17936,7 @@
       <c r="H90" s="64"/>
       <c r="I90" s="61"/>
       <c r="K90" s="15"/>
-      <c r="L90" s="73"/>
+      <c r="L90" s="78"/>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18">
@@ -17987,7 +17951,7 @@
       <c r="H91" s="64"/>
       <c r="I91" s="61"/>
       <c r="K91" s="15"/>
-      <c r="L91" s="73"/>
+      <c r="L91" s="78"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18">
@@ -18002,7 +17966,7 @@
       <c r="H92" s="64"/>
       <c r="I92" s="61"/>
       <c r="K92" s="15"/>
-      <c r="L92" s="73"/>
+      <c r="L92" s="78"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18">
@@ -18017,7 +17981,7 @@
       <c r="H93" s="64"/>
       <c r="I93" s="61"/>
       <c r="K93" s="15"/>
-      <c r="L93" s="73"/>
+      <c r="L93" s="78"/>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18">
@@ -18032,7 +17996,7 @@
       <c r="H94" s="64"/>
       <c r="I94" s="61"/>
       <c r="K94" s="15"/>
-      <c r="L94" s="73"/>
+      <c r="L94" s="78"/>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18">
@@ -18047,7 +18011,7 @@
       <c r="H95" s="64"/>
       <c r="I95" s="61"/>
       <c r="K95" s="15"/>
-      <c r="L95" s="73"/>
+      <c r="L95" s="78"/>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18">
@@ -18062,7 +18026,7 @@
       <c r="H96" s="64"/>
       <c r="I96" s="61"/>
       <c r="K96" s="15"/>
-      <c r="L96" s="73"/>
+      <c r="L96" s="78"/>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="18">
@@ -18077,7 +18041,7 @@
       <c r="H97" s="64"/>
       <c r="I97" s="61"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="73"/>
+      <c r="L97" s="78"/>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="18">
@@ -18092,7 +18056,7 @@
       <c r="H98" s="64"/>
       <c r="I98" s="61"/>
       <c r="K98" s="15"/>
-      <c r="L98" s="73"/>
+      <c r="L98" s="78"/>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="18">
@@ -18107,7 +18071,7 @@
       <c r="H99" s="64"/>
       <c r="I99" s="61"/>
       <c r="K99" s="15"/>
-      <c r="L99" s="73"/>
+      <c r="L99" s="78"/>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="18">
@@ -18122,7 +18086,7 @@
       <c r="H100" s="64"/>
       <c r="I100" s="61"/>
       <c r="K100" s="15"/>
-      <c r="L100" s="73"/>
+      <c r="L100" s="78"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A101" s="18">
@@ -18137,7 +18101,7 @@
       <c r="H101" s="64"/>
       <c r="I101" s="61"/>
       <c r="K101" s="15"/>
-      <c r="L101" s="73"/>
+      <c r="L101" s="78"/>
     </row>
     <row r="102" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="18">
@@ -18152,7 +18116,7 @@
       <c r="H102" s="65"/>
       <c r="I102" s="62"/>
       <c r="K102" s="16"/>
-      <c r="L102" s="74"/>
+      <c r="L102" s="78"/>
     </row>
     <row r="103" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="51" t="s">
@@ -18210,16 +18174,16 @@
   <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="75" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="75" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="75" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="75" customWidth="1"/>
-    <col min="8" max="9" width="10.625" style="75" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="75" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="75" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="72" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="72" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="72" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="72" customWidth="1"/>
+    <col min="8" max="9" width="10.625" style="72" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -18235,7 +18199,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="59"/>
@@ -18280,9 +18244,7 @@
       <c r="K2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="72" t="s">
-        <v>25</v>
-      </c>
+      <c r="L2" s="77"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="18">
@@ -18297,7 +18259,7 @@
       <c r="H3" s="63"/>
       <c r="I3" s="61"/>
       <c r="K3" s="15"/>
-      <c r="L3" s="73"/>
+      <c r="L3" s="78"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18">
@@ -18312,7 +18274,7 @@
       <c r="H4" s="64"/>
       <c r="I4" s="61"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="73"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18">
@@ -18327,7 +18289,7 @@
       <c r="H5" s="64"/>
       <c r="I5" s="61"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="73"/>
+      <c r="L5" s="78"/>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18">
@@ -18342,7 +18304,7 @@
       <c r="H6" s="64"/>
       <c r="I6" s="61"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="73"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18">
@@ -18357,7 +18319,7 @@
       <c r="H7" s="64"/>
       <c r="I7" s="61"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="73"/>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18">
@@ -18372,7 +18334,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="61"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="73"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18">
@@ -18387,7 +18349,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="61"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="73"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18">
@@ -18402,7 +18364,7 @@
       <c r="H10" s="64"/>
       <c r="I10" s="61"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="73"/>
+      <c r="L10" s="78"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18">
@@ -18417,7 +18379,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="61"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="73"/>
+      <c r="L11" s="78"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18">
@@ -18432,7 +18394,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="61"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="73"/>
+      <c r="L12" s="78"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="18">
@@ -18447,7 +18409,7 @@
       <c r="H13" s="64"/>
       <c r="I13" s="61"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="73"/>
+      <c r="L13" s="78"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18">
@@ -18462,7 +18424,7 @@
       <c r="H14" s="64"/>
       <c r="I14" s="61"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="73"/>
+      <c r="L14" s="78"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18">
@@ -18477,7 +18439,7 @@
       <c r="H15" s="64"/>
       <c r="I15" s="61"/>
       <c r="K15" s="15"/>
-      <c r="L15" s="73"/>
+      <c r="L15" s="78"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18">
@@ -18492,7 +18454,7 @@
       <c r="H16" s="64"/>
       <c r="I16" s="61"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="73"/>
+      <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18">
@@ -18507,7 +18469,7 @@
       <c r="H17" s="64"/>
       <c r="I17" s="61"/>
       <c r="K17" s="15"/>
-      <c r="L17" s="73"/>
+      <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18">
@@ -18522,7 +18484,7 @@
       <c r="H18" s="64"/>
       <c r="I18" s="61"/>
       <c r="K18" s="15"/>
-      <c r="L18" s="73"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18">
@@ -18537,7 +18499,7 @@
       <c r="H19" s="64"/>
       <c r="I19" s="61"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="73"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18">
@@ -18552,7 +18514,7 @@
       <c r="H20" s="64"/>
       <c r="I20" s="61"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="73"/>
+      <c r="L20" s="78"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18">
@@ -18567,7 +18529,7 @@
       <c r="H21" s="64"/>
       <c r="I21" s="61"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="73"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18">
@@ -18582,7 +18544,7 @@
       <c r="H22" s="64"/>
       <c r="I22" s="61"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="73"/>
+      <c r="L22" s="78"/>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18">
@@ -18597,7 +18559,7 @@
       <c r="H23" s="64"/>
       <c r="I23" s="61"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="73"/>
+      <c r="L23" s="78"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18">
@@ -18612,7 +18574,7 @@
       <c r="H24" s="64"/>
       <c r="I24" s="61"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="73"/>
+      <c r="L24" s="78"/>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18">
@@ -18627,7 +18589,7 @@
       <c r="H25" s="64"/>
       <c r="I25" s="61"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="73"/>
+      <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18">
@@ -18642,7 +18604,7 @@
       <c r="H26" s="64"/>
       <c r="I26" s="61"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="73"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="18">
@@ -18657,7 +18619,7 @@
       <c r="H27" s="64"/>
       <c r="I27" s="61"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="73"/>
+      <c r="L27" s="78"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18">
@@ -18672,7 +18634,7 @@
       <c r="H28" s="64"/>
       <c r="I28" s="61"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="73"/>
+      <c r="L28" s="78"/>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18">
@@ -18687,7 +18649,7 @@
       <c r="H29" s="64"/>
       <c r="I29" s="61"/>
       <c r="K29" s="15"/>
-      <c r="L29" s="73"/>
+      <c r="L29" s="78"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18">
@@ -18702,7 +18664,7 @@
       <c r="H30" s="64"/>
       <c r="I30" s="61"/>
       <c r="K30" s="15"/>
-      <c r="L30" s="73"/>
+      <c r="L30" s="78"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18">
@@ -18717,7 +18679,7 @@
       <c r="H31" s="64"/>
       <c r="I31" s="61"/>
       <c r="K31" s="15"/>
-      <c r="L31" s="73"/>
+      <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18">
@@ -18732,7 +18694,7 @@
       <c r="H32" s="64"/>
       <c r="I32" s="61"/>
       <c r="K32" s="15"/>
-      <c r="L32" s="73"/>
+      <c r="L32" s="78"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18">
@@ -18747,7 +18709,7 @@
       <c r="H33" s="64"/>
       <c r="I33" s="61"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="73"/>
+      <c r="L33" s="78"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18">
@@ -18762,7 +18724,7 @@
       <c r="H34" s="64"/>
       <c r="I34" s="61"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="73"/>
+      <c r="L34" s="78"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18">
@@ -18777,7 +18739,7 @@
       <c r="H35" s="64"/>
       <c r="I35" s="61"/>
       <c r="K35" s="15"/>
-      <c r="L35" s="73"/>
+      <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18">
@@ -18792,7 +18754,7 @@
       <c r="H36" s="64"/>
       <c r="I36" s="61"/>
       <c r="K36" s="15"/>
-      <c r="L36" s="73"/>
+      <c r="L36" s="78"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18">
@@ -18807,7 +18769,7 @@
       <c r="H37" s="64"/>
       <c r="I37" s="61"/>
       <c r="K37" s="15"/>
-      <c r="L37" s="73"/>
+      <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18">
@@ -18822,7 +18784,7 @@
       <c r="H38" s="64"/>
       <c r="I38" s="61"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="78"/>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18">
@@ -18837,7 +18799,7 @@
       <c r="H39" s="64"/>
       <c r="I39" s="61"/>
       <c r="K39" s="15"/>
-      <c r="L39" s="73"/>
+      <c r="L39" s="78"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18">
@@ -18852,7 +18814,7 @@
       <c r="H40" s="64"/>
       <c r="I40" s="61"/>
       <c r="K40" s="15"/>
-      <c r="L40" s="73"/>
+      <c r="L40" s="78"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18">
@@ -18867,7 +18829,7 @@
       <c r="H41" s="64"/>
       <c r="I41" s="61"/>
       <c r="K41" s="15"/>
-      <c r="L41" s="73"/>
+      <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18">
@@ -18882,7 +18844,7 @@
       <c r="H42" s="64"/>
       <c r="I42" s="61"/>
       <c r="K42" s="15"/>
-      <c r="L42" s="73"/>
+      <c r="L42" s="78"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18">
@@ -18897,7 +18859,7 @@
       <c r="H43" s="64"/>
       <c r="I43" s="61"/>
       <c r="K43" s="15"/>
-      <c r="L43" s="73"/>
+      <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18">
@@ -18912,7 +18874,7 @@
       <c r="H44" s="64"/>
       <c r="I44" s="61"/>
       <c r="K44" s="15"/>
-      <c r="L44" s="73"/>
+      <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18">
@@ -18927,7 +18889,7 @@
       <c r="H45" s="64"/>
       <c r="I45" s="61"/>
       <c r="K45" s="15"/>
-      <c r="L45" s="73"/>
+      <c r="L45" s="78"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18">
@@ -18942,7 +18904,7 @@
       <c r="H46" s="64"/>
       <c r="I46" s="61"/>
       <c r="K46" s="15"/>
-      <c r="L46" s="73"/>
+      <c r="L46" s="78"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18">
@@ -18957,7 +18919,7 @@
       <c r="H47" s="64"/>
       <c r="I47" s="61"/>
       <c r="K47" s="15"/>
-      <c r="L47" s="73"/>
+      <c r="L47" s="78"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18">
@@ -18972,7 +18934,7 @@
       <c r="H48" s="64"/>
       <c r="I48" s="61"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="73"/>
+      <c r="L48" s="78"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18">
@@ -18987,7 +18949,7 @@
       <c r="H49" s="64"/>
       <c r="I49" s="61"/>
       <c r="K49" s="15"/>
-      <c r="L49" s="73"/>
+      <c r="L49" s="78"/>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18">
@@ -19002,7 +18964,7 @@
       <c r="H50" s="64"/>
       <c r="I50" s="61"/>
       <c r="K50" s="15"/>
-      <c r="L50" s="73"/>
+      <c r="L50" s="78"/>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18">
@@ -19017,7 +18979,7 @@
       <c r="H51" s="64"/>
       <c r="I51" s="61"/>
       <c r="K51" s="15"/>
-      <c r="L51" s="73"/>
+      <c r="L51" s="78"/>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18">
@@ -19032,7 +18994,7 @@
       <c r="H52" s="64"/>
       <c r="I52" s="61"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="73"/>
+      <c r="L52" s="78"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="18">
@@ -19047,7 +19009,7 @@
       <c r="H53" s="64"/>
       <c r="I53" s="61"/>
       <c r="K53" s="15"/>
-      <c r="L53" s="73"/>
+      <c r="L53" s="78"/>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18">
@@ -19062,7 +19024,7 @@
       <c r="H54" s="64"/>
       <c r="I54" s="61"/>
       <c r="K54" s="15"/>
-      <c r="L54" s="73"/>
+      <c r="L54" s="78"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18">
@@ -19077,7 +19039,7 @@
       <c r="H55" s="64"/>
       <c r="I55" s="61"/>
       <c r="K55" s="15"/>
-      <c r="L55" s="73"/>
+      <c r="L55" s="78"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18">
@@ -19092,7 +19054,7 @@
       <c r="H56" s="64"/>
       <c r="I56" s="61"/>
       <c r="K56" s="15"/>
-      <c r="L56" s="73"/>
+      <c r="L56" s="78"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18">
@@ -19107,7 +19069,7 @@
       <c r="H57" s="64"/>
       <c r="I57" s="61"/>
       <c r="K57" s="15"/>
-      <c r="L57" s="73"/>
+      <c r="L57" s="78"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18">
@@ -19122,7 +19084,7 @@
       <c r="H58" s="64"/>
       <c r="I58" s="61"/>
       <c r="K58" s="15"/>
-      <c r="L58" s="73"/>
+      <c r="L58" s="78"/>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18">
@@ -19137,7 +19099,7 @@
       <c r="H59" s="64"/>
       <c r="I59" s="61"/>
       <c r="K59" s="15"/>
-      <c r="L59" s="73"/>
+      <c r="L59" s="78"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18">
@@ -19152,7 +19114,7 @@
       <c r="H60" s="64"/>
       <c r="I60" s="61"/>
       <c r="K60" s="15"/>
-      <c r="L60" s="73"/>
+      <c r="L60" s="78"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18">
@@ -19167,7 +19129,7 @@
       <c r="H61" s="64"/>
       <c r="I61" s="61"/>
       <c r="K61" s="15"/>
-      <c r="L61" s="73"/>
+      <c r="L61" s="78"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="18">
@@ -19182,7 +19144,7 @@
       <c r="H62" s="64"/>
       <c r="I62" s="61"/>
       <c r="K62" s="15"/>
-      <c r="L62" s="73"/>
+      <c r="L62" s="78"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18">
@@ -19197,7 +19159,7 @@
       <c r="H63" s="64"/>
       <c r="I63" s="61"/>
       <c r="K63" s="15"/>
-      <c r="L63" s="73"/>
+      <c r="L63" s="78"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18">
@@ -19212,7 +19174,7 @@
       <c r="H64" s="64"/>
       <c r="I64" s="61"/>
       <c r="K64" s="15"/>
-      <c r="L64" s="73"/>
+      <c r="L64" s="78"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18">
@@ -19227,7 +19189,7 @@
       <c r="H65" s="64"/>
       <c r="I65" s="61"/>
       <c r="K65" s="15"/>
-      <c r="L65" s="73"/>
+      <c r="L65" s="78"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18">
@@ -19242,7 +19204,7 @@
       <c r="H66" s="64"/>
       <c r="I66" s="61"/>
       <c r="K66" s="15"/>
-      <c r="L66" s="73"/>
+      <c r="L66" s="78"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18">
@@ -19257,7 +19219,7 @@
       <c r="H67" s="64"/>
       <c r="I67" s="61"/>
       <c r="K67" s="15"/>
-      <c r="L67" s="73"/>
+      <c r="L67" s="78"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18">
@@ -19272,7 +19234,7 @@
       <c r="H68" s="64"/>
       <c r="I68" s="61"/>
       <c r="K68" s="15"/>
-      <c r="L68" s="73"/>
+      <c r="L68" s="78"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18">
@@ -19287,7 +19249,7 @@
       <c r="H69" s="64"/>
       <c r="I69" s="61"/>
       <c r="K69" s="15"/>
-      <c r="L69" s="73"/>
+      <c r="L69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18">
@@ -19302,7 +19264,7 @@
       <c r="H70" s="64"/>
       <c r="I70" s="61"/>
       <c r="K70" s="15"/>
-      <c r="L70" s="73"/>
+      <c r="L70" s="78"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18">
@@ -19317,7 +19279,7 @@
       <c r="H71" s="64"/>
       <c r="I71" s="61"/>
       <c r="K71" s="15"/>
-      <c r="L71" s="73"/>
+      <c r="L71" s="78"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18">
@@ -19332,7 +19294,7 @@
       <c r="H72" s="64"/>
       <c r="I72" s="61"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="73"/>
+      <c r="L72" s="78"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18">
@@ -19347,7 +19309,7 @@
       <c r="H73" s="64"/>
       <c r="I73" s="61"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="73"/>
+      <c r="L73" s="78"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18">
@@ -19362,7 +19324,7 @@
       <c r="H74" s="64"/>
       <c r="I74" s="61"/>
       <c r="K74" s="15"/>
-      <c r="L74" s="73"/>
+      <c r="L74" s="78"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18">
@@ -19377,7 +19339,7 @@
       <c r="H75" s="64"/>
       <c r="I75" s="61"/>
       <c r="K75" s="15"/>
-      <c r="L75" s="73"/>
+      <c r="L75" s="78"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="18">
@@ -19392,7 +19354,7 @@
       <c r="H76" s="64"/>
       <c r="I76" s="61"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="73"/>
+      <c r="L76" s="78"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18">
@@ -19407,7 +19369,7 @@
       <c r="H77" s="64"/>
       <c r="I77" s="61"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="73"/>
+      <c r="L77" s="78"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18">
@@ -19422,7 +19384,7 @@
       <c r="H78" s="64"/>
       <c r="I78" s="61"/>
       <c r="K78" s="15"/>
-      <c r="L78" s="73"/>
+      <c r="L78" s="78"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18">
@@ -19437,7 +19399,7 @@
       <c r="H79" s="64"/>
       <c r="I79" s="61"/>
       <c r="K79" s="15"/>
-      <c r="L79" s="73"/>
+      <c r="L79" s="78"/>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18">
@@ -19452,7 +19414,7 @@
       <c r="H80" s="64"/>
       <c r="I80" s="61"/>
       <c r="K80" s="15"/>
-      <c r="L80" s="73"/>
+      <c r="L80" s="78"/>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18">
@@ -19467,7 +19429,7 @@
       <c r="H81" s="64"/>
       <c r="I81" s="61"/>
       <c r="K81" s="15"/>
-      <c r="L81" s="73"/>
+      <c r="L81" s="78"/>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18">
@@ -19482,7 +19444,7 @@
       <c r="H82" s="64"/>
       <c r="I82" s="61"/>
       <c r="K82" s="15"/>
-      <c r="L82" s="73"/>
+      <c r="L82" s="78"/>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18">
@@ -19497,7 +19459,7 @@
       <c r="H83" s="64"/>
       <c r="I83" s="61"/>
       <c r="K83" s="15"/>
-      <c r="L83" s="73"/>
+      <c r="L83" s="78"/>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18">
@@ -19512,7 +19474,7 @@
       <c r="H84" s="64"/>
       <c r="I84" s="61"/>
       <c r="K84" s="15"/>
-      <c r="L84" s="73"/>
+      <c r="L84" s="78"/>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18">
@@ -19527,7 +19489,7 @@
       <c r="H85" s="64"/>
       <c r="I85" s="61"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="73"/>
+      <c r="L85" s="78"/>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18">
@@ -19542,7 +19504,7 @@
       <c r="H86" s="64"/>
       <c r="I86" s="61"/>
       <c r="K86" s="15"/>
-      <c r="L86" s="73"/>
+      <c r="L86" s="78"/>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18">
@@ -19557,7 +19519,7 @@
       <c r="H87" s="64"/>
       <c r="I87" s="61"/>
       <c r="K87" s="15"/>
-      <c r="L87" s="73"/>
+      <c r="L87" s="78"/>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18">
@@ -19572,7 +19534,7 @@
       <c r="H88" s="64"/>
       <c r="I88" s="61"/>
       <c r="K88" s="15"/>
-      <c r="L88" s="73"/>
+      <c r="L88" s="78"/>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="18">
@@ -19587,7 +19549,7 @@
       <c r="H89" s="64"/>
       <c r="I89" s="61"/>
       <c r="K89" s="15"/>
-      <c r="L89" s="73"/>
+      <c r="L89" s="78"/>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18">
@@ -19602,7 +19564,7 @@
       <c r="H90" s="64"/>
       <c r="I90" s="61"/>
       <c r="K90" s="15"/>
-      <c r="L90" s="73"/>
+      <c r="L90" s="78"/>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18">
@@ -19617,7 +19579,7 @@
       <c r="H91" s="64"/>
       <c r="I91" s="61"/>
       <c r="K91" s="15"/>
-      <c r="L91" s="73"/>
+      <c r="L91" s="78"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18">
@@ -19632,7 +19594,7 @@
       <c r="H92" s="64"/>
       <c r="I92" s="61"/>
       <c r="K92" s="15"/>
-      <c r="L92" s="73"/>
+      <c r="L92" s="78"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18">
@@ -19647,7 +19609,7 @@
       <c r="H93" s="64"/>
       <c r="I93" s="61"/>
       <c r="K93" s="15"/>
-      <c r="L93" s="73"/>
+      <c r="L93" s="78"/>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18">
@@ -19662,7 +19624,7 @@
       <c r="H94" s="64"/>
       <c r="I94" s="61"/>
       <c r="K94" s="15"/>
-      <c r="L94" s="73"/>
+      <c r="L94" s="78"/>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18">
@@ -19677,7 +19639,7 @@
       <c r="H95" s="64"/>
       <c r="I95" s="61"/>
       <c r="K95" s="15"/>
-      <c r="L95" s="73"/>
+      <c r="L95" s="78"/>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18">
@@ -19692,7 +19654,7 @@
       <c r="H96" s="64"/>
       <c r="I96" s="61"/>
       <c r="K96" s="15"/>
-      <c r="L96" s="73"/>
+      <c r="L96" s="78"/>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="18">
@@ -19707,7 +19669,7 @@
       <c r="H97" s="64"/>
       <c r="I97" s="61"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="73"/>
+      <c r="L97" s="78"/>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="18">
@@ -19722,7 +19684,7 @@
       <c r="H98" s="64"/>
       <c r="I98" s="61"/>
       <c r="K98" s="15"/>
-      <c r="L98" s="73"/>
+      <c r="L98" s="78"/>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="18">
@@ -19737,7 +19699,7 @@
       <c r="H99" s="64"/>
       <c r="I99" s="61"/>
       <c r="K99" s="15"/>
-      <c r="L99" s="73"/>
+      <c r="L99" s="78"/>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="18">
@@ -19752,7 +19714,7 @@
       <c r="H100" s="64"/>
       <c r="I100" s="61"/>
       <c r="K100" s="15"/>
-      <c r="L100" s="73"/>
+      <c r="L100" s="78"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A101" s="18">
@@ -19767,7 +19729,7 @@
       <c r="H101" s="64"/>
       <c r="I101" s="61"/>
       <c r="K101" s="15"/>
-      <c r="L101" s="73"/>
+      <c r="L101" s="78"/>
     </row>
     <row r="102" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="18">
@@ -19782,7 +19744,7 @@
       <c r="H102" s="65"/>
       <c r="I102" s="62"/>
       <c r="K102" s="16"/>
-      <c r="L102" s="74"/>
+      <c r="L102" s="78"/>
     </row>
     <row r="103" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="51" t="s">
